--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122773452</v>
+        <v>122774696</v>
       </c>
       <c r="B18" t="n">
-        <v>57428</v>
+        <v>79843</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,47 +2383,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102621</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494786</v>
+        <v>494538</v>
       </c>
       <c r="R18" t="n">
-        <v>7023741</v>
+        <v>7023761</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2456,6 +2447,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2482,7 +2478,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122774696</v>
+        <v>122773465</v>
       </c>
       <c r="B19" t="n">
         <v>79843</v>
@@ -2516,16 +2512,21 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494538</v>
+        <v>494786</v>
       </c>
       <c r="R19" t="n">
-        <v>7023761</v>
+        <v>7023741</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2558,11 +2559,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2589,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122773465</v>
+        <v>122773452</v>
       </c>
       <c r="B20" t="n">
-        <v>79843</v>
+        <v>57428</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2601,31 +2597,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>102621</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2696,10 +2696,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122772413</v>
+        <v>122772994</v>
       </c>
       <c r="B21" t="n">
-        <v>79843</v>
+        <v>57631</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2712,34 +2712,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494559</v>
+        <v>494664</v>
       </c>
       <c r="R21" t="n">
-        <v>7023689</v>
+        <v>7023760</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,10 +2807,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122772994</v>
+        <v>122772413</v>
       </c>
       <c r="B22" t="n">
-        <v>57631</v>
+        <v>79843</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2814,43 +2823,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494664</v>
+        <v>494559</v>
       </c>
       <c r="R22" t="n">
-        <v>7023760</v>
+        <v>7023689</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122771901</v>
+        <v>122771489</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3654,39 +3654,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494516</v>
+        <v>494147</v>
       </c>
       <c r="R30" t="n">
-        <v>7023586</v>
+        <v>7023571</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3719,11 +3714,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3750,7 +3740,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122771891</v>
+        <v>122771901</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -3795,10 +3785,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494515</v>
+        <v>494516</v>
       </c>
       <c r="R31" t="n">
-        <v>7023580</v>
+        <v>7023586</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3862,7 +3852,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122770429</v>
+        <v>122771891</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -3903,14 +3893,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493992</v>
+        <v>494515</v>
       </c>
       <c r="R32" t="n">
-        <v>7023434</v>
+        <v>7023580</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3947,7 +3937,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3974,10 +3964,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122771489</v>
+        <v>122770429</v>
       </c>
       <c r="B33" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3990,34 +3980,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494147</v>
+        <v>493992</v>
       </c>
       <c r="R33" t="n">
-        <v>7023571</v>
+        <v>7023434</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4050,6 +4045,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4907,10 +4907,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122772874</v>
+        <v>122772729</v>
       </c>
       <c r="B42" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4923,27 +4923,27 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494680</v>
+        <v>494591</v>
       </c>
       <c r="R42" t="n">
-        <v>7023737</v>
+        <v>7023673</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4988,6 +4988,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5014,7 +5019,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122774764</v>
+        <v>122772874</v>
       </c>
       <c r="B43" t="n">
         <v>79843</v>
@@ -5048,16 +5053,21 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494568</v>
+        <v>494680</v>
       </c>
       <c r="R43" t="n">
-        <v>7023757</v>
+        <v>7023737</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5090,11 +5100,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5121,7 +5126,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122774597</v>
+        <v>122774764</v>
       </c>
       <c r="B44" t="n">
         <v>79843</v>
@@ -5161,10 +5166,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494556</v>
+        <v>494568</v>
       </c>
       <c r="R44" t="n">
-        <v>7023778</v>
+        <v>7023757</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5197,6 +5202,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5223,10 +5233,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122772729</v>
+        <v>122774597</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>79843</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5239,39 +5249,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494591</v>
+        <v>494556</v>
       </c>
       <c r="R45" t="n">
-        <v>7023673</v>
+        <v>7023778</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5304,11 +5309,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5860,7 +5860,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122773407</v>
+        <v>122772714</v>
       </c>
       <c r="B51" t="n">
         <v>79843</v>
@@ -5900,10 +5900,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494790</v>
+        <v>494589</v>
       </c>
       <c r="R51" t="n">
-        <v>7023741</v>
+        <v>7023675</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5936,11 +5936,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5967,7 +5962,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122772714</v>
+        <v>122773407</v>
       </c>
       <c r="B52" t="n">
         <v>79843</v>
@@ -6007,10 +6002,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494589</v>
+        <v>494790</v>
       </c>
       <c r="R52" t="n">
-        <v>7023675</v>
+        <v>7023741</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6043,6 +6038,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122773254</v>
+        <v>122774455</v>
       </c>
       <c r="B2" t="n">
-        <v>79843</v>
+        <v>91511</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494730</v>
+        <v>494571</v>
       </c>
       <c r="R2" t="n">
-        <v>7023730</v>
+        <v>7023780</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122771956</v>
+        <v>122772356</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494521</v>
+        <v>494558</v>
       </c>
       <c r="R3" t="n">
-        <v>7023591</v>
+        <v>7023688</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122771667</v>
+        <v>122774538</v>
       </c>
       <c r="B4" t="n">
-        <v>79803</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,38 +896,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494425</v>
+        <v>494563</v>
       </c>
       <c r="R4" t="n">
-        <v>7023600</v>
+        <v>7023781</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122774538</v>
+        <v>122771474</v>
       </c>
       <c r="B5" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494563</v>
+        <v>494356</v>
       </c>
       <c r="R5" t="n">
-        <v>7023781</v>
+        <v>7023575</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122771745</v>
+        <v>122774563</v>
       </c>
       <c r="B6" t="n">
-        <v>79843</v>
+        <v>79848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494449</v>
+        <v>494563</v>
       </c>
       <c r="R6" t="n">
-        <v>7023602</v>
+        <v>7023786</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122771384</v>
+        <v>122774987</v>
       </c>
       <c r="B7" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1216,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494334</v>
+        <v>494357</v>
       </c>
       <c r="R7" t="n">
-        <v>7023580</v>
+        <v>7023735</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122772044</v>
+        <v>122774745</v>
       </c>
       <c r="B8" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494524</v>
+        <v>494558</v>
       </c>
       <c r="R8" t="n">
-        <v>7023624</v>
+        <v>7023767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122772290</v>
+        <v>122771661</v>
       </c>
       <c r="B9" t="n">
-        <v>79843</v>
+        <v>79876</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,43 +1426,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494557</v>
+        <v>494425</v>
       </c>
       <c r="R9" t="n">
-        <v>7023675</v>
+        <v>7023600</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122774745</v>
+        <v>122774597</v>
       </c>
       <c r="B10" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494558</v>
+        <v>494556</v>
       </c>
       <c r="R10" t="n">
-        <v>7023767</v>
+        <v>7023778</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122772081</v>
+        <v>122773452</v>
       </c>
       <c r="B11" t="n">
-        <v>79843</v>
+        <v>57428</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,38 +1630,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>102621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494512</v>
+        <v>494786</v>
       </c>
       <c r="R11" t="n">
-        <v>7023641</v>
+        <v>7023741</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122774670</v>
+        <v>122773527</v>
       </c>
       <c r="B12" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,34 +1745,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494555</v>
+        <v>494802</v>
       </c>
       <c r="R12" t="n">
-        <v>7023779</v>
+        <v>7023657</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,6 +1810,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773216</v>
+        <v>122772729</v>
       </c>
       <c r="B13" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,27 +1857,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1867,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494716</v>
+        <v>494591</v>
       </c>
       <c r="R13" t="n">
-        <v>7023730</v>
+        <v>7023673</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,6 +1922,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122774455</v>
+        <v>122774696</v>
       </c>
       <c r="B14" t="n">
-        <v>91507</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1941,25 +1965,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1993,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494571</v>
+        <v>494538</v>
       </c>
       <c r="R14" t="n">
-        <v>7023780</v>
+        <v>7023761</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,6 +2029,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122770929</v>
+        <v>122772714</v>
       </c>
       <c r="B15" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,48 +2076,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494181</v>
+        <v>494589</v>
       </c>
       <c r="R15" t="n">
-        <v>7023603</v>
+        <v>7023675</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,10 +2162,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122777145</v>
+        <v>122772044</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2163,39 +2178,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494559</v>
+        <v>494524</v>
       </c>
       <c r="R16" t="n">
-        <v>7023653</v>
+        <v>7023624</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,11 +2238,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2259,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122772707</v>
+        <v>122771745</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2275,39 +2280,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494582</v>
+        <v>494449</v>
       </c>
       <c r="R17" t="n">
-        <v>7023673</v>
+        <v>7023602</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,11 +2340,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2371,10 +2366,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122774696</v>
+        <v>122770929</v>
       </c>
       <c r="B18" t="n">
-        <v>79843</v>
+        <v>57631</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,34 +2382,48 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494538</v>
+        <v>494181</v>
       </c>
       <c r="R18" t="n">
-        <v>7023761</v>
+        <v>7023603</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,11 +2456,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2478,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122773465</v>
+        <v>122771956</v>
       </c>
       <c r="B19" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2494,27 +2498,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2523,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494786</v>
+        <v>494521</v>
       </c>
       <c r="R19" t="n">
-        <v>7023741</v>
+        <v>7023591</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,6 +2563,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2585,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122773452</v>
+        <v>122774372</v>
       </c>
       <c r="B20" t="n">
-        <v>57428</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,47 +2606,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102621</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494786</v>
+        <v>494839</v>
       </c>
       <c r="R20" t="n">
-        <v>7023741</v>
+        <v>7023830</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,10 +2696,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122772994</v>
+        <v>122774566</v>
       </c>
       <c r="B21" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2712,43 +2712,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494664</v>
+        <v>494563</v>
       </c>
       <c r="R21" t="n">
-        <v>7023760</v>
+        <v>7023786</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,10 +2798,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122772413</v>
+        <v>122773216</v>
       </c>
       <c r="B22" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2841,16 +2832,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494559</v>
+        <v>494716</v>
       </c>
       <c r="R22" t="n">
-        <v>7023689</v>
+        <v>7023730</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2909,10 +2905,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122770882</v>
+        <v>122772985</v>
       </c>
       <c r="B23" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2925,34 +2921,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494160</v>
+        <v>494655</v>
       </c>
       <c r="R23" t="n">
-        <v>7023595</v>
+        <v>7023708</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2985,6 +2986,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3011,10 +3017,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122774372</v>
+        <v>122774828</v>
       </c>
       <c r="B24" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3051,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494839</v>
+        <v>494562</v>
       </c>
       <c r="R24" t="n">
-        <v>7023830</v>
+        <v>7023728</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122771655</v>
+        <v>122771891</v>
       </c>
       <c r="B25" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3129,34 +3135,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494427</v>
+        <v>494515</v>
       </c>
       <c r="R25" t="n">
-        <v>7023595</v>
+        <v>7023580</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3189,6 +3200,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3215,10 +3231,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122772531</v>
+        <v>122774764</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3231,39 +3247,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494557</v>
+        <v>494568</v>
       </c>
       <c r="R26" t="n">
-        <v>7023650</v>
+        <v>7023757</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3300,7 +3311,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3327,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122774777</v>
+        <v>122771489</v>
       </c>
       <c r="B27" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3343,34 +3354,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494582</v>
+        <v>494147</v>
       </c>
       <c r="R27" t="n">
-        <v>7023728</v>
+        <v>7023571</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3403,11 +3414,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3434,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122774693</v>
+        <v>122772081</v>
       </c>
       <c r="B28" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3474,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494544</v>
+        <v>494512</v>
       </c>
       <c r="R28" t="n">
-        <v>7023772</v>
+        <v>7023641</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3536,10 +3542,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122774393</v>
+        <v>122774715</v>
       </c>
       <c r="B29" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3576,10 +3582,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494710</v>
+        <v>494547</v>
       </c>
       <c r="R29" t="n">
-        <v>7023786</v>
+        <v>7023756</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3638,10 +3644,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122771489</v>
+        <v>122771655</v>
       </c>
       <c r="B30" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3654,34 +3660,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494147</v>
+        <v>494427</v>
       </c>
       <c r="R30" t="n">
-        <v>7023571</v>
+        <v>7023595</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3740,10 +3746,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122771901</v>
+        <v>122771384</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3756,39 +3762,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494516</v>
+        <v>494334</v>
       </c>
       <c r="R31" t="n">
-        <v>7023586</v>
+        <v>7023580</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3821,11 +3822,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3852,10 +3848,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122771891</v>
+        <v>122773319</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>90955</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3864,43 +3860,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494515</v>
+        <v>494758</v>
       </c>
       <c r="R32" t="n">
-        <v>7023580</v>
+        <v>7023767</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3933,11 +3924,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3964,10 +3950,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122770429</v>
+        <v>122773465</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3980,39 +3966,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493992</v>
+        <v>494786</v>
       </c>
       <c r="R33" t="n">
-        <v>7023434</v>
+        <v>7023741</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4045,11 +4031,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4076,10 +4057,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122773319</v>
+        <v>122773088</v>
       </c>
       <c r="B34" t="n">
-        <v>90951</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4088,38 +4069,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494758</v>
+        <v>494700</v>
       </c>
       <c r="R34" t="n">
-        <v>7023767</v>
+        <v>7023729</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4178,10 +4164,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122774563</v>
+        <v>122772874</v>
       </c>
       <c r="B35" t="n">
-        <v>79844</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4194,34 +4180,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494563</v>
+        <v>494680</v>
       </c>
       <c r="R35" t="n">
-        <v>7023786</v>
+        <v>7023737</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4280,10 +4271,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122774715</v>
+        <v>122773254</v>
       </c>
       <c r="B36" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4314,16 +4305,21 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494547</v>
+        <v>494730</v>
       </c>
       <c r="R36" t="n">
-        <v>7023756</v>
+        <v>7023730</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4382,10 +4378,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122772356</v>
+        <v>122772531</v>
       </c>
       <c r="B37" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4398,34 +4394,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494558</v>
+        <v>494557</v>
       </c>
       <c r="R37" t="n">
-        <v>7023688</v>
+        <v>7023650</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4462,7 +4463,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4489,10 +4490,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122773458</v>
+        <v>122772707</v>
       </c>
       <c r="B38" t="n">
-        <v>79844</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4505,34 +4506,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494786</v>
+        <v>494582</v>
       </c>
       <c r="R38" t="n">
-        <v>7023741</v>
+        <v>7023673</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,6 +4571,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4591,10 +4602,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122774828</v>
+        <v>122774464</v>
       </c>
       <c r="B39" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4625,16 +4636,21 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494562</v>
+        <v>494570</v>
       </c>
       <c r="R39" t="n">
-        <v>7023728</v>
+        <v>7023783</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4693,10 +4709,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122771481</v>
+        <v>122772030</v>
       </c>
       <c r="B40" t="n">
-        <v>79879</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4705,25 +4721,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4733,10 +4749,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494353</v>
+        <v>494526</v>
       </c>
       <c r="R40" t="n">
-        <v>7023580</v>
+        <v>7023606</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4795,10 +4811,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122772985</v>
+        <v>122774777</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4811,39 +4827,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494655</v>
+        <v>494582</v>
       </c>
       <c r="R41" t="n">
-        <v>7023708</v>
+        <v>7023728</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4880,7 +4891,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4907,10 +4918,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122772729</v>
+        <v>122774393</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4923,39 +4934,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494591</v>
+        <v>494710</v>
       </c>
       <c r="R42" t="n">
-        <v>7023673</v>
+        <v>7023786</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4988,11 +4994,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5019,10 +5020,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122772874</v>
+        <v>122774670</v>
       </c>
       <c r="B43" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5053,21 +5054,16 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494680</v>
+        <v>494555</v>
       </c>
       <c r="R43" t="n">
-        <v>7023737</v>
+        <v>7023779</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5126,10 +5122,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122774764</v>
+        <v>122772290</v>
       </c>
       <c r="B44" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5160,16 +5156,21 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494568</v>
+        <v>494557</v>
       </c>
       <c r="R44" t="n">
-        <v>7023757</v>
+        <v>7023675</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5202,11 +5203,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5233,10 +5229,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122774597</v>
+        <v>122770429</v>
       </c>
       <c r="B45" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5249,34 +5245,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494556</v>
+        <v>493992</v>
       </c>
       <c r="R45" t="n">
-        <v>7023778</v>
+        <v>7023434</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5309,6 +5310,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5335,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122771474</v>
+        <v>122772994</v>
       </c>
       <c r="B46" t="n">
-        <v>79843</v>
+        <v>57631</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5351,27 +5357,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5380,10 +5390,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494356</v>
+        <v>494664</v>
       </c>
       <c r="R46" t="n">
-        <v>7023575</v>
+        <v>7023760</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5442,10 +5452,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122772030</v>
+        <v>122773458</v>
       </c>
       <c r="B47" t="n">
-        <v>79843</v>
+        <v>79848</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5458,21 +5468,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5482,10 +5492,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494526</v>
+        <v>494786</v>
       </c>
       <c r="R47" t="n">
-        <v>7023606</v>
+        <v>7023741</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5544,7 +5554,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122773527</v>
+        <v>122771901</v>
       </c>
       <c r="B48" t="n">
         <v>57478</v>
@@ -5589,10 +5599,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494802</v>
+        <v>494516</v>
       </c>
       <c r="R48" t="n">
-        <v>7023657</v>
+        <v>7023586</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5656,10 +5666,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122771661</v>
+        <v>122770882</v>
       </c>
       <c r="B49" t="n">
-        <v>79872</v>
+        <v>90962</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5668,38 +5678,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494425</v>
+        <v>494160</v>
       </c>
       <c r="R49" t="n">
-        <v>7023600</v>
+        <v>7023595</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5758,10 +5768,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122774566</v>
+        <v>122771481</v>
       </c>
       <c r="B50" t="n">
-        <v>79843</v>
+        <v>79883</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5770,25 +5780,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5798,10 +5808,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494563</v>
+        <v>494353</v>
       </c>
       <c r="R50" t="n">
-        <v>7023786</v>
+        <v>7023580</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5860,10 +5870,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122772714</v>
+        <v>122772413</v>
       </c>
       <c r="B51" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5900,10 +5910,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494589</v>
+        <v>494559</v>
       </c>
       <c r="R51" t="n">
-        <v>7023675</v>
+        <v>7023689</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5962,10 +5972,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122773407</v>
+        <v>122777145</v>
       </c>
       <c r="B52" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5978,34 +5988,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494790</v>
+        <v>494559</v>
       </c>
       <c r="R52" t="n">
-        <v>7023741</v>
+        <v>7023653</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6042,7 +6057,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6069,10 +6084,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122773088</v>
+        <v>122771667</v>
       </c>
       <c r="B53" t="n">
-        <v>79843</v>
+        <v>79807</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6081,43 +6096,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494700</v>
+        <v>494425</v>
       </c>
       <c r="R53" t="n">
-        <v>7023729</v>
+        <v>7023600</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6176,10 +6186,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122774464</v>
+        <v>122773407</v>
       </c>
       <c r="B54" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6210,21 +6220,16 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494570</v>
+        <v>494790</v>
       </c>
       <c r="R54" t="n">
-        <v>7023783</v>
+        <v>7023741</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6257,6 +6262,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6283,10 +6293,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122774987</v>
+        <v>122774693</v>
       </c>
       <c r="B55" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6299,39 +6309,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494357</v>
+        <v>494544</v>
       </c>
       <c r="R55" t="n">
-        <v>7023735</v>
+        <v>7023772</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6364,11 +6369,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6395,10 +6395,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122791391</v>
+        <v>122790194</v>
       </c>
       <c r="B56" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6411,34 +6411,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494717</v>
+        <v>494560</v>
       </c>
       <c r="R56" t="n">
-        <v>7023829</v>
+        <v>7023660</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6471,6 +6476,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6497,10 +6507,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122791209</v>
+        <v>122790452</v>
       </c>
       <c r="B57" t="n">
-        <v>79844</v>
+        <v>79847</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6513,34 +6523,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494707</v>
+        <v>494479</v>
       </c>
       <c r="R57" t="n">
-        <v>7023829</v>
+        <v>7023680</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6599,10 +6614,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122790826</v>
+        <v>122791171</v>
       </c>
       <c r="B58" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6639,10 +6654,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494767</v>
+        <v>494727</v>
       </c>
       <c r="R58" t="n">
-        <v>7023760</v>
+        <v>7023818</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6675,6 +6690,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6701,10 +6721,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122791151</v>
+        <v>122791209</v>
       </c>
       <c r="B59" t="n">
-        <v>79843</v>
+        <v>79848</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6717,39 +6737,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494727</v>
+        <v>494707</v>
       </c>
       <c r="R59" t="n">
-        <v>7023818</v>
+        <v>7023829</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6808,10 +6823,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122789797</v>
+        <v>122789784</v>
       </c>
       <c r="B60" t="n">
-        <v>57494</v>
+        <v>56680</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6824,16 +6839,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6846,16 +6861,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M60" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -6867,10 +6872,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494329</v>
+        <v>494225</v>
       </c>
       <c r="R60" t="n">
-        <v>7023594</v>
+        <v>7023525</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6929,10 +6934,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122790839</v>
+        <v>122789892</v>
       </c>
       <c r="B61" t="n">
-        <v>91628</v>
+        <v>79847</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6941,25 +6946,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6969,10 +6974,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494767</v>
+        <v>494409</v>
       </c>
       <c r="R61" t="n">
-        <v>7023761</v>
+        <v>7023573</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7031,10 +7036,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122789892</v>
+        <v>122790289</v>
       </c>
       <c r="B62" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7071,10 +7076,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494409</v>
+        <v>494551</v>
       </c>
       <c r="R62" t="n">
-        <v>7023573</v>
+        <v>7023731</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7107,6 +7112,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7133,10 +7143,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122790194</v>
+        <v>122790826</v>
       </c>
       <c r="B63" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7149,39 +7159,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494560</v>
+        <v>494767</v>
       </c>
       <c r="R63" t="n">
-        <v>7023660</v>
+        <v>7023760</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7214,11 +7219,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7245,10 +7245,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122790289</v>
+        <v>122790839</v>
       </c>
       <c r="B64" t="n">
-        <v>79843</v>
+        <v>91632</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7257,25 +7257,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494551</v>
+        <v>494767</v>
       </c>
       <c r="R64" t="n">
-        <v>7023731</v>
+        <v>7023761</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7321,11 +7321,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7352,10 +7347,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122790452</v>
+        <v>122790286</v>
       </c>
       <c r="B65" t="n">
-        <v>79843</v>
+        <v>79848</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7368,39 +7363,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494479</v>
+        <v>494551</v>
       </c>
       <c r="R65" t="n">
-        <v>7023680</v>
+        <v>7023728</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7433,6 +7423,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7459,10 +7454,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122789784</v>
+        <v>122789797</v>
       </c>
       <c r="B66" t="n">
-        <v>56680</v>
+        <v>57494</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7475,16 +7470,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7497,6 +7492,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -7508,10 +7513,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494225</v>
+        <v>494329</v>
       </c>
       <c r="R66" t="n">
-        <v>7023525</v>
+        <v>7023594</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7570,10 +7575,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122790286</v>
+        <v>122791391</v>
       </c>
       <c r="B67" t="n">
-        <v>79844</v>
+        <v>79847</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7586,21 +7591,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7610,10 +7615,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494551</v>
+        <v>494717</v>
       </c>
       <c r="R67" t="n">
-        <v>7023728</v>
+        <v>7023829</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7646,11 +7651,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -1729,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122773527</v>
+        <v>122772714</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1745,39 +1745,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494802</v>
+        <v>494589</v>
       </c>
       <c r="R12" t="n">
-        <v>7023657</v>
+        <v>7023675</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,11 +1805,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122772729</v>
+        <v>122772044</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,39 +1847,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494591</v>
+        <v>494524</v>
       </c>
       <c r="R13" t="n">
-        <v>7023673</v>
+        <v>7023624</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,11 +1907,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1953,7 +1933,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122774696</v>
+        <v>122771745</v>
       </c>
       <c r="B14" t="n">
         <v>79847</v>
@@ -1993,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494538</v>
+        <v>494449</v>
       </c>
       <c r="R14" t="n">
-        <v>7023761</v>
+        <v>7023602</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,11 +2009,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2060,10 +2035,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122772714</v>
+        <v>122770929</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2076,34 +2051,48 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494589</v>
+        <v>494181</v>
       </c>
       <c r="R15" t="n">
-        <v>7023675</v>
+        <v>7023603</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,10 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122772044</v>
+        <v>122773527</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2178,34 +2167,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494524</v>
+        <v>494802</v>
       </c>
       <c r="R16" t="n">
-        <v>7023624</v>
+        <v>7023657</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,6 +2232,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2264,10 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122771745</v>
+        <v>122772729</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2280,34 +2279,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494449</v>
+        <v>494591</v>
       </c>
       <c r="R17" t="n">
-        <v>7023602</v>
+        <v>7023673</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,6 +2344,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2366,10 +2375,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122770929</v>
+        <v>122774696</v>
       </c>
       <c r="B18" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2382,48 +2391,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494181</v>
+        <v>494538</v>
       </c>
       <c r="R18" t="n">
-        <v>7023603</v>
+        <v>7023761</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2456,6 +2451,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -5122,10 +5122,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122772290</v>
+        <v>122770429</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5138,39 +5138,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494557</v>
+        <v>493992</v>
       </c>
       <c r="R44" t="n">
-        <v>7023675</v>
+        <v>7023434</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5203,6 +5203,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5229,10 +5234,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122770429</v>
+        <v>122772994</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5245,39 +5250,43 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493992</v>
+        <v>494664</v>
       </c>
       <c r="R45" t="n">
-        <v>7023434</v>
+        <v>7023760</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5310,11 +5319,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5341,10 +5345,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122772994</v>
+        <v>122772290</v>
       </c>
       <c r="B46" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5357,31 +5361,27 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494664</v>
+        <v>494557</v>
       </c>
       <c r="R46" t="n">
-        <v>7023760</v>
+        <v>7023675</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6084,10 +6084,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122771667</v>
+        <v>122773407</v>
       </c>
       <c r="B53" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6096,25 +6096,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6124,10 +6124,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494425</v>
+        <v>494790</v>
       </c>
       <c r="R53" t="n">
-        <v>7023600</v>
+        <v>7023741</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6160,6 +6160,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6186,7 +6191,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122773407</v>
+        <v>122774693</v>
       </c>
       <c r="B54" t="n">
         <v>79847</v>
@@ -6226,10 +6231,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494790</v>
+        <v>494544</v>
       </c>
       <c r="R54" t="n">
-        <v>7023741</v>
+        <v>7023772</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6262,11 +6267,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6293,10 +6293,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122774693</v>
+        <v>122771667</v>
       </c>
       <c r="B55" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6305,25 +6305,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6333,10 +6333,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494544</v>
+        <v>494425</v>
       </c>
       <c r="R55" t="n">
-        <v>7023772</v>
+        <v>7023600</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7036,7 +7036,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122790289</v>
+        <v>122790826</v>
       </c>
       <c r="B62" t="n">
         <v>79847</v>
@@ -7076,10 +7076,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494551</v>
+        <v>494767</v>
       </c>
       <c r="R62" t="n">
-        <v>7023731</v>
+        <v>7023760</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7112,11 +7112,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7143,7 +7138,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122790826</v>
+        <v>122790289</v>
       </c>
       <c r="B63" t="n">
         <v>79847</v>
@@ -7183,10 +7178,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494767</v>
+        <v>494551</v>
       </c>
       <c r="R63" t="n">
-        <v>7023760</v>
+        <v>7023731</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7219,6 +7214,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122774455</v>
+        <v>122774563</v>
       </c>
       <c r="B2" t="n">
-        <v>91511</v>
+        <v>79848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494571</v>
+        <v>494563</v>
       </c>
       <c r="R2" t="n">
-        <v>7023780</v>
+        <v>7023786</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122772356</v>
+        <v>122774764</v>
       </c>
       <c r="B3" t="n">
         <v>79847</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494558</v>
+        <v>494568</v>
       </c>
       <c r="R3" t="n">
-        <v>7023688</v>
+        <v>7023757</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122774538</v>
+        <v>122771655</v>
       </c>
       <c r="B4" t="n">
         <v>79847</v>
@@ -918,21 +918,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494563</v>
+        <v>494427</v>
       </c>
       <c r="R4" t="n">
-        <v>7023781</v>
+        <v>7023595</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122771474</v>
+        <v>122774777</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1025,21 +1020,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494356</v>
+        <v>494582</v>
       </c>
       <c r="R5" t="n">
-        <v>7023575</v>
+        <v>7023728</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122774563</v>
+        <v>122773216</v>
       </c>
       <c r="B6" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,34 +1109,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494563</v>
+        <v>494716</v>
       </c>
       <c r="R6" t="n">
-        <v>7023786</v>
+        <v>7023730</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122774987</v>
+        <v>122771661</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,43 +1212,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494357</v>
+        <v>494425</v>
       </c>
       <c r="R7" t="n">
-        <v>7023735</v>
+        <v>7023600</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122774745</v>
+        <v>122774987</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,34 +1318,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494558</v>
+        <v>494357</v>
       </c>
       <c r="R8" t="n">
-        <v>7023767</v>
+        <v>7023735</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122771661</v>
+        <v>122773527</v>
       </c>
       <c r="B9" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,38 +1426,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494425</v>
+        <v>494802</v>
       </c>
       <c r="R9" t="n">
-        <v>7023600</v>
+        <v>7023657</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773452</v>
+        <v>122770929</v>
       </c>
       <c r="B11" t="n">
-        <v>57428</v>
+        <v>57631</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,47 +1640,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102621</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494786</v>
+        <v>494181</v>
       </c>
       <c r="R11" t="n">
-        <v>7023741</v>
+        <v>7023603</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1744,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122772714</v>
+        <v>122774745</v>
       </c>
       <c r="B12" t="n">
         <v>79847</v>
@@ -1769,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494589</v>
+        <v>494558</v>
       </c>
       <c r="R12" t="n">
-        <v>7023675</v>
+        <v>7023767</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,7 +1846,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122772044</v>
+        <v>122773254</v>
       </c>
       <c r="B13" t="n">
         <v>79847</v>
@@ -1865,16 +1880,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494524</v>
+        <v>494730</v>
       </c>
       <c r="R13" t="n">
-        <v>7023624</v>
+        <v>7023730</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,7 +1953,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122771745</v>
+        <v>122773465</v>
       </c>
       <c r="B14" t="n">
         <v>79847</v>
@@ -1967,16 +1987,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494449</v>
+        <v>494786</v>
       </c>
       <c r="R14" t="n">
-        <v>7023602</v>
+        <v>7023741</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2035,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122770929</v>
+        <v>122771956</v>
       </c>
       <c r="B15" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2051,48 +2076,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494181</v>
+        <v>494521</v>
       </c>
       <c r="R15" t="n">
-        <v>7023603</v>
+        <v>7023591</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2125,6 +2141,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,10 +2172,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122773527</v>
+        <v>122771489</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2167,39 +2188,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494802</v>
+        <v>494147</v>
       </c>
       <c r="R16" t="n">
-        <v>7023657</v>
+        <v>7023571</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2232,11 +2248,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,10 +2274,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122772729</v>
+        <v>122774828</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2279,39 +2290,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494591</v>
+        <v>494562</v>
       </c>
       <c r="R17" t="n">
-        <v>7023673</v>
+        <v>7023728</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2344,11 +2350,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122774696</v>
+        <v>122772985</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,34 +2392,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494538</v>
+        <v>494655</v>
       </c>
       <c r="R18" t="n">
-        <v>7023761</v>
+        <v>7023708</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,7 +2461,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2482,10 +2488,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122771956</v>
+        <v>122771745</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,39 +2504,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494521</v>
+        <v>494449</v>
       </c>
       <c r="R19" t="n">
-        <v>7023591</v>
+        <v>7023602</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,11 +2564,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,7 +2590,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122774372</v>
+        <v>122774393</v>
       </c>
       <c r="B20" t="n">
         <v>79847</v>
@@ -2634,10 +2630,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494839</v>
+        <v>494710</v>
       </c>
       <c r="R20" t="n">
-        <v>7023830</v>
+        <v>7023786</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,7 +2692,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122774566</v>
+        <v>122774693</v>
       </c>
       <c r="B21" t="n">
         <v>79847</v>
@@ -2736,10 +2732,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494563</v>
+        <v>494544</v>
       </c>
       <c r="R21" t="n">
-        <v>7023786</v>
+        <v>7023772</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,10 +2794,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122773216</v>
+        <v>122770429</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2814,39 +2810,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494716</v>
+        <v>493992</v>
       </c>
       <c r="R22" t="n">
-        <v>7023730</v>
+        <v>7023434</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2879,6 +2875,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2905,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122772985</v>
+        <v>122772994</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2921,27 +2922,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2950,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494655</v>
+        <v>494664</v>
       </c>
       <c r="R23" t="n">
-        <v>7023708</v>
+        <v>7023760</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2986,11 +2991,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3017,7 +3017,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122774828</v>
+        <v>122772413</v>
       </c>
       <c r="B24" t="n">
         <v>79847</v>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494562</v>
+        <v>494559</v>
       </c>
       <c r="R24" t="n">
-        <v>7023728</v>
+        <v>7023689</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122771891</v>
+        <v>122774455</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>91511</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3131,43 +3131,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494515</v>
+        <v>494571</v>
       </c>
       <c r="R25" t="n">
-        <v>7023580</v>
+        <v>7023780</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3200,11 +3195,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3231,7 +3221,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122774764</v>
+        <v>122774464</v>
       </c>
       <c r="B26" t="n">
         <v>79847</v>
@@ -3265,16 +3255,21 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494568</v>
+        <v>494570</v>
       </c>
       <c r="R26" t="n">
-        <v>7023757</v>
+        <v>7023783</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3307,11 +3302,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3338,10 +3328,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122771489</v>
+        <v>122772081</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3354,34 +3344,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494147</v>
+        <v>494512</v>
       </c>
       <c r="R27" t="n">
-        <v>7023571</v>
+        <v>7023641</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,7 +3430,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122772081</v>
+        <v>122771474</v>
       </c>
       <c r="B28" t="n">
         <v>79847</v>
@@ -3474,16 +3464,21 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494512</v>
+        <v>494356</v>
       </c>
       <c r="R28" t="n">
-        <v>7023641</v>
+        <v>7023575</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3542,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122774715</v>
+        <v>122777145</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3558,34 +3553,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494547</v>
+        <v>494559</v>
       </c>
       <c r="R29" t="n">
-        <v>7023756</v>
+        <v>7023653</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3618,6 +3618,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3644,10 +3649,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122771655</v>
+        <v>122772707</v>
       </c>
       <c r="B30" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3660,34 +3665,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494427</v>
+        <v>494582</v>
       </c>
       <c r="R30" t="n">
-        <v>7023595</v>
+        <v>7023673</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3720,6 +3730,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3746,7 +3761,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122771384</v>
+        <v>122772290</v>
       </c>
       <c r="B31" t="n">
         <v>79847</v>
@@ -3780,16 +3795,21 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494334</v>
+        <v>494557</v>
       </c>
       <c r="R31" t="n">
-        <v>7023580</v>
+        <v>7023675</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,10 +3868,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122773319</v>
+        <v>122773407</v>
       </c>
       <c r="B32" t="n">
-        <v>90955</v>
+        <v>79847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3860,25 +3880,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3888,10 +3908,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494758</v>
+        <v>494790</v>
       </c>
       <c r="R32" t="n">
-        <v>7023767</v>
+        <v>7023741</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3924,6 +3944,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3950,7 +3975,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122773465</v>
+        <v>122774372</v>
       </c>
       <c r="B33" t="n">
         <v>79847</v>
@@ -3984,21 +4009,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494786</v>
+        <v>494839</v>
       </c>
       <c r="R33" t="n">
-        <v>7023741</v>
+        <v>7023830</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4057,7 +4077,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122773088</v>
+        <v>122772874</v>
       </c>
       <c r="B34" t="n">
         <v>79847</v>
@@ -4102,10 +4122,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494700</v>
+        <v>494680</v>
       </c>
       <c r="R34" t="n">
-        <v>7023729</v>
+        <v>7023737</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4164,7 +4184,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122772874</v>
+        <v>122772044</v>
       </c>
       <c r="B35" t="n">
         <v>79847</v>
@@ -4198,21 +4218,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494680</v>
+        <v>494524</v>
       </c>
       <c r="R35" t="n">
-        <v>7023737</v>
+        <v>7023624</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4271,7 +4286,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122773254</v>
+        <v>122774566</v>
       </c>
       <c r="B36" t="n">
         <v>79847</v>
@@ -4305,21 +4320,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494730</v>
+        <v>494563</v>
       </c>
       <c r="R36" t="n">
-        <v>7023730</v>
+        <v>7023786</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4378,10 +4388,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122772531</v>
+        <v>122774696</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4394,39 +4404,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494557</v>
+        <v>494538</v>
       </c>
       <c r="R37" t="n">
-        <v>7023650</v>
+        <v>7023761</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4463,7 +4468,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4490,10 +4495,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122772707</v>
+        <v>122771384</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4506,39 +4511,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494582</v>
+        <v>494334</v>
       </c>
       <c r="R38" t="n">
-        <v>7023673</v>
+        <v>7023580</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4571,11 +4571,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4602,10 +4597,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122774464</v>
+        <v>122771901</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4618,27 +4613,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4647,10 +4642,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494570</v>
+        <v>494516</v>
       </c>
       <c r="R39" t="n">
-        <v>7023783</v>
+        <v>7023586</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4683,6 +4678,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4709,10 +4709,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122772030</v>
+        <v>122772729</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4725,34 +4725,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494526</v>
+        <v>494591</v>
       </c>
       <c r="R40" t="n">
-        <v>7023606</v>
+        <v>7023673</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4785,6 +4790,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4811,10 +4821,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122774777</v>
+        <v>122772531</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4827,34 +4837,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494582</v>
+        <v>494557</v>
       </c>
       <c r="R41" t="n">
-        <v>7023728</v>
+        <v>7023650</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4891,7 +4906,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4918,10 +4933,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122774393</v>
+        <v>122773452</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>57428</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4930,38 +4945,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>102621</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494710</v>
+        <v>494786</v>
       </c>
       <c r="R42" t="n">
-        <v>7023786</v>
+        <v>7023741</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5020,10 +5044,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122774670</v>
+        <v>122771667</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5032,25 +5056,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5060,10 +5084,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494555</v>
+        <v>494425</v>
       </c>
       <c r="R43" t="n">
-        <v>7023779</v>
+        <v>7023600</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5122,10 +5146,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122770429</v>
+        <v>122770882</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5138,39 +5162,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493992</v>
+        <v>494160</v>
       </c>
       <c r="R44" t="n">
-        <v>7023434</v>
+        <v>7023595</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5203,11 +5222,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5234,10 +5248,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122772994</v>
+        <v>122772714</v>
       </c>
       <c r="B45" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5250,43 +5264,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494664</v>
+        <v>494589</v>
       </c>
       <c r="R45" t="n">
-        <v>7023760</v>
+        <v>7023675</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5345,10 +5350,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122772290</v>
+        <v>122771481</v>
       </c>
       <c r="B46" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5357,43 +5362,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494557</v>
+        <v>494353</v>
       </c>
       <c r="R46" t="n">
-        <v>7023675</v>
+        <v>7023580</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5452,10 +5452,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122773458</v>
+        <v>122771891</v>
       </c>
       <c r="B47" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5468,34 +5468,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494786</v>
+        <v>494515</v>
       </c>
       <c r="R47" t="n">
-        <v>7023741</v>
+        <v>7023580</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,6 +5533,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5554,10 +5564,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122771901</v>
+        <v>122773319</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>90955</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5566,43 +5576,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494516</v>
+        <v>494758</v>
       </c>
       <c r="R48" t="n">
-        <v>7023586</v>
+        <v>7023767</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5635,11 +5640,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5666,10 +5666,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122770882</v>
+        <v>122774670</v>
       </c>
       <c r="B49" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5682,34 +5682,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494160</v>
+        <v>494555</v>
       </c>
       <c r="R49" t="n">
-        <v>7023595</v>
+        <v>7023779</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5768,10 +5768,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122771481</v>
+        <v>122773458</v>
       </c>
       <c r="B50" t="n">
-        <v>79883</v>
+        <v>79848</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5780,25 +5780,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5808,10 +5808,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494353</v>
+        <v>494786</v>
       </c>
       <c r="R50" t="n">
-        <v>7023580</v>
+        <v>7023741</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5870,7 +5870,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122772413</v>
+        <v>122772356</v>
       </c>
       <c r="B51" t="n">
         <v>79847</v>
@@ -5910,10 +5910,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494559</v>
+        <v>494558</v>
       </c>
       <c r="R51" t="n">
-        <v>7023689</v>
+        <v>7023688</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5946,6 +5946,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5972,10 +5977,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122777145</v>
+        <v>122772030</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5988,39 +5993,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494559</v>
+        <v>494526</v>
       </c>
       <c r="R52" t="n">
-        <v>7023653</v>
+        <v>7023606</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6053,11 +6053,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6084,7 +6079,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122773407</v>
+        <v>122773088</v>
       </c>
       <c r="B53" t="n">
         <v>79847</v>
@@ -6118,16 +6113,21 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494790</v>
+        <v>494700</v>
       </c>
       <c r="R53" t="n">
-        <v>7023741</v>
+        <v>7023729</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6160,11 +6160,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6191,7 +6186,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122774693</v>
+        <v>122774715</v>
       </c>
       <c r="B54" t="n">
         <v>79847</v>
@@ -6231,10 +6226,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494544</v>
+        <v>494547</v>
       </c>
       <c r="R54" t="n">
-        <v>7023772</v>
+        <v>7023756</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6293,10 +6288,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122771667</v>
+        <v>122774538</v>
       </c>
       <c r="B55" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6305,38 +6300,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494425</v>
+        <v>494563</v>
       </c>
       <c r="R55" t="n">
-        <v>7023600</v>
+        <v>7023781</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6395,10 +6395,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122790194</v>
+        <v>122790839</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
+        <v>91632</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6407,43 +6407,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494560</v>
+        <v>494767</v>
       </c>
       <c r="R56" t="n">
-        <v>7023660</v>
+        <v>7023761</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6476,11 +6471,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6507,10 +6497,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122790452</v>
+        <v>122790194</v>
       </c>
       <c r="B57" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6523,27 +6513,27 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6552,10 +6542,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494479</v>
+        <v>494560</v>
       </c>
       <c r="R57" t="n">
-        <v>7023680</v>
+        <v>7023660</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6588,6 +6578,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6614,7 +6609,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122791171</v>
+        <v>122789892</v>
       </c>
       <c r="B58" t="n">
         <v>79847</v>
@@ -6654,10 +6649,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494727</v>
+        <v>494409</v>
       </c>
       <c r="R58" t="n">
-        <v>7023818</v>
+        <v>7023573</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6690,11 +6685,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6823,10 +6813,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122789784</v>
+        <v>122790826</v>
       </c>
       <c r="B60" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6839,43 +6829,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494225</v>
+        <v>494767</v>
       </c>
       <c r="R60" t="n">
-        <v>7023525</v>
+        <v>7023760</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6934,7 +6915,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122789892</v>
+        <v>122791391</v>
       </c>
       <c r="B61" t="n">
         <v>79847</v>
@@ -6974,10 +6955,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494409</v>
+        <v>494717</v>
       </c>
       <c r="R61" t="n">
-        <v>7023573</v>
+        <v>7023829</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7036,10 +7017,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122790826</v>
+        <v>122789797</v>
       </c>
       <c r="B62" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7052,34 +7033,53 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494767</v>
+        <v>494329</v>
       </c>
       <c r="R62" t="n">
-        <v>7023760</v>
+        <v>7023594</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7138,7 +7138,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122790289</v>
+        <v>122790452</v>
       </c>
       <c r="B63" t="n">
         <v>79847</v>
@@ -7172,16 +7172,21 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494551</v>
+        <v>494479</v>
       </c>
       <c r="R63" t="n">
-        <v>7023731</v>
+        <v>7023680</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7214,11 +7219,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7245,10 +7245,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122790839</v>
+        <v>122790289</v>
       </c>
       <c r="B64" t="n">
-        <v>91632</v>
+        <v>79847</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7257,25 +7257,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494767</v>
+        <v>494551</v>
       </c>
       <c r="R64" t="n">
-        <v>7023761</v>
+        <v>7023731</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7321,6 +7321,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7347,10 +7352,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122790286</v>
+        <v>122791151</v>
       </c>
       <c r="B65" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7363,34 +7368,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494551</v>
+        <v>494727</v>
       </c>
       <c r="R65" t="n">
-        <v>7023728</v>
+        <v>7023818</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7423,11 +7433,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7454,10 +7459,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122789797</v>
+        <v>122789784</v>
       </c>
       <c r="B66" t="n">
-        <v>57494</v>
+        <v>56680</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7470,16 +7475,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7492,16 +7497,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -7513,10 +7508,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494329</v>
+        <v>494225</v>
       </c>
       <c r="R66" t="n">
-        <v>7023594</v>
+        <v>7023525</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7575,10 +7570,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122791391</v>
+        <v>122790286</v>
       </c>
       <c r="B67" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7591,21 +7586,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7615,10 +7610,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494717</v>
+        <v>494551</v>
       </c>
       <c r="R67" t="n">
-        <v>7023829</v>
+        <v>7023728</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7651,6 +7646,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122774563</v>
+        <v>122772729</v>
       </c>
       <c r="B2" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494563</v>
+        <v>494591</v>
       </c>
       <c r="R2" t="n">
-        <v>7023786</v>
+        <v>7023673</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122774764</v>
+        <v>122771655</v>
       </c>
       <c r="B3" t="n">
         <v>79847</v>
@@ -817,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494568</v>
+        <v>494427</v>
       </c>
       <c r="R3" t="n">
-        <v>7023757</v>
+        <v>7023595</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122771655</v>
+        <v>122774566</v>
       </c>
       <c r="B4" t="n">
         <v>79847</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494427</v>
+        <v>494563</v>
       </c>
       <c r="R4" t="n">
-        <v>7023595</v>
+        <v>7023786</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122774777</v>
+        <v>122774730</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1020,16 +1025,21 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494582</v>
+        <v>494558</v>
       </c>
       <c r="R5" t="n">
-        <v>7023728</v>
+        <v>7023767</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122773216</v>
+        <v>122771901</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,27 +1114,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494716</v>
+        <v>494516</v>
       </c>
       <c r="R6" t="n">
-        <v>7023730</v>
+        <v>7023586</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122771661</v>
+        <v>122777145</v>
       </c>
       <c r="B7" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,38 +1222,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494425</v>
+        <v>494559</v>
       </c>
       <c r="R7" t="n">
-        <v>7023600</v>
+        <v>7023653</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1291,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122774987</v>
+        <v>122774538</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,27 +1338,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1347,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494357</v>
+        <v>494563</v>
       </c>
       <c r="R8" t="n">
-        <v>7023735</v>
+        <v>7023781</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,11 +1403,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122773527</v>
+        <v>122773465</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,27 +1445,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1459,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494802</v>
+        <v>494786</v>
       </c>
       <c r="R9" t="n">
-        <v>7023657</v>
+        <v>7023741</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1510,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122774597</v>
+        <v>122774828</v>
       </c>
       <c r="B10" t="n">
         <v>79847</v>
@@ -1566,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494556</v>
+        <v>494562</v>
       </c>
       <c r="R10" t="n">
-        <v>7023778</v>
+        <v>7023728</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122770929</v>
+        <v>122773407</v>
       </c>
       <c r="B11" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,48 +1654,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494181</v>
+        <v>494790</v>
       </c>
       <c r="R11" t="n">
-        <v>7023603</v>
+        <v>7023741</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,6 +1714,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122774745</v>
+        <v>122773088</v>
       </c>
       <c r="B12" t="n">
         <v>79847</v>
@@ -1778,16 +1779,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494558</v>
+        <v>494700</v>
       </c>
       <c r="R12" t="n">
-        <v>7023767</v>
+        <v>7023729</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773254</v>
+        <v>122773319</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>90955</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,43 +1864,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494730</v>
+        <v>494758</v>
       </c>
       <c r="R13" t="n">
-        <v>7023730</v>
+        <v>7023767</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122773465</v>
+        <v>122771481</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,43 +1966,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494786</v>
+        <v>494353</v>
       </c>
       <c r="R14" t="n">
-        <v>7023741</v>
+        <v>7023580</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122771956</v>
+        <v>122772356</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2076,39 +2072,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494521</v>
+        <v>494558</v>
       </c>
       <c r="R15" t="n">
-        <v>7023591</v>
+        <v>7023688</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,7 +2136,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2172,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122771489</v>
+        <v>122773527</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2188,34 +2179,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494147</v>
+        <v>494802</v>
       </c>
       <c r="R16" t="n">
-        <v>7023571</v>
+        <v>7023657</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,6 +2244,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2274,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122774828</v>
+        <v>122771667</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,25 +2287,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2314,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494562</v>
+        <v>494425</v>
       </c>
       <c r="R17" t="n">
-        <v>7023728</v>
+        <v>7023600</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122772985</v>
+        <v>122774670</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2392,39 +2393,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494655</v>
+        <v>494555</v>
       </c>
       <c r="R18" t="n">
-        <v>7023708</v>
+        <v>7023779</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,11 +2453,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2488,7 +2479,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122771745</v>
+        <v>122774715</v>
       </c>
       <c r="B19" t="n">
         <v>79847</v>
@@ -2528,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494449</v>
+        <v>494547</v>
       </c>
       <c r="R19" t="n">
-        <v>7023602</v>
+        <v>7023756</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2590,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122774393</v>
+        <v>122771745</v>
       </c>
       <c r="B20" t="n">
         <v>79847</v>
@@ -2630,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494710</v>
+        <v>494449</v>
       </c>
       <c r="R20" t="n">
-        <v>7023786</v>
+        <v>7023602</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2692,10 +2683,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122774693</v>
+        <v>122771956</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2708,34 +2699,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494544</v>
+        <v>494521</v>
       </c>
       <c r="R21" t="n">
-        <v>7023772</v>
+        <v>7023591</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,6 +2764,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2794,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122770429</v>
+        <v>122774455</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>91511</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2806,43 +2807,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493992</v>
+        <v>494571</v>
       </c>
       <c r="R22" t="n">
-        <v>7023434</v>
+        <v>7023780</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,11 +2871,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2906,10 +2897,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122772994</v>
+        <v>122772985</v>
       </c>
       <c r="B23" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2922,31 +2913,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2955,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494664</v>
+        <v>494655</v>
       </c>
       <c r="R23" t="n">
-        <v>7023760</v>
+        <v>7023708</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2991,6 +2978,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3017,10 +3009,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122772413</v>
+        <v>122773452</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>57428</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3029,38 +3021,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>102621</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494559</v>
+        <v>494786</v>
       </c>
       <c r="R24" t="n">
-        <v>7023689</v>
+        <v>7023741</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3119,10 +3120,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122774455</v>
+        <v>122774563</v>
       </c>
       <c r="B25" t="n">
-        <v>91511</v>
+        <v>79848</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3131,25 +3132,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3159,10 +3160,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494571</v>
+        <v>494563</v>
       </c>
       <c r="R25" t="n">
-        <v>7023780</v>
+        <v>7023786</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3221,10 +3222,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122774464</v>
+        <v>122770882</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>90962</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3237,39 +3238,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494570</v>
+        <v>494160</v>
       </c>
       <c r="R26" t="n">
-        <v>7023783</v>
+        <v>7023595</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3328,7 +3324,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122772081</v>
+        <v>122772874</v>
       </c>
       <c r="B27" t="n">
         <v>79847</v>
@@ -3362,16 +3358,21 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494512</v>
+        <v>494680</v>
       </c>
       <c r="R27" t="n">
-        <v>7023641</v>
+        <v>7023737</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122771474</v>
+        <v>122772707</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3446,27 +3447,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3475,10 +3476,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494356</v>
+        <v>494582</v>
       </c>
       <c r="R28" t="n">
-        <v>7023575</v>
+        <v>7023673</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3511,6 +3512,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3537,10 +3543,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122777145</v>
+        <v>122773254</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3553,27 +3559,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3582,10 +3588,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494559</v>
+        <v>494730</v>
       </c>
       <c r="R29" t="n">
-        <v>7023653</v>
+        <v>7023730</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3618,11 +3624,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3649,10 +3650,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122772707</v>
+        <v>122771661</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3661,43 +3662,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494582</v>
+        <v>494425</v>
       </c>
       <c r="R30" t="n">
-        <v>7023673</v>
+        <v>7023600</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3730,11 +3726,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3761,7 +3752,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122772290</v>
+        <v>122771474</v>
       </c>
       <c r="B31" t="n">
         <v>79847</v>
@@ -3806,10 +3797,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494557</v>
+        <v>494356</v>
       </c>
       <c r="R31" t="n">
-        <v>7023675</v>
+        <v>7023575</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3868,7 +3859,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122773407</v>
+        <v>122772030</v>
       </c>
       <c r="B32" t="n">
         <v>79847</v>
@@ -3908,10 +3899,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494790</v>
+        <v>494526</v>
       </c>
       <c r="R32" t="n">
-        <v>7023741</v>
+        <v>7023606</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3944,11 +3935,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3975,7 +3961,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122774372</v>
+        <v>122774777</v>
       </c>
       <c r="B33" t="n">
         <v>79847</v>
@@ -4015,10 +4001,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494839</v>
+        <v>494582</v>
       </c>
       <c r="R33" t="n">
-        <v>7023830</v>
+        <v>7023728</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4051,6 +4037,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4077,10 +4068,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122772874</v>
+        <v>122772531</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4093,27 +4084,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4122,10 +4113,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494680</v>
+        <v>494557</v>
       </c>
       <c r="R34" t="n">
-        <v>7023737</v>
+        <v>7023650</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4158,6 +4149,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4184,10 +4180,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122772044</v>
+        <v>122772994</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4200,34 +4196,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494524</v>
+        <v>494664</v>
       </c>
       <c r="R35" t="n">
-        <v>7023624</v>
+        <v>7023760</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4286,7 +4291,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122774566</v>
+        <v>122772714</v>
       </c>
       <c r="B36" t="n">
         <v>79847</v>
@@ -4326,10 +4331,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494563</v>
+        <v>494589</v>
       </c>
       <c r="R36" t="n">
-        <v>7023786</v>
+        <v>7023675</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4388,7 +4393,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122774696</v>
+        <v>122774764</v>
       </c>
       <c r="B37" t="n">
         <v>79847</v>
@@ -4428,10 +4433,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494538</v>
+        <v>494568</v>
       </c>
       <c r="R37" t="n">
-        <v>7023761</v>
+        <v>7023757</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4495,7 +4500,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122771384</v>
+        <v>122773216</v>
       </c>
       <c r="B38" t="n">
         <v>79847</v>
@@ -4529,16 +4534,21 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494334</v>
+        <v>494716</v>
       </c>
       <c r="R38" t="n">
-        <v>7023580</v>
+        <v>7023730</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4607,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122771901</v>
+        <v>122771891</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -4642,10 +4652,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494516</v>
+        <v>494515</v>
       </c>
       <c r="R39" t="n">
-        <v>7023586</v>
+        <v>7023580</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,7 +4719,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122772729</v>
+        <v>122774987</v>
       </c>
       <c r="B40" t="n">
         <v>57478</v>
@@ -4754,10 +4764,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494591</v>
+        <v>494357</v>
       </c>
       <c r="R40" t="n">
-        <v>7023673</v>
+        <v>7023735</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4821,10 +4831,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122772531</v>
+        <v>122774393</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4837,39 +4847,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494557</v>
+        <v>494710</v>
       </c>
       <c r="R41" t="n">
-        <v>7023650</v>
+        <v>7023786</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4902,11 +4907,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4933,10 +4933,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122773452</v>
+        <v>122772081</v>
       </c>
       <c r="B42" t="n">
-        <v>57428</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4945,47 +4945,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102621</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494786</v>
+        <v>494512</v>
       </c>
       <c r="R42" t="n">
-        <v>7023741</v>
+        <v>7023641</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5044,10 +5035,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122771667</v>
+        <v>122774372</v>
       </c>
       <c r="B43" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5056,25 +5047,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5084,10 +5075,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494425</v>
+        <v>494839</v>
       </c>
       <c r="R43" t="n">
-        <v>7023600</v>
+        <v>7023830</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5146,10 +5137,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122770882</v>
+        <v>122774693</v>
       </c>
       <c r="B44" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5162,34 +5153,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494160</v>
+        <v>494544</v>
       </c>
       <c r="R44" t="n">
-        <v>7023595</v>
+        <v>7023772</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5248,7 +5239,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122772714</v>
+        <v>122774464</v>
       </c>
       <c r="B45" t="n">
         <v>79847</v>
@@ -5282,16 +5273,21 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494589</v>
+        <v>494570</v>
       </c>
       <c r="R45" t="n">
-        <v>7023675</v>
+        <v>7023783</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5350,10 +5346,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122771481</v>
+        <v>122771489</v>
       </c>
       <c r="B46" t="n">
-        <v>79883</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5362,38 +5358,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494353</v>
+        <v>494147</v>
       </c>
       <c r="R46" t="n">
-        <v>7023580</v>
+        <v>7023571</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5452,7 +5448,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122771891</v>
+        <v>122770429</v>
       </c>
       <c r="B47" t="n">
         <v>57478</v>
@@ -5493,14 +5489,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494515</v>
+        <v>493992</v>
       </c>
       <c r="R47" t="n">
-        <v>7023580</v>
+        <v>7023434</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5537,7 +5533,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5564,10 +5560,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122773319</v>
+        <v>122774696</v>
       </c>
       <c r="B48" t="n">
-        <v>90955</v>
+        <v>79847</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5576,25 +5572,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5604,10 +5600,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494758</v>
+        <v>494538</v>
       </c>
       <c r="R48" t="n">
-        <v>7023767</v>
+        <v>7023761</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5640,6 +5636,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5666,7 +5667,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122774670</v>
+        <v>122774597</v>
       </c>
       <c r="B49" t="n">
         <v>79847</v>
@@ -5706,10 +5707,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494555</v>
+        <v>494556</v>
       </c>
       <c r="R49" t="n">
-        <v>7023779</v>
+        <v>7023778</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5768,10 +5769,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122773458</v>
+        <v>122772290</v>
       </c>
       <c r="B50" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5784,34 +5785,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494786</v>
+        <v>494557</v>
       </c>
       <c r="R50" t="n">
-        <v>7023741</v>
+        <v>7023675</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5870,7 +5876,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122772356</v>
+        <v>122772413</v>
       </c>
       <c r="B51" t="n">
         <v>79847</v>
@@ -5910,10 +5916,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494558</v>
+        <v>494559</v>
       </c>
       <c r="R51" t="n">
-        <v>7023688</v>
+        <v>7023689</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5946,11 +5952,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5977,7 +5978,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122772030</v>
+        <v>122771384</v>
       </c>
       <c r="B52" t="n">
         <v>79847</v>
@@ -6017,10 +6018,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494526</v>
+        <v>494334</v>
       </c>
       <c r="R52" t="n">
-        <v>7023606</v>
+        <v>7023580</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6079,7 +6080,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122773088</v>
+        <v>122772044</v>
       </c>
       <c r="B53" t="n">
         <v>79847</v>
@@ -6113,21 +6114,16 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494700</v>
+        <v>494524</v>
       </c>
       <c r="R53" t="n">
-        <v>7023729</v>
+        <v>7023624</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6186,10 +6182,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122774715</v>
+        <v>122773458</v>
       </c>
       <c r="B54" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6202,21 +6198,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6226,10 +6222,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494547</v>
+        <v>494786</v>
       </c>
       <c r="R54" t="n">
-        <v>7023756</v>
+        <v>7023741</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6288,10 +6284,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122774538</v>
+        <v>122770929</v>
       </c>
       <c r="B55" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6304,39 +6300,48 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494563</v>
+        <v>494181</v>
       </c>
       <c r="R55" t="n">
-        <v>7023781</v>
+        <v>7023603</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6395,10 +6400,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122790839</v>
+        <v>122791171</v>
       </c>
       <c r="B56" t="n">
-        <v>91632</v>
+        <v>79847</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6407,25 +6412,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6435,10 +6440,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494767</v>
+        <v>494727</v>
       </c>
       <c r="R56" t="n">
-        <v>7023761</v>
+        <v>7023818</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6471,6 +6476,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6497,10 +6507,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122790194</v>
+        <v>122791209</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6513,39 +6523,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494560</v>
+        <v>494707</v>
       </c>
       <c r="R57" t="n">
-        <v>7023660</v>
+        <v>7023829</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6578,11 +6583,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6609,7 +6609,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122789892</v>
+        <v>122790289</v>
       </c>
       <c r="B58" t="n">
         <v>79847</v>
@@ -6649,10 +6649,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494409</v>
+        <v>494551</v>
       </c>
       <c r="R58" t="n">
-        <v>7023573</v>
+        <v>7023731</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6685,6 +6685,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6711,10 +6716,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122791209</v>
+        <v>122790452</v>
       </c>
       <c r="B59" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6727,34 +6732,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494707</v>
+        <v>494479</v>
       </c>
       <c r="R59" t="n">
-        <v>7023829</v>
+        <v>7023680</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6813,10 +6823,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122790826</v>
+        <v>122789797</v>
       </c>
       <c r="B60" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6829,34 +6839,53 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494767</v>
+        <v>494329</v>
       </c>
       <c r="R60" t="n">
-        <v>7023760</v>
+        <v>7023594</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6915,7 +6944,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122791391</v>
+        <v>122790826</v>
       </c>
       <c r="B61" t="n">
         <v>79847</v>
@@ -6955,10 +6984,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494717</v>
+        <v>494767</v>
       </c>
       <c r="R61" t="n">
-        <v>7023829</v>
+        <v>7023760</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7017,10 +7046,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122789797</v>
+        <v>122790839</v>
       </c>
       <c r="B62" t="n">
-        <v>57494</v>
+        <v>91632</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7029,57 +7058,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494329</v>
+        <v>494767</v>
       </c>
       <c r="R62" t="n">
-        <v>7023594</v>
+        <v>7023761</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7138,10 +7148,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122790452</v>
+        <v>122789784</v>
       </c>
       <c r="B63" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7154,27 +7164,31 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7183,10 +7197,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494479</v>
+        <v>494225</v>
       </c>
       <c r="R63" t="n">
-        <v>7023680</v>
+        <v>7023525</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7245,10 +7259,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122790289</v>
+        <v>122790286</v>
       </c>
       <c r="B64" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7261,21 +7275,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7288,7 +7302,7 @@
         <v>494551</v>
       </c>
       <c r="R64" t="n">
-        <v>7023731</v>
+        <v>7023728</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7352,7 +7366,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122791151</v>
+        <v>122791391</v>
       </c>
       <c r="B65" t="n">
         <v>79847</v>
@@ -7386,21 +7400,16 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494727</v>
+        <v>494717</v>
       </c>
       <c r="R65" t="n">
-        <v>7023818</v>
+        <v>7023829</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7459,10 +7468,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122789784</v>
+        <v>122789892</v>
       </c>
       <c r="B66" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7475,43 +7484,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494225</v>
+        <v>494409</v>
       </c>
       <c r="R66" t="n">
-        <v>7023525</v>
+        <v>7023573</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7570,10 +7570,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122790286</v>
+        <v>122790194</v>
       </c>
       <c r="B67" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7586,34 +7586,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494551</v>
+        <v>494560</v>
       </c>
       <c r="R67" t="n">
-        <v>7023728</v>
+        <v>7023660</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7650,7 +7655,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122777145</v>
+        <v>122774538</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,27 +1226,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494559</v>
+        <v>494563</v>
       </c>
       <c r="R7" t="n">
-        <v>7023653</v>
+        <v>7023781</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,11 +1291,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122774538</v>
+        <v>122777145</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,27 +1333,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1367,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494563</v>
+        <v>494559</v>
       </c>
       <c r="R8" t="n">
-        <v>7023781</v>
+        <v>7023653</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,6 +1398,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773319</v>
+        <v>122771481</v>
       </c>
       <c r="B13" t="n">
-        <v>90955</v>
+        <v>79883</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1205</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494758</v>
+        <v>494353</v>
       </c>
       <c r="R13" t="n">
-        <v>7023767</v>
+        <v>7023580</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122771481</v>
+        <v>122772356</v>
       </c>
       <c r="B14" t="n">
-        <v>79883</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1966,25 +1966,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494353</v>
+        <v>494558</v>
       </c>
       <c r="R14" t="n">
-        <v>7023580</v>
+        <v>7023688</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,6 +2030,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122772356</v>
+        <v>122773319</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>90955</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2068,25 +2073,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494558</v>
+        <v>494758</v>
       </c>
       <c r="R15" t="n">
-        <v>7023688</v>
+        <v>7023767</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,11 +2137,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122774455</v>
+        <v>122772985</v>
       </c>
       <c r="B22" t="n">
-        <v>91511</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,38 +2807,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494571</v>
+        <v>494655</v>
       </c>
       <c r="R22" t="n">
-        <v>7023780</v>
+        <v>7023708</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2871,6 +2876,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2897,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122772985</v>
+        <v>122773452</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>57428</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2909,20 +2919,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2930,10 +2940,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2942,10 +2956,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494655</v>
+        <v>494786</v>
       </c>
       <c r="R23" t="n">
-        <v>7023708</v>
+        <v>7023741</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2978,11 +2992,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3009,10 +3018,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122773452</v>
+        <v>122774455</v>
       </c>
       <c r="B24" t="n">
-        <v>57428</v>
+        <v>91511</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3021,47 +3030,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102621</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494786</v>
+        <v>494571</v>
       </c>
       <c r="R24" t="n">
-        <v>7023741</v>
+        <v>7023780</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122770882</v>
+        <v>122772707</v>
       </c>
       <c r="B26" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3238,34 +3238,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494160</v>
+        <v>494582</v>
       </c>
       <c r="R26" t="n">
-        <v>7023595</v>
+        <v>7023673</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,6 +3303,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3431,10 +3441,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122772707</v>
+        <v>122770882</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3447,39 +3457,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494582</v>
+        <v>494160</v>
       </c>
       <c r="R28" t="n">
-        <v>7023673</v>
+        <v>7023595</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3512,11 +3517,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122771481</v>
+        <v>122773319</v>
       </c>
       <c r="B13" t="n">
-        <v>79883</v>
+        <v>90955</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>1205</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494353</v>
+        <v>494758</v>
       </c>
       <c r="R13" t="n">
-        <v>7023580</v>
+        <v>7023767</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122772356</v>
+        <v>122771481</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1966,25 +1966,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494558</v>
+        <v>494353</v>
       </c>
       <c r="R14" t="n">
-        <v>7023688</v>
+        <v>7023580</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,11 +2030,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122773319</v>
+        <v>122772356</v>
       </c>
       <c r="B15" t="n">
-        <v>90955</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2073,25 +2068,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494758</v>
+        <v>494558</v>
       </c>
       <c r="R15" t="n">
-        <v>7023767</v>
+        <v>7023688</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,6 +2132,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122773527</v>
+        <v>122771667</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>79807</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,43 +2175,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494802</v>
+        <v>494425</v>
       </c>
       <c r="R16" t="n">
-        <v>7023657</v>
+        <v>7023600</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,11 +2239,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122771667</v>
+        <v>122773527</v>
       </c>
       <c r="B17" t="n">
-        <v>79807</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,38 +2277,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494425</v>
+        <v>494802</v>
       </c>
       <c r="R17" t="n">
-        <v>7023600</v>
+        <v>7023657</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,6 +2346,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122772729</v>
+        <v>122772714</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494591</v>
+        <v>494589</v>
       </c>
       <c r="R2" t="n">
-        <v>7023673</v>
+        <v>7023675</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122771655</v>
+        <v>122771474</v>
       </c>
       <c r="B3" t="n">
         <v>79847</v>
@@ -821,16 +811,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494427</v>
+        <v>494356</v>
       </c>
       <c r="R3" t="n">
-        <v>7023595</v>
+        <v>7023575</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122774566</v>
+        <v>122771384</v>
       </c>
       <c r="B4" t="n">
         <v>79847</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494563</v>
+        <v>494334</v>
       </c>
       <c r="R4" t="n">
-        <v>7023786</v>
+        <v>7023580</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122774730</v>
+        <v>122771745</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1025,21 +1020,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494558</v>
+        <v>494449</v>
       </c>
       <c r="R5" t="n">
-        <v>7023767</v>
+        <v>7023602</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122771901</v>
+        <v>122774670</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,39 +1104,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494516</v>
+        <v>494555</v>
       </c>
       <c r="R6" t="n">
-        <v>7023586</v>
+        <v>7023779</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122774538</v>
+        <v>122774696</v>
       </c>
       <c r="B7" t="n">
         <v>79847</v>
@@ -1244,21 +1224,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494563</v>
+        <v>494538</v>
       </c>
       <c r="R7" t="n">
-        <v>7023781</v>
+        <v>7023761</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122777145</v>
+        <v>122772081</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,39 +1313,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494559</v>
+        <v>494512</v>
       </c>
       <c r="R8" t="n">
-        <v>7023653</v>
+        <v>7023641</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,11 +1373,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122773465</v>
+        <v>122772356</v>
       </c>
       <c r="B9" t="n">
         <v>79847</v>
@@ -1463,21 +1433,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494786</v>
+        <v>494558</v>
       </c>
       <c r="R9" t="n">
-        <v>7023741</v>
+        <v>7023688</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122774828</v>
+        <v>122774538</v>
       </c>
       <c r="B10" t="n">
         <v>79847</v>
@@ -1570,16 +1540,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494562</v>
+        <v>494563</v>
       </c>
       <c r="R10" t="n">
-        <v>7023728</v>
+        <v>7023781</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773407</v>
+        <v>122771667</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,25 +1625,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494790</v>
+        <v>494425</v>
       </c>
       <c r="R11" t="n">
-        <v>7023741</v>
+        <v>7023600</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,11 +1689,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122773088</v>
+        <v>122771901</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,27 +1731,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1790,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494700</v>
+        <v>494516</v>
       </c>
       <c r="R12" t="n">
-        <v>7023729</v>
+        <v>7023586</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773319</v>
+        <v>122773527</v>
       </c>
       <c r="B13" t="n">
-        <v>90955</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1864,38 +1839,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494758</v>
+        <v>494802</v>
       </c>
       <c r="R13" t="n">
-        <v>7023767</v>
+        <v>7023657</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,6 +1908,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122771481</v>
+        <v>122777145</v>
       </c>
       <c r="B14" t="n">
-        <v>79883</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1966,38 +1951,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494353</v>
+        <v>494559</v>
       </c>
       <c r="R14" t="n">
-        <v>7023580</v>
+        <v>7023653</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,6 +2020,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122772356</v>
+        <v>122773254</v>
       </c>
       <c r="B15" t="n">
         <v>79847</v>
@@ -2090,16 +2085,21 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494558</v>
+        <v>494730</v>
       </c>
       <c r="R15" t="n">
-        <v>7023688</v>
+        <v>7023730</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,11 +2132,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122771667</v>
+        <v>122773407</v>
       </c>
       <c r="B16" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,25 +2170,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2203,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494425</v>
+        <v>494790</v>
       </c>
       <c r="R16" t="n">
-        <v>7023600</v>
+        <v>7023741</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,6 +2234,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122773527</v>
+        <v>122772290</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,27 +2281,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494802</v>
+        <v>494557</v>
       </c>
       <c r="R17" t="n">
-        <v>7023657</v>
+        <v>7023675</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,11 +2346,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,7 +2372,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122774670</v>
+        <v>122774777</v>
       </c>
       <c r="B18" t="n">
         <v>79847</v>
@@ -2417,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494555</v>
+        <v>494582</v>
       </c>
       <c r="R18" t="n">
-        <v>7023779</v>
+        <v>7023728</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,6 +2448,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122774715</v>
+        <v>122771956</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,34 +2495,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494547</v>
+        <v>494521</v>
       </c>
       <c r="R19" t="n">
-        <v>7023756</v>
+        <v>7023591</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,6 +2560,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122771745</v>
+        <v>122771891</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,34 +2607,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494449</v>
+        <v>494515</v>
       </c>
       <c r="R20" t="n">
-        <v>7023602</v>
+        <v>7023580</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,6 +2672,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2683,7 +2703,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122771956</v>
+        <v>122772729</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2728,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494521</v>
+        <v>494591</v>
       </c>
       <c r="R21" t="n">
-        <v>7023591</v>
+        <v>7023673</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122772985</v>
+        <v>122771481</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>79883</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,43 +2827,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494655</v>
+        <v>494353</v>
       </c>
       <c r="R22" t="n">
-        <v>7023708</v>
+        <v>7023580</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,11 +2891,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122773452</v>
+        <v>122772413</v>
       </c>
       <c r="B23" t="n">
-        <v>57428</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2919,47 +2929,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102621</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494786</v>
+        <v>494559</v>
       </c>
       <c r="R23" t="n">
-        <v>7023741</v>
+        <v>7023689</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3018,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122774455</v>
+        <v>122774730</v>
       </c>
       <c r="B24" t="n">
-        <v>91511</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3030,38 +3031,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494571</v>
+        <v>494558</v>
       </c>
       <c r="R24" t="n">
-        <v>7023780</v>
+        <v>7023767</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,10 +3126,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122774563</v>
+        <v>122774455</v>
       </c>
       <c r="B25" t="n">
-        <v>79848</v>
+        <v>91511</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,25 +3138,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3160,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494563</v>
+        <v>494571</v>
       </c>
       <c r="R25" t="n">
-        <v>7023786</v>
+        <v>7023780</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3222,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122772707</v>
+        <v>122773319</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>90955</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3234,43 +3240,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494582</v>
+        <v>494758</v>
       </c>
       <c r="R26" t="n">
-        <v>7023673</v>
+        <v>7023767</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,11 +3304,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3334,7 +3330,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122772874</v>
+        <v>122774764</v>
       </c>
       <c r="B27" t="n">
         <v>79847</v>
@@ -3368,21 +3364,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494680</v>
+        <v>494568</v>
       </c>
       <c r="R27" t="n">
-        <v>7023737</v>
+        <v>7023757</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3415,6 +3406,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3441,10 +3437,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122770882</v>
+        <v>122772707</v>
       </c>
       <c r="B28" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3457,34 +3453,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494160</v>
+        <v>494582</v>
       </c>
       <c r="R28" t="n">
-        <v>7023595</v>
+        <v>7023673</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3517,6 +3518,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3543,10 +3549,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122773254</v>
+        <v>122772994</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3559,27 +3565,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3588,10 +3598,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494730</v>
+        <v>494664</v>
       </c>
       <c r="R29" t="n">
-        <v>7023730</v>
+        <v>7023760</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3650,10 +3660,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122771661</v>
+        <v>122774464</v>
       </c>
       <c r="B30" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3662,38 +3672,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494425</v>
+        <v>494570</v>
       </c>
       <c r="R30" t="n">
-        <v>7023600</v>
+        <v>7023783</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3752,10 +3767,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122771474</v>
+        <v>122771489</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3768,39 +3783,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494356</v>
+        <v>494147</v>
       </c>
       <c r="R31" t="n">
-        <v>7023575</v>
+        <v>7023571</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3859,7 +3869,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122772030</v>
+        <v>122774828</v>
       </c>
       <c r="B32" t="n">
         <v>79847</v>
@@ -3899,10 +3909,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494526</v>
+        <v>494562</v>
       </c>
       <c r="R32" t="n">
-        <v>7023606</v>
+        <v>7023728</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3961,7 +3971,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122774777</v>
+        <v>122774566</v>
       </c>
       <c r="B33" t="n">
         <v>79847</v>
@@ -4001,10 +4011,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494582</v>
+        <v>494563</v>
       </c>
       <c r="R33" t="n">
-        <v>7023728</v>
+        <v>7023786</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4037,11 +4047,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4068,10 +4073,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122772531</v>
+        <v>122772044</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4084,39 +4089,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494557</v>
+        <v>494524</v>
       </c>
       <c r="R34" t="n">
-        <v>7023650</v>
+        <v>7023624</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4149,11 +4149,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4180,10 +4175,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122772994</v>
+        <v>122773465</v>
       </c>
       <c r="B35" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4196,31 +4191,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4229,10 +4220,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494664</v>
+        <v>494786</v>
       </c>
       <c r="R35" t="n">
-        <v>7023760</v>
+        <v>7023741</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4291,7 +4282,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122772714</v>
+        <v>122772874</v>
       </c>
       <c r="B36" t="n">
         <v>79847</v>
@@ -4325,16 +4316,21 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494589</v>
+        <v>494680</v>
       </c>
       <c r="R36" t="n">
-        <v>7023675</v>
+        <v>7023737</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4393,10 +4389,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122774764</v>
+        <v>122770929</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4409,34 +4405,48 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494568</v>
+        <v>494181</v>
       </c>
       <c r="R37" t="n">
-        <v>7023757</v>
+        <v>7023603</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4469,11 +4479,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4500,7 +4505,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122773216</v>
+        <v>122774597</v>
       </c>
       <c r="B38" t="n">
         <v>79847</v>
@@ -4534,21 +4539,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494716</v>
+        <v>494556</v>
       </c>
       <c r="R38" t="n">
-        <v>7023730</v>
+        <v>7023778</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4607,10 +4607,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122771891</v>
+        <v>122773216</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4623,27 +4623,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494515</v>
+        <v>494716</v>
       </c>
       <c r="R39" t="n">
-        <v>7023580</v>
+        <v>7023730</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4688,11 +4688,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4719,7 +4714,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122774987</v>
+        <v>122772985</v>
       </c>
       <c r="B40" t="n">
         <v>57478</v>
@@ -4764,10 +4759,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494357</v>
+        <v>494655</v>
       </c>
       <c r="R40" t="n">
-        <v>7023735</v>
+        <v>7023708</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4831,10 +4826,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122774393</v>
+        <v>122772531</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4847,34 +4842,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494710</v>
+        <v>494557</v>
       </c>
       <c r="R41" t="n">
-        <v>7023786</v>
+        <v>7023650</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4907,6 +4907,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4933,10 +4938,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122772081</v>
+        <v>122774987</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4949,34 +4954,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494512</v>
+        <v>494357</v>
       </c>
       <c r="R42" t="n">
-        <v>7023641</v>
+        <v>7023735</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5009,6 +5019,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5035,10 +5050,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122774372</v>
+        <v>122773458</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5051,21 +5066,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5075,10 +5090,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494839</v>
+        <v>494786</v>
       </c>
       <c r="R43" t="n">
-        <v>7023830</v>
+        <v>7023741</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5137,7 +5152,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122774693</v>
+        <v>122774372</v>
       </c>
       <c r="B44" t="n">
         <v>79847</v>
@@ -5177,10 +5192,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494544</v>
+        <v>494839</v>
       </c>
       <c r="R44" t="n">
-        <v>7023772</v>
+        <v>7023830</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5239,10 +5254,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122774464</v>
+        <v>122774563</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5255,39 +5270,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494570</v>
+        <v>494563</v>
       </c>
       <c r="R45" t="n">
-        <v>7023783</v>
+        <v>7023786</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,10 +5356,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122771489</v>
+        <v>122771655</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5362,34 +5372,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494147</v>
+        <v>494427</v>
       </c>
       <c r="R46" t="n">
-        <v>7023571</v>
+        <v>7023595</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5448,10 +5458,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122770429</v>
+        <v>122774393</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5464,39 +5474,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493992</v>
+        <v>494710</v>
       </c>
       <c r="R47" t="n">
-        <v>7023434</v>
+        <v>7023786</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5529,11 +5534,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5560,7 +5560,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122774696</v>
+        <v>122772030</v>
       </c>
       <c r="B48" t="n">
         <v>79847</v>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494538</v>
+        <v>494526</v>
       </c>
       <c r="R48" t="n">
-        <v>7023761</v>
+        <v>7023606</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5636,11 +5636,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5667,10 +5662,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122774597</v>
+        <v>122771661</v>
       </c>
       <c r="B49" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5679,25 +5674,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5707,10 +5702,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494556</v>
+        <v>494425</v>
       </c>
       <c r="R49" t="n">
-        <v>7023778</v>
+        <v>7023600</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5769,7 +5764,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122772290</v>
+        <v>122774693</v>
       </c>
       <c r="B50" t="n">
         <v>79847</v>
@@ -5803,21 +5798,16 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494557</v>
+        <v>494544</v>
       </c>
       <c r="R50" t="n">
-        <v>7023675</v>
+        <v>7023772</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5876,10 +5866,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122772413</v>
+        <v>122770429</v>
       </c>
       <c r="B51" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5892,34 +5882,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494559</v>
+        <v>493992</v>
       </c>
       <c r="R51" t="n">
-        <v>7023689</v>
+        <v>7023434</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5952,6 +5947,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5978,7 +5978,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122771384</v>
+        <v>122773088</v>
       </c>
       <c r="B52" t="n">
         <v>79847</v>
@@ -6012,16 +6012,21 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494334</v>
+        <v>494700</v>
       </c>
       <c r="R52" t="n">
-        <v>7023580</v>
+        <v>7023729</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6080,7 +6085,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122772044</v>
+        <v>122774715</v>
       </c>
       <c r="B53" t="n">
         <v>79847</v>
@@ -6120,10 +6125,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494524</v>
+        <v>494547</v>
       </c>
       <c r="R53" t="n">
-        <v>7023624</v>
+        <v>7023756</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6182,10 +6187,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122773458</v>
+        <v>122773452</v>
       </c>
       <c r="B54" t="n">
-        <v>79848</v>
+        <v>57428</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6194,28 +6199,37 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>102621</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
@@ -6284,10 +6298,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122770929</v>
+        <v>122770882</v>
       </c>
       <c r="B55" t="n">
-        <v>57631</v>
+        <v>90962</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6300,48 +6314,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494181</v>
+        <v>494160</v>
       </c>
       <c r="R55" t="n">
-        <v>7023603</v>
+        <v>7023595</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6400,7 +6400,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122791171</v>
+        <v>122790452</v>
       </c>
       <c r="B56" t="n">
         <v>79847</v>
@@ -6434,16 +6434,21 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494727</v>
+        <v>494479</v>
       </c>
       <c r="R56" t="n">
-        <v>7023818</v>
+        <v>7023680</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6476,11 +6481,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6507,10 +6507,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122791209</v>
+        <v>122790289</v>
       </c>
       <c r="B57" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6523,21 +6523,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6547,10 +6547,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494707</v>
+        <v>494551</v>
       </c>
       <c r="R57" t="n">
-        <v>7023829</v>
+        <v>7023731</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6583,6 +6583,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6609,7 +6614,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122790289</v>
+        <v>122791171</v>
       </c>
       <c r="B58" t="n">
         <v>79847</v>
@@ -6649,10 +6654,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494551</v>
+        <v>494727</v>
       </c>
       <c r="R58" t="n">
-        <v>7023731</v>
+        <v>7023818</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6716,10 +6721,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122790452</v>
+        <v>122789797</v>
       </c>
       <c r="B59" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6732,27 +6737,41 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6761,10 +6780,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494479</v>
+        <v>494329</v>
       </c>
       <c r="R59" t="n">
-        <v>7023680</v>
+        <v>7023594</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6823,10 +6842,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122789797</v>
+        <v>122791209</v>
       </c>
       <c r="B60" t="n">
-        <v>57494</v>
+        <v>79848</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6839,53 +6858,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494329</v>
+        <v>494707</v>
       </c>
       <c r="R60" t="n">
-        <v>7023594</v>
+        <v>7023829</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6944,10 +6944,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122790826</v>
+        <v>122790194</v>
       </c>
       <c r="B61" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6960,34 +6960,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494767</v>
+        <v>494560</v>
       </c>
       <c r="R61" t="n">
-        <v>7023760</v>
+        <v>7023660</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7020,6 +7025,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7046,10 +7056,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122790839</v>
+        <v>122790286</v>
       </c>
       <c r="B62" t="n">
-        <v>91632</v>
+        <v>79848</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7058,25 +7068,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7086,10 +7096,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494767</v>
+        <v>494551</v>
       </c>
       <c r="R62" t="n">
-        <v>7023761</v>
+        <v>7023728</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7122,6 +7132,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7148,10 +7163,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122789784</v>
+        <v>122790839</v>
       </c>
       <c r="B63" t="n">
-        <v>56680</v>
+        <v>91632</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7160,47 +7175,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102612</v>
+        <v>3298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494225</v>
+        <v>494767</v>
       </c>
       <c r="R63" t="n">
-        <v>7023525</v>
+        <v>7023761</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7259,10 +7265,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122790286</v>
+        <v>122789892</v>
       </c>
       <c r="B64" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7275,21 +7281,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7299,10 +7305,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494551</v>
+        <v>494409</v>
       </c>
       <c r="R64" t="n">
-        <v>7023728</v>
+        <v>7023573</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7335,11 +7341,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7468,10 +7469,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122789892</v>
+        <v>122789784</v>
       </c>
       <c r="B66" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7484,34 +7485,43 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494409</v>
+        <v>494225</v>
       </c>
       <c r="R66" t="n">
-        <v>7023573</v>
+        <v>7023525</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7570,10 +7580,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122790194</v>
+        <v>122790826</v>
       </c>
       <c r="B67" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7586,39 +7596,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494560</v>
+        <v>494767</v>
       </c>
       <c r="R67" t="n">
-        <v>7023660</v>
+        <v>7023760</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7651,11 +7656,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122774538</v>
+        <v>122771667</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,43 +1518,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494563</v>
+        <v>494425</v>
       </c>
       <c r="R10" t="n">
-        <v>7023781</v>
+        <v>7023600</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122771667</v>
+        <v>122771901</v>
       </c>
       <c r="B11" t="n">
-        <v>79807</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,38 +1620,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494425</v>
+        <v>494516</v>
       </c>
       <c r="R11" t="n">
-        <v>7023600</v>
+        <v>7023586</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,6 +1689,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,7 +1720,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122771901</v>
+        <v>122773527</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1760,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494516</v>
+        <v>494802</v>
       </c>
       <c r="R12" t="n">
-        <v>7023586</v>
+        <v>7023657</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,7 +1832,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773527</v>
+        <v>122777145</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1863,7 +1868,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1872,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494802</v>
+        <v>494559</v>
       </c>
       <c r="R13" t="n">
-        <v>7023657</v>
+        <v>7023653</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122777145</v>
+        <v>122774538</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,27 +1960,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1984,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494559</v>
+        <v>494563</v>
       </c>
       <c r="R14" t="n">
-        <v>7023653</v>
+        <v>7023781</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,11 +2025,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2591,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122771891</v>
+        <v>122773319</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>90955</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2603,43 +2603,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494515</v>
+        <v>494758</v>
       </c>
       <c r="R20" t="n">
-        <v>7023580</v>
+        <v>7023767</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2672,11 +2667,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122772729</v>
+        <v>122774455</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>91511</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2715,43 +2705,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494591</v>
+        <v>494571</v>
       </c>
       <c r="R21" t="n">
-        <v>7023673</v>
+        <v>7023780</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2784,11 +2769,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3126,10 +3106,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122774455</v>
+        <v>122771891</v>
       </c>
       <c r="B25" t="n">
-        <v>91511</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3138,38 +3118,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494571</v>
+        <v>494515</v>
       </c>
       <c r="R25" t="n">
-        <v>7023780</v>
+        <v>7023580</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3202,6 +3187,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122773319</v>
+        <v>122772729</v>
       </c>
       <c r="B26" t="n">
-        <v>90955</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3240,38 +3230,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494758</v>
+        <v>494591</v>
       </c>
       <c r="R26" t="n">
-        <v>7023767</v>
+        <v>7023673</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3304,6 +3299,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -6187,10 +6187,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122773452</v>
+        <v>122770882</v>
       </c>
       <c r="B54" t="n">
-        <v>57428</v>
+        <v>90962</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6199,47 +6199,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102621</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494786</v>
+        <v>494160</v>
       </c>
       <c r="R54" t="n">
-        <v>7023741</v>
+        <v>7023595</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6298,10 +6289,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122770882</v>
+        <v>122790452</v>
       </c>
       <c r="B55" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6314,34 +6305,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494160</v>
+        <v>494479</v>
       </c>
       <c r="R55" t="n">
-        <v>7023595</v>
+        <v>7023680</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6368,12 +6364,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6400,7 +6396,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122790452</v>
+        <v>122790289</v>
       </c>
       <c r="B56" t="n">
         <v>79847</v>
@@ -6434,21 +6430,16 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494479</v>
+        <v>494551</v>
       </c>
       <c r="R56" t="n">
-        <v>7023680</v>
+        <v>7023731</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6481,6 +6472,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6507,7 +6503,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122790289</v>
+        <v>122791171</v>
       </c>
       <c r="B57" t="n">
         <v>79847</v>
@@ -6547,10 +6543,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494551</v>
+        <v>494727</v>
       </c>
       <c r="R57" t="n">
-        <v>7023731</v>
+        <v>7023818</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6614,10 +6610,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122791171</v>
+        <v>122789797</v>
       </c>
       <c r="B58" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6630,34 +6626,53 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494727</v>
+        <v>494329</v>
       </c>
       <c r="R58" t="n">
-        <v>7023818</v>
+        <v>7023594</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6690,11 +6705,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6721,10 +6731,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122789797</v>
+        <v>122791209</v>
       </c>
       <c r="B59" t="n">
-        <v>57494</v>
+        <v>79848</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6737,53 +6747,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494329</v>
+        <v>494707</v>
       </c>
       <c r="R59" t="n">
-        <v>7023594</v>
+        <v>7023829</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6842,10 +6833,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122791209</v>
+        <v>122790194</v>
       </c>
       <c r="B60" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6858,34 +6849,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494707</v>
+        <v>494560</v>
       </c>
       <c r="R60" t="n">
-        <v>7023829</v>
+        <v>7023660</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6918,6 +6914,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6944,10 +6945,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122790194</v>
+        <v>122790286</v>
       </c>
       <c r="B61" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6960,39 +6961,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494560</v>
+        <v>494551</v>
       </c>
       <c r="R61" t="n">
-        <v>7023660</v>
+        <v>7023728</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7029,7 +7025,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7056,10 +7052,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122790286</v>
+        <v>122790839</v>
       </c>
       <c r="B62" t="n">
-        <v>79848</v>
+        <v>91632</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7068,25 +7064,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7096,10 +7092,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494551</v>
+        <v>494767</v>
       </c>
       <c r="R62" t="n">
-        <v>7023728</v>
+        <v>7023761</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7132,11 +7128,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7163,10 +7154,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122790839</v>
+        <v>122789892</v>
       </c>
       <c r="B63" t="n">
-        <v>91632</v>
+        <v>79847</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7175,25 +7166,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7203,10 +7194,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494767</v>
+        <v>494409</v>
       </c>
       <c r="R63" t="n">
-        <v>7023761</v>
+        <v>7023573</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7265,10 +7256,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122789892</v>
+        <v>122789784</v>
       </c>
       <c r="B64" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7281,34 +7272,43 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494409</v>
+        <v>494225</v>
       </c>
       <c r="R64" t="n">
-        <v>7023573</v>
+        <v>7023525</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7469,10 +7469,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122789784</v>
+        <v>122790826</v>
       </c>
       <c r="B66" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7485,43 +7485,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494225</v>
+        <v>494767</v>
       </c>
       <c r="R66" t="n">
-        <v>7023525</v>
+        <v>7023760</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7580,50 +7571,59 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122790826</v>
+        <v>122773452</v>
       </c>
       <c r="B67" t="n">
-        <v>79847</v>
+        <v>57428</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>102621</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494767</v>
+        <v>494786</v>
       </c>
       <c r="R67" t="n">
-        <v>7023760</v>
+        <v>7023741</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7650,12 +7650,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -2591,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122773319</v>
+        <v>122771891</v>
       </c>
       <c r="B20" t="n">
-        <v>90955</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2603,38 +2603,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494758</v>
+        <v>494515</v>
       </c>
       <c r="R20" t="n">
-        <v>7023767</v>
+        <v>7023580</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,6 +2672,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122774455</v>
+        <v>122772729</v>
       </c>
       <c r="B21" t="n">
-        <v>91511</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,38 +2715,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494571</v>
+        <v>494591</v>
       </c>
       <c r="R21" t="n">
-        <v>7023780</v>
+        <v>7023673</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,6 +2784,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3106,10 +3126,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122771891</v>
+        <v>122774455</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>91511</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3118,43 +3138,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494515</v>
+        <v>494571</v>
       </c>
       <c r="R25" t="n">
-        <v>7023580</v>
+        <v>7023780</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3187,11 +3202,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3218,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122772729</v>
+        <v>122773319</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>90955</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3230,43 +3240,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494591</v>
+        <v>494758</v>
       </c>
       <c r="R26" t="n">
-        <v>7023673</v>
+        <v>7023767</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3299,11 +3304,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4175,7 +4175,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122773465</v>
+        <v>122772874</v>
       </c>
       <c r="B35" t="n">
         <v>79847</v>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494786</v>
+        <v>494680</v>
       </c>
       <c r="R35" t="n">
-        <v>7023741</v>
+        <v>7023737</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4282,10 +4282,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122772874</v>
+        <v>122770929</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4298,39 +4298,48 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494680</v>
+        <v>494181</v>
       </c>
       <c r="R36" t="n">
-        <v>7023737</v>
+        <v>7023603</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4389,10 +4398,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122770929</v>
+        <v>122773465</v>
       </c>
       <c r="B37" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4405,48 +4414,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494181</v>
+        <v>494786</v>
       </c>
       <c r="R37" t="n">
-        <v>7023603</v>
+        <v>7023741</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4607,10 +4607,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122773216</v>
+        <v>122772985</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4623,27 +4623,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494716</v>
+        <v>494655</v>
       </c>
       <c r="R39" t="n">
-        <v>7023730</v>
+        <v>7023708</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4688,6 +4688,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4714,7 +4719,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122772985</v>
+        <v>122772531</v>
       </c>
       <c r="B40" t="n">
         <v>57478</v>
@@ -4759,10 +4764,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494655</v>
+        <v>494557</v>
       </c>
       <c r="R40" t="n">
-        <v>7023708</v>
+        <v>7023650</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4826,10 +4831,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122772531</v>
+        <v>122773216</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4842,27 +4847,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4871,10 +4876,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494557</v>
+        <v>494716</v>
       </c>
       <c r="R41" t="n">
-        <v>7023650</v>
+        <v>7023730</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4907,11 +4912,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4938,10 +4938,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122774987</v>
+        <v>122773458</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4954,39 +4954,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494357</v>
+        <v>494786</v>
       </c>
       <c r="R42" t="n">
-        <v>7023735</v>
+        <v>7023741</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5019,11 +5014,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5050,10 +5040,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122773458</v>
+        <v>122774372</v>
       </c>
       <c r="B43" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5066,21 +5056,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5090,10 +5080,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494786</v>
+        <v>494839</v>
       </c>
       <c r="R43" t="n">
-        <v>7023741</v>
+        <v>7023830</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5152,10 +5142,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122774372</v>
+        <v>122774987</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5168,34 +5158,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494839</v>
+        <v>494357</v>
       </c>
       <c r="R44" t="n">
-        <v>7023830</v>
+        <v>7023735</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5228,6 +5223,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122772714</v>
+        <v>122774464</v>
       </c>
       <c r="B2" t="n">
         <v>79847</v>
@@ -709,16 +709,21 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494589</v>
+        <v>494570</v>
       </c>
       <c r="R2" t="n">
-        <v>7023675</v>
+        <v>7023783</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122771384</v>
+        <v>122771891</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,31 +905,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494334</v>
+        <v>494515</v>
       </c>
       <c r="R4" t="n">
         <v>7023580</v>
@@ -960,6 +970,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122771745</v>
+        <v>122773319</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>90963</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +1013,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494449</v>
+        <v>494758</v>
       </c>
       <c r="R5" t="n">
-        <v>7023602</v>
+        <v>7023767</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122774670</v>
+        <v>122770429</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,34 +1119,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494555</v>
+        <v>493992</v>
       </c>
       <c r="R6" t="n">
-        <v>7023779</v>
+        <v>7023434</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,6 +1184,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122774696</v>
+        <v>122774670</v>
       </c>
       <c r="B7" t="n">
         <v>79847</v>
@@ -1230,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494538</v>
+        <v>494555</v>
       </c>
       <c r="R7" t="n">
-        <v>7023761</v>
+        <v>7023779</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1291,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122772081</v>
+        <v>122773407</v>
       </c>
       <c r="B8" t="n">
         <v>79847</v>
@@ -1337,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494512</v>
+        <v>494790</v>
       </c>
       <c r="R8" t="n">
-        <v>7023641</v>
+        <v>7023741</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,6 +1393,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122772356</v>
+        <v>122772531</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,34 +1440,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494558</v>
+        <v>494557</v>
       </c>
       <c r="R9" t="n">
-        <v>7023688</v>
+        <v>7023650</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,7 +1509,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122771667</v>
+        <v>122774987</v>
       </c>
       <c r="B10" t="n">
-        <v>79807</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,38 +1548,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494425</v>
+        <v>494357</v>
       </c>
       <c r="R10" t="n">
-        <v>7023600</v>
+        <v>7023735</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,6 +1617,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,7 +1648,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122771901</v>
+        <v>122772707</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1653,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494516</v>
+        <v>494582</v>
       </c>
       <c r="R11" t="n">
-        <v>7023586</v>
+        <v>7023673</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122773527</v>
+        <v>122772985</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1765,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494802</v>
+        <v>494655</v>
       </c>
       <c r="R12" t="n">
-        <v>7023657</v>
+        <v>7023708</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122777145</v>
+        <v>122773088</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,27 +1888,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1877,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494559</v>
+        <v>494700</v>
       </c>
       <c r="R13" t="n">
-        <v>7023653</v>
+        <v>7023729</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,11 +1953,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,7 +1979,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122774538</v>
+        <v>122774715</v>
       </c>
       <c r="B14" t="n">
         <v>79847</v>
@@ -1978,21 +2013,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494563</v>
+        <v>494547</v>
       </c>
       <c r="R14" t="n">
-        <v>7023781</v>
+        <v>7023756</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122773254</v>
+        <v>122774730</v>
       </c>
       <c r="B15" t="n">
         <v>79847</v>
@@ -2096,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494730</v>
+        <v>494558</v>
       </c>
       <c r="R15" t="n">
-        <v>7023730</v>
+        <v>7023767</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2188,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122773407</v>
+        <v>122774538</v>
       </c>
       <c r="B16" t="n">
         <v>79847</v>
@@ -2192,16 +2222,21 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494790</v>
+        <v>494563</v>
       </c>
       <c r="R16" t="n">
-        <v>7023741</v>
+        <v>7023781</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,11 +2269,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,7 +2295,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122772290</v>
+        <v>122774764</v>
       </c>
       <c r="B17" t="n">
         <v>79847</v>
@@ -2299,21 +2329,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494557</v>
+        <v>494568</v>
       </c>
       <c r="R17" t="n">
-        <v>7023675</v>
+        <v>7023757</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,6 +2371,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,7 +2402,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122774777</v>
+        <v>122774828</v>
       </c>
       <c r="B18" t="n">
         <v>79847</v>
@@ -2412,7 +2442,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494582</v>
+        <v>494562</v>
       </c>
       <c r="R18" t="n">
         <v>7023728</v>
@@ -2448,11 +2478,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122771956</v>
+        <v>122772081</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,39 +2520,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494521</v>
+        <v>494512</v>
       </c>
       <c r="R19" t="n">
-        <v>7023591</v>
+        <v>7023641</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,11 +2580,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,7 +2606,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122771891</v>
+        <v>122771901</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2636,10 +2651,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494515</v>
+        <v>494516</v>
       </c>
       <c r="R20" t="n">
-        <v>7023580</v>
+        <v>7023586</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122771481</v>
+        <v>122773458</v>
       </c>
       <c r="B22" t="n">
-        <v>79883</v>
+        <v>79848</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2827,25 +2842,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494353</v>
+        <v>494786</v>
       </c>
       <c r="R22" t="n">
-        <v>7023580</v>
+        <v>7023741</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2917,10 +2932,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122772413</v>
+        <v>122773527</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2933,34 +2948,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494559</v>
+        <v>494802</v>
       </c>
       <c r="R23" t="n">
-        <v>7023689</v>
+        <v>7023657</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2993,6 +3013,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,10 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122774730</v>
+        <v>122777145</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3035,27 +3060,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3064,10 +3089,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494558</v>
+        <v>494559</v>
       </c>
       <c r="R24" t="n">
-        <v>7023767</v>
+        <v>7023653</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3100,6 +3125,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,10 +3156,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122774455</v>
+        <v>122771956</v>
       </c>
       <c r="B25" t="n">
-        <v>91511</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3138,38 +3168,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494571</v>
+        <v>494521</v>
       </c>
       <c r="R25" t="n">
-        <v>7023780</v>
+        <v>7023591</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3202,6 +3237,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3268,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122773319</v>
+        <v>122774372</v>
       </c>
       <c r="B26" t="n">
-        <v>90955</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3240,25 +3280,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3308,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494758</v>
+        <v>494839</v>
       </c>
       <c r="R26" t="n">
-        <v>7023767</v>
+        <v>7023830</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,7 +3370,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122774764</v>
+        <v>122771745</v>
       </c>
       <c r="B27" t="n">
         <v>79847</v>
@@ -3370,10 +3410,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494568</v>
+        <v>494449</v>
       </c>
       <c r="R27" t="n">
-        <v>7023757</v>
+        <v>7023602</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3406,11 +3446,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3437,10 +3472,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122772707</v>
+        <v>122772290</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3453,27 +3488,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3482,10 +3517,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494582</v>
+        <v>494557</v>
       </c>
       <c r="R28" t="n">
-        <v>7023673</v>
+        <v>7023675</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3518,11 +3553,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3549,10 +3579,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122772994</v>
+        <v>122774777</v>
       </c>
       <c r="B29" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3565,43 +3595,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494664</v>
+        <v>494582</v>
       </c>
       <c r="R29" t="n">
-        <v>7023760</v>
+        <v>7023728</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,6 +3655,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3660,7 +3686,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122774464</v>
+        <v>122773216</v>
       </c>
       <c r="B30" t="n">
         <v>79847</v>
@@ -3705,10 +3731,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494570</v>
+        <v>494716</v>
       </c>
       <c r="R30" t="n">
-        <v>7023783</v>
+        <v>7023730</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3869,7 +3895,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122774828</v>
+        <v>122774696</v>
       </c>
       <c r="B32" t="n">
         <v>79847</v>
@@ -3909,10 +3935,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494562</v>
+        <v>494538</v>
       </c>
       <c r="R32" t="n">
-        <v>7023728</v>
+        <v>7023761</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,6 +3971,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3971,10 +4002,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122774566</v>
+        <v>122771661</v>
       </c>
       <c r="B33" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3983,25 +4014,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4011,10 +4042,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494563</v>
+        <v>494425</v>
       </c>
       <c r="R33" t="n">
-        <v>7023786</v>
+        <v>7023600</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4073,7 +4104,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122772044</v>
+        <v>122772413</v>
       </c>
       <c r="B34" t="n">
         <v>79847</v>
@@ -4113,10 +4144,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494524</v>
+        <v>494559</v>
       </c>
       <c r="R34" t="n">
-        <v>7023624</v>
+        <v>7023689</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4175,7 +4206,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122772874</v>
+        <v>122772030</v>
       </c>
       <c r="B35" t="n">
         <v>79847</v>
@@ -4209,21 +4240,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494680</v>
+        <v>494526</v>
       </c>
       <c r="R35" t="n">
-        <v>7023737</v>
+        <v>7023606</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4282,10 +4308,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122770929</v>
+        <v>122771384</v>
       </c>
       <c r="B36" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4298,48 +4324,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494181</v>
+        <v>494334</v>
       </c>
       <c r="R36" t="n">
-        <v>7023603</v>
+        <v>7023580</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4398,7 +4410,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122773465</v>
+        <v>122772714</v>
       </c>
       <c r="B37" t="n">
         <v>79847</v>
@@ -4432,21 +4444,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494786</v>
+        <v>494589</v>
       </c>
       <c r="R37" t="n">
-        <v>7023741</v>
+        <v>7023675</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4607,10 +4614,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122772985</v>
+        <v>122774693</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4623,39 +4630,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494655</v>
+        <v>494544</v>
       </c>
       <c r="R39" t="n">
-        <v>7023708</v>
+        <v>7023772</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4688,11 +4690,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4719,10 +4716,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122772531</v>
+        <v>122772044</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4735,39 +4732,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494557</v>
+        <v>494524</v>
       </c>
       <c r="R40" t="n">
-        <v>7023650</v>
+        <v>7023624</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4800,11 +4792,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4831,10 +4818,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122773216</v>
+        <v>122770882</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4847,39 +4834,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494716</v>
+        <v>494160</v>
       </c>
       <c r="R41" t="n">
-        <v>7023730</v>
+        <v>7023595</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4938,10 +4920,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122773458</v>
+        <v>122772874</v>
       </c>
       <c r="B42" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4954,34 +4936,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494786</v>
+        <v>494680</v>
       </c>
       <c r="R42" t="n">
-        <v>7023741</v>
+        <v>7023737</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5040,7 +5027,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122774372</v>
+        <v>122774566</v>
       </c>
       <c r="B43" t="n">
         <v>79847</v>
@@ -5080,10 +5067,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494839</v>
+        <v>494563</v>
       </c>
       <c r="R43" t="n">
-        <v>7023830</v>
+        <v>7023786</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5142,10 +5129,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122774987</v>
+        <v>122772356</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5158,39 +5145,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494357</v>
+        <v>494558</v>
       </c>
       <c r="R44" t="n">
-        <v>7023735</v>
+        <v>7023688</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5227,7 +5209,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5254,10 +5236,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122774563</v>
+        <v>122772994</v>
       </c>
       <c r="B45" t="n">
-        <v>79848</v>
+        <v>57631</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5270,34 +5252,43 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494563</v>
+        <v>494664</v>
       </c>
       <c r="R45" t="n">
-        <v>7023786</v>
+        <v>7023760</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5356,10 +5347,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122771655</v>
+        <v>122774563</v>
       </c>
       <c r="B46" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5372,21 +5363,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5396,10 +5387,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494427</v>
+        <v>494563</v>
       </c>
       <c r="R46" t="n">
-        <v>7023595</v>
+        <v>7023786</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5458,7 +5449,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122774393</v>
+        <v>122773465</v>
       </c>
       <c r="B47" t="n">
         <v>79847</v>
@@ -5492,16 +5483,21 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494710</v>
+        <v>494786</v>
       </c>
       <c r="R47" t="n">
-        <v>7023786</v>
+        <v>7023741</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5560,10 +5556,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122772030</v>
+        <v>122771481</v>
       </c>
       <c r="B48" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5572,25 +5568,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5600,10 +5596,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494526</v>
+        <v>494353</v>
       </c>
       <c r="R48" t="n">
-        <v>7023606</v>
+        <v>7023580</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5662,10 +5658,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122771661</v>
+        <v>122771655</v>
       </c>
       <c r="B49" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5674,25 +5670,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5702,10 +5698,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494425</v>
+        <v>494427</v>
       </c>
       <c r="R49" t="n">
-        <v>7023600</v>
+        <v>7023595</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5764,10 +5760,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122774693</v>
+        <v>122774455</v>
       </c>
       <c r="B50" t="n">
-        <v>79847</v>
+        <v>91519</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5776,25 +5772,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5804,10 +5800,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494544</v>
+        <v>494571</v>
       </c>
       <c r="R50" t="n">
-        <v>7023772</v>
+        <v>7023780</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5866,10 +5862,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122770429</v>
+        <v>122774393</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5882,39 +5878,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493992</v>
+        <v>494710</v>
       </c>
       <c r="R51" t="n">
-        <v>7023434</v>
+        <v>7023786</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5947,11 +5938,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5978,7 +5964,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122773088</v>
+        <v>122773254</v>
       </c>
       <c r="B52" t="n">
         <v>79847</v>
@@ -6023,10 +6009,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494700</v>
+        <v>494730</v>
       </c>
       <c r="R52" t="n">
-        <v>7023729</v>
+        <v>7023730</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6085,10 +6071,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122774715</v>
+        <v>122770929</v>
       </c>
       <c r="B53" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6101,34 +6087,48 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494547</v>
+        <v>494181</v>
       </c>
       <c r="R53" t="n">
-        <v>7023756</v>
+        <v>7023603</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6187,10 +6187,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122770882</v>
+        <v>122771667</v>
       </c>
       <c r="B54" t="n">
-        <v>90962</v>
+        <v>79807</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6199,38 +6199,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494160</v>
+        <v>494425</v>
       </c>
       <c r="R54" t="n">
-        <v>7023595</v>
+        <v>7023600</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6289,7 +6289,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122790452</v>
+        <v>122791151</v>
       </c>
       <c r="B55" t="n">
         <v>79847</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494479</v>
+        <v>494727</v>
       </c>
       <c r="R55" t="n">
-        <v>7023680</v>
+        <v>7023818</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6396,7 +6396,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122790289</v>
+        <v>122790826</v>
       </c>
       <c r="B56" t="n">
         <v>79847</v>
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494551</v>
+        <v>494767</v>
       </c>
       <c r="R56" t="n">
-        <v>7023731</v>
+        <v>7023760</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6472,11 +6472,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6503,7 +6498,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122791171</v>
+        <v>122789892</v>
       </c>
       <c r="B57" t="n">
         <v>79847</v>
@@ -6543,10 +6538,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494727</v>
+        <v>494409</v>
       </c>
       <c r="R57" t="n">
-        <v>7023818</v>
+        <v>7023573</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6579,11 +6574,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6610,10 +6600,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122789797</v>
+        <v>122790839</v>
       </c>
       <c r="B58" t="n">
-        <v>57494</v>
+        <v>91640</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6622,57 +6612,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494329</v>
+        <v>494767</v>
       </c>
       <c r="R58" t="n">
-        <v>7023594</v>
+        <v>7023761</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6833,10 +6804,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122790194</v>
+        <v>122790289</v>
       </c>
       <c r="B60" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6849,39 +6820,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494560</v>
+        <v>494551</v>
       </c>
       <c r="R60" t="n">
-        <v>7023660</v>
+        <v>7023731</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6918,7 +6884,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6945,10 +6911,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122790286</v>
+        <v>122790452</v>
       </c>
       <c r="B61" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6961,34 +6927,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494551</v>
+        <v>494479</v>
       </c>
       <c r="R61" t="n">
-        <v>7023728</v>
+        <v>7023680</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7021,11 +6992,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7052,10 +7018,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122790839</v>
+        <v>122791391</v>
       </c>
       <c r="B62" t="n">
-        <v>91632</v>
+        <v>79847</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7064,25 +7030,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7092,10 +7058,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494767</v>
+        <v>494717</v>
       </c>
       <c r="R62" t="n">
-        <v>7023761</v>
+        <v>7023829</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7154,10 +7120,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122789892</v>
+        <v>122789784</v>
       </c>
       <c r="B63" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7170,34 +7136,43 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494409</v>
+        <v>494225</v>
       </c>
       <c r="R63" t="n">
-        <v>7023573</v>
+        <v>7023525</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7256,10 +7231,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122789784</v>
+        <v>122789797</v>
       </c>
       <c r="B64" t="n">
-        <v>56680</v>
+        <v>57494</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7272,16 +7247,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7294,6 +7269,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -7305,10 +7290,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494225</v>
+        <v>494329</v>
       </c>
       <c r="R64" t="n">
-        <v>7023525</v>
+        <v>7023594</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7367,10 +7352,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122791391</v>
+        <v>122790194</v>
       </c>
       <c r="B65" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7383,34 +7368,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494717</v>
+        <v>494560</v>
       </c>
       <c r="R65" t="n">
-        <v>7023829</v>
+        <v>7023660</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7443,6 +7433,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7469,10 +7464,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122790826</v>
+        <v>122790286</v>
       </c>
       <c r="B66" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7485,21 +7480,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7509,10 +7504,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494767</v>
+        <v>494551</v>
       </c>
       <c r="R66" t="n">
-        <v>7023760</v>
+        <v>7023728</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7545,6 +7540,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122770429</v>
+        <v>122774670</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493992</v>
+        <v>494555</v>
       </c>
       <c r="R6" t="n">
-        <v>7023434</v>
+        <v>7023779</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122774670</v>
+        <v>122770429</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,34 +1221,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494555</v>
+        <v>493992</v>
       </c>
       <c r="R7" t="n">
-        <v>7023779</v>
+        <v>7023434</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2830,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122773458</v>
+        <v>122773527</v>
       </c>
       <c r="B22" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2846,34 +2846,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494786</v>
+        <v>494802</v>
       </c>
       <c r="R22" t="n">
-        <v>7023741</v>
+        <v>7023657</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,6 +2911,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2932,7 +2942,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122773527</v>
+        <v>122777145</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -2968,7 +2978,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2977,10 +2987,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494802</v>
+        <v>494559</v>
       </c>
       <c r="R23" t="n">
-        <v>7023657</v>
+        <v>7023653</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3044,10 +3054,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122777145</v>
+        <v>122773458</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3060,39 +3070,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494559</v>
+        <v>494786</v>
       </c>
       <c r="R24" t="n">
-        <v>7023653</v>
+        <v>7023741</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3125,11 +3130,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -5449,10 +5449,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122773465</v>
+        <v>122771481</v>
       </c>
       <c r="B47" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5461,43 +5461,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494786</v>
+        <v>494353</v>
       </c>
       <c r="R47" t="n">
-        <v>7023741</v>
+        <v>7023580</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5556,10 +5551,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122771481</v>
+        <v>122771655</v>
       </c>
       <c r="B48" t="n">
-        <v>79883</v>
+        <v>79847</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5568,25 +5563,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5596,10 +5591,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494353</v>
+        <v>494427</v>
       </c>
       <c r="R48" t="n">
-        <v>7023580</v>
+        <v>7023595</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5658,7 +5653,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122771655</v>
+        <v>122773465</v>
       </c>
       <c r="B49" t="n">
         <v>79847</v>
@@ -5692,16 +5687,21 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494427</v>
+        <v>494786</v>
       </c>
       <c r="R49" t="n">
-        <v>7023595</v>
+        <v>7023741</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6600,10 +6600,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122790839</v>
+        <v>122791209</v>
       </c>
       <c r="B58" t="n">
-        <v>91640</v>
+        <v>79848</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6612,25 +6612,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494767</v>
+        <v>494707</v>
       </c>
       <c r="R58" t="n">
-        <v>7023761</v>
+        <v>7023829</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6702,10 +6702,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122791209</v>
+        <v>122790839</v>
       </c>
       <c r="B59" t="n">
-        <v>79848</v>
+        <v>91640</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6714,25 +6714,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494707</v>
+        <v>494767</v>
       </c>
       <c r="R59" t="n">
-        <v>7023829</v>
+        <v>7023761</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7120,10 +7120,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122789784</v>
+        <v>122790194</v>
       </c>
       <c r="B63" t="n">
-        <v>56680</v>
+        <v>57478</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7136,16 +7136,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7153,14 +7153,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7169,10 +7165,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494225</v>
+        <v>494560</v>
       </c>
       <c r="R63" t="n">
-        <v>7023525</v>
+        <v>7023660</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7205,6 +7201,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7231,10 +7232,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122789797</v>
+        <v>122789784</v>
       </c>
       <c r="B64" t="n">
-        <v>57494</v>
+        <v>56680</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7247,16 +7248,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7269,16 +7270,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -7290,10 +7281,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494329</v>
+        <v>494225</v>
       </c>
       <c r="R64" t="n">
-        <v>7023594</v>
+        <v>7023525</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7352,10 +7343,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122790194</v>
+        <v>122789797</v>
       </c>
       <c r="B65" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7368,16 +7359,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7385,10 +7376,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7397,10 +7402,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494560</v>
+        <v>494329</v>
       </c>
       <c r="R65" t="n">
-        <v>7023660</v>
+        <v>7023594</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7433,11 +7438,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122771474</v>
+        <v>122770929</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +798,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494356</v>
+        <v>494181</v>
       </c>
       <c r="R3" t="n">
-        <v>7023575</v>
+        <v>7023603</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122771891</v>
+        <v>122774455</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>91519</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,43 +910,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494515</v>
+        <v>494571</v>
       </c>
       <c r="R4" t="n">
-        <v>7023580</v>
+        <v>7023780</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,11 +974,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122773319</v>
+        <v>122772874</v>
       </c>
       <c r="B5" t="n">
-        <v>90963</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,38 +1012,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494758</v>
+        <v>494680</v>
       </c>
       <c r="R5" t="n">
-        <v>7023767</v>
+        <v>7023737</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122774670</v>
+        <v>122772290</v>
       </c>
       <c r="B6" t="n">
         <v>79847</v>
@@ -1137,16 +1141,21 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494555</v>
+        <v>494557</v>
       </c>
       <c r="R6" t="n">
-        <v>7023779</v>
+        <v>7023675</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122770429</v>
+        <v>122774566</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,39 +1230,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493992</v>
+        <v>494563</v>
       </c>
       <c r="R7" t="n">
-        <v>7023434</v>
+        <v>7023786</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1290,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122773407</v>
+        <v>122771661</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494790</v>
+        <v>494425</v>
       </c>
       <c r="R8" t="n">
-        <v>7023741</v>
+        <v>7023600</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,11 +1392,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122772531</v>
+        <v>122772413</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,39 +1434,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494557</v>
+        <v>494559</v>
       </c>
       <c r="R9" t="n">
-        <v>7023650</v>
+        <v>7023689</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,11 +1494,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122774987</v>
+        <v>122774597</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,39 +1536,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494357</v>
+        <v>494556</v>
       </c>
       <c r="R10" t="n">
-        <v>7023735</v>
+        <v>7023778</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,11 +1596,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122772707</v>
+        <v>122774693</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1664,39 +1638,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494582</v>
+        <v>494544</v>
       </c>
       <c r="R11" t="n">
-        <v>7023673</v>
+        <v>7023772</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,11 +1698,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122772985</v>
+        <v>122771481</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>79883</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,43 +1736,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494655</v>
+        <v>494353</v>
       </c>
       <c r="R12" t="n">
-        <v>7023708</v>
+        <v>7023580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,11 +1800,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,7 +1826,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773088</v>
+        <v>122772714</v>
       </c>
       <c r="B13" t="n">
         <v>79847</v>
@@ -1906,21 +1860,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494700</v>
+        <v>494589</v>
       </c>
       <c r="R13" t="n">
-        <v>7023729</v>
+        <v>7023675</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,7 +1928,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122774715</v>
+        <v>122774730</v>
       </c>
       <c r="B14" t="n">
         <v>79847</v>
@@ -2013,16 +1962,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494547</v>
+        <v>494558</v>
       </c>
       <c r="R14" t="n">
-        <v>7023756</v>
+        <v>7023767</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,7 +2035,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122774730</v>
+        <v>122774670</v>
       </c>
       <c r="B15" t="n">
         <v>79847</v>
@@ -2115,21 +2069,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494558</v>
+        <v>494555</v>
       </c>
       <c r="R15" t="n">
-        <v>7023767</v>
+        <v>7023779</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2188,10 +2137,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122774538</v>
+        <v>122773527</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,27 +2153,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2233,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494563</v>
+        <v>494802</v>
       </c>
       <c r="R16" t="n">
-        <v>7023781</v>
+        <v>7023657</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,6 +2218,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2249,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122774764</v>
+        <v>122771667</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2307,25 +2261,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2289,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494568</v>
+        <v>494425</v>
       </c>
       <c r="R17" t="n">
-        <v>7023757</v>
+        <v>7023600</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,11 +2325,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,10 +2351,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122774828</v>
+        <v>122771956</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2418,34 +2367,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494562</v>
+        <v>494521</v>
       </c>
       <c r="R18" t="n">
-        <v>7023728</v>
+        <v>7023591</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2478,6 +2432,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2504,10 +2463,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122772081</v>
+        <v>122772994</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2520,34 +2479,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494512</v>
+        <v>494664</v>
       </c>
       <c r="R19" t="n">
-        <v>7023641</v>
+        <v>7023760</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,10 +2574,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122771901</v>
+        <v>122772081</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2622,39 +2590,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494516</v>
+        <v>494512</v>
       </c>
       <c r="R20" t="n">
-        <v>7023586</v>
+        <v>7023641</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,11 +2650,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2718,10 +2676,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122772729</v>
+        <v>122771384</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2734,39 +2692,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494591</v>
+        <v>494334</v>
       </c>
       <c r="R21" t="n">
-        <v>7023673</v>
+        <v>7023580</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,11 +2752,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,10 +2778,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122773527</v>
+        <v>122772356</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2846,39 +2794,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494802</v>
+        <v>494558</v>
       </c>
       <c r="R22" t="n">
-        <v>7023657</v>
+        <v>7023688</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,7 +2858,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,7 +2885,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122777145</v>
+        <v>122771901</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -2978,7 +2921,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2987,10 +2930,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494559</v>
+        <v>494516</v>
       </c>
       <c r="R23" t="n">
-        <v>7023653</v>
+        <v>7023586</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3054,10 +2997,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122773458</v>
+        <v>122772531</v>
       </c>
       <c r="B24" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3070,34 +3013,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494786</v>
+        <v>494557</v>
       </c>
       <c r="R24" t="n">
-        <v>7023741</v>
+        <v>7023650</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,6 +3078,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,10 +3109,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122771956</v>
+        <v>122774538</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3172,27 +3125,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3201,10 +3154,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494521</v>
+        <v>494563</v>
       </c>
       <c r="R25" t="n">
-        <v>7023591</v>
+        <v>7023781</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,11 +3190,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3268,7 +3216,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122774372</v>
+        <v>122773407</v>
       </c>
       <c r="B26" t="n">
         <v>79847</v>
@@ -3308,10 +3256,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494839</v>
+        <v>494790</v>
       </c>
       <c r="R26" t="n">
-        <v>7023830</v>
+        <v>7023741</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3344,6 +3292,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3370,10 +3323,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122771745</v>
+        <v>122772729</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3386,34 +3339,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494449</v>
+        <v>494591</v>
       </c>
       <c r="R27" t="n">
-        <v>7023602</v>
+        <v>7023673</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3446,6 +3404,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3472,10 +3435,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122772290</v>
+        <v>122777145</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3488,27 +3451,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3517,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494557</v>
+        <v>494559</v>
       </c>
       <c r="R28" t="n">
-        <v>7023675</v>
+        <v>7023653</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3553,6 +3516,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3579,10 +3547,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122774777</v>
+        <v>122774987</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3595,34 +3563,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494582</v>
+        <v>494357</v>
       </c>
       <c r="R29" t="n">
-        <v>7023728</v>
+        <v>7023735</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3659,7 +3632,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3686,7 +3659,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122773216</v>
+        <v>122774828</v>
       </c>
       <c r="B30" t="n">
         <v>79847</v>
@@ -3720,21 +3693,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494716</v>
+        <v>494562</v>
       </c>
       <c r="R30" t="n">
-        <v>7023730</v>
+        <v>7023728</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3793,10 +3761,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122771489</v>
+        <v>122774777</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3809,34 +3777,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494147</v>
+        <v>494582</v>
       </c>
       <c r="R31" t="n">
-        <v>7023571</v>
+        <v>7023728</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3869,6 +3837,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3895,7 +3868,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122774696</v>
+        <v>122772044</v>
       </c>
       <c r="B32" t="n">
         <v>79847</v>
@@ -3935,10 +3908,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494538</v>
+        <v>494524</v>
       </c>
       <c r="R32" t="n">
-        <v>7023761</v>
+        <v>7023624</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3971,11 +3944,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4002,10 +3970,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122771661</v>
+        <v>122772707</v>
       </c>
       <c r="B33" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4014,38 +3982,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494425</v>
+        <v>494582</v>
       </c>
       <c r="R33" t="n">
-        <v>7023600</v>
+        <v>7023673</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4078,6 +4051,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4104,10 +4082,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122772413</v>
+        <v>122771489</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4120,34 +4098,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494559</v>
+        <v>494147</v>
       </c>
       <c r="R34" t="n">
-        <v>7023689</v>
+        <v>7023571</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4206,10 +4184,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122772030</v>
+        <v>122773458</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4222,21 +4200,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4246,10 +4224,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494526</v>
+        <v>494786</v>
       </c>
       <c r="R35" t="n">
-        <v>7023606</v>
+        <v>7023741</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4308,7 +4286,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122771384</v>
+        <v>122771474</v>
       </c>
       <c r="B36" t="n">
         <v>79847</v>
@@ -4342,16 +4320,21 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494334</v>
+        <v>494356</v>
       </c>
       <c r="R36" t="n">
-        <v>7023580</v>
+        <v>7023575</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4410,7 +4393,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122772714</v>
+        <v>122774372</v>
       </c>
       <c r="B37" t="n">
         <v>79847</v>
@@ -4450,10 +4433,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494589</v>
+        <v>494839</v>
       </c>
       <c r="R37" t="n">
-        <v>7023675</v>
+        <v>7023830</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4512,7 +4495,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122774597</v>
+        <v>122773465</v>
       </c>
       <c r="B38" t="n">
         <v>79847</v>
@@ -4546,16 +4529,21 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494556</v>
+        <v>494786</v>
       </c>
       <c r="R38" t="n">
-        <v>7023778</v>
+        <v>7023741</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4614,7 +4602,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122774693</v>
+        <v>122774764</v>
       </c>
       <c r="B39" t="n">
         <v>79847</v>
@@ -4654,10 +4642,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494544</v>
+        <v>494568</v>
       </c>
       <c r="R39" t="n">
-        <v>7023772</v>
+        <v>7023757</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4690,6 +4678,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4716,10 +4709,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122772044</v>
+        <v>122773319</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>90963</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4728,25 +4721,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4756,10 +4749,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494524</v>
+        <v>494758</v>
       </c>
       <c r="R40" t="n">
-        <v>7023624</v>
+        <v>7023767</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4818,10 +4811,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122770882</v>
+        <v>122773088</v>
       </c>
       <c r="B41" t="n">
-        <v>90970</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4834,34 +4827,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494160</v>
+        <v>494700</v>
       </c>
       <c r="R41" t="n">
-        <v>7023595</v>
+        <v>7023729</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4920,7 +4918,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122772874</v>
+        <v>122774696</v>
       </c>
       <c r="B42" t="n">
         <v>79847</v>
@@ -4954,21 +4952,16 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494680</v>
+        <v>494538</v>
       </c>
       <c r="R42" t="n">
-        <v>7023737</v>
+        <v>7023761</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5001,6 +4994,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5027,10 +5025,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122774566</v>
+        <v>122771891</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5043,34 +5041,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494563</v>
+        <v>494515</v>
       </c>
       <c r="R43" t="n">
-        <v>7023786</v>
+        <v>7023580</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5103,6 +5106,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5129,10 +5137,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122772356</v>
+        <v>122774563</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5145,21 +5153,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5169,10 +5177,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494558</v>
+        <v>494563</v>
       </c>
       <c r="R44" t="n">
-        <v>7023688</v>
+        <v>7023786</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5205,11 +5213,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5236,10 +5239,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122772994</v>
+        <v>122771655</v>
       </c>
       <c r="B45" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5252,43 +5255,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494664</v>
+        <v>494427</v>
       </c>
       <c r="R45" t="n">
-        <v>7023760</v>
+        <v>7023595</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5347,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122774563</v>
+        <v>122774715</v>
       </c>
       <c r="B46" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5363,21 +5357,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5387,10 +5381,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494563</v>
+        <v>494547</v>
       </c>
       <c r="R46" t="n">
-        <v>7023786</v>
+        <v>7023756</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5449,10 +5443,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122771481</v>
+        <v>122770429</v>
       </c>
       <c r="B47" t="n">
-        <v>79883</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5461,38 +5455,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494353</v>
+        <v>493992</v>
       </c>
       <c r="R47" t="n">
-        <v>7023580</v>
+        <v>7023434</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5525,6 +5524,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5551,7 +5555,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122771655</v>
+        <v>122772030</v>
       </c>
       <c r="B48" t="n">
         <v>79847</v>
@@ -5591,10 +5595,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494427</v>
+        <v>494526</v>
       </c>
       <c r="R48" t="n">
-        <v>7023595</v>
+        <v>7023606</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5653,7 +5657,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122773465</v>
+        <v>122773216</v>
       </c>
       <c r="B49" t="n">
         <v>79847</v>
@@ -5698,10 +5702,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494786</v>
+        <v>494716</v>
       </c>
       <c r="R49" t="n">
-        <v>7023741</v>
+        <v>7023730</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5760,10 +5764,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122774455</v>
+        <v>122772985</v>
       </c>
       <c r="B50" t="n">
-        <v>91519</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5772,38 +5776,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494571</v>
+        <v>494655</v>
       </c>
       <c r="R50" t="n">
-        <v>7023780</v>
+        <v>7023708</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5836,6 +5845,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5862,7 +5876,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122774393</v>
+        <v>122773254</v>
       </c>
       <c r="B51" t="n">
         <v>79847</v>
@@ -5896,16 +5910,21 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494710</v>
+        <v>494730</v>
       </c>
       <c r="R51" t="n">
-        <v>7023786</v>
+        <v>7023730</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5964,7 +5983,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122773254</v>
+        <v>122774393</v>
       </c>
       <c r="B52" t="n">
         <v>79847</v>
@@ -5998,21 +6017,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494730</v>
+        <v>494710</v>
       </c>
       <c r="R52" t="n">
-        <v>7023730</v>
+        <v>7023786</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6071,10 +6085,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122770929</v>
+        <v>122771745</v>
       </c>
       <c r="B53" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6087,48 +6101,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494181</v>
+        <v>494449</v>
       </c>
       <c r="R53" t="n">
-        <v>7023603</v>
+        <v>7023602</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6187,10 +6187,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122771667</v>
+        <v>122770882</v>
       </c>
       <c r="B54" t="n">
-        <v>79807</v>
+        <v>90970</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6199,38 +6199,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494425</v>
+        <v>494160</v>
       </c>
       <c r="R54" t="n">
-        <v>7023600</v>
+        <v>7023595</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6289,10 +6289,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122791151</v>
+        <v>122789784</v>
       </c>
       <c r="B55" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6305,27 +6305,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6334,10 +6338,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494727</v>
+        <v>494225</v>
       </c>
       <c r="R55" t="n">
-        <v>7023818</v>
+        <v>7023525</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6396,7 +6400,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122790826</v>
+        <v>122789892</v>
       </c>
       <c r="B56" t="n">
         <v>79847</v>
@@ -6436,10 +6440,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494767</v>
+        <v>494409</v>
       </c>
       <c r="R56" t="n">
-        <v>7023760</v>
+        <v>7023573</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6498,7 +6502,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122789892</v>
+        <v>122791171</v>
       </c>
       <c r="B57" t="n">
         <v>79847</v>
@@ -6538,10 +6542,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494409</v>
+        <v>494727</v>
       </c>
       <c r="R57" t="n">
-        <v>7023573</v>
+        <v>7023818</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6574,6 +6578,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6600,10 +6609,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122791209</v>
+        <v>122789797</v>
       </c>
       <c r="B58" t="n">
-        <v>79848</v>
+        <v>57494</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6616,34 +6625,53 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494707</v>
+        <v>494329</v>
       </c>
       <c r="R58" t="n">
-        <v>7023829</v>
+        <v>7023594</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6702,10 +6730,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122790839</v>
+        <v>122790194</v>
       </c>
       <c r="B59" t="n">
-        <v>91640</v>
+        <v>57478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6714,38 +6742,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494767</v>
+        <v>494560</v>
       </c>
       <c r="R59" t="n">
-        <v>7023761</v>
+        <v>7023660</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6778,6 +6811,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6804,7 +6842,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122790289</v>
+        <v>122790826</v>
       </c>
       <c r="B60" t="n">
         <v>79847</v>
@@ -6844,10 +6882,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494551</v>
+        <v>494767</v>
       </c>
       <c r="R60" t="n">
-        <v>7023731</v>
+        <v>7023760</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6880,11 +6918,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7018,10 +7051,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122791391</v>
+        <v>122791209</v>
       </c>
       <c r="B62" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7034,21 +7067,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7058,7 +7091,7 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494717</v>
+        <v>494707</v>
       </c>
       <c r="R62" t="n">
         <v>7023829</v>
@@ -7120,10 +7153,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122790194</v>
+        <v>122791391</v>
       </c>
       <c r="B63" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7136,39 +7169,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494560</v>
+        <v>494717</v>
       </c>
       <c r="R63" t="n">
-        <v>7023660</v>
+        <v>7023829</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7201,11 +7229,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7232,10 +7255,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122789784</v>
+        <v>122790839</v>
       </c>
       <c r="B64" t="n">
-        <v>56680</v>
+        <v>91640</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7244,47 +7267,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102612</v>
+        <v>3298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494225</v>
+        <v>494767</v>
       </c>
       <c r="R64" t="n">
-        <v>7023525</v>
+        <v>7023761</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7343,10 +7357,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122789797</v>
+        <v>122790289</v>
       </c>
       <c r="B65" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7359,53 +7373,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494329</v>
+        <v>494551</v>
       </c>
       <c r="R65" t="n">
-        <v>7023594</v>
+        <v>7023731</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7438,6 +7433,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122774455</v>
+        <v>122772874</v>
       </c>
       <c r="B4" t="n">
-        <v>91519</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,38 +910,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494571</v>
+        <v>494680</v>
       </c>
       <c r="R4" t="n">
-        <v>7023780</v>
+        <v>7023737</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1005,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122772874</v>
+        <v>122772290</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1045,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494680</v>
+        <v>494557</v>
       </c>
       <c r="R5" t="n">
-        <v>7023737</v>
+        <v>7023675</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122772290</v>
+        <v>122774566</v>
       </c>
       <c r="B6" t="n">
         <v>79847</v>
@@ -1141,21 +1146,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494557</v>
+        <v>494563</v>
       </c>
       <c r="R6" t="n">
-        <v>7023675</v>
+        <v>7023786</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122774566</v>
+        <v>122774455</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>91519</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,25 +1226,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494563</v>
+        <v>494571</v>
       </c>
       <c r="R7" t="n">
-        <v>7023786</v>
+        <v>7023780</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -3868,10 +3868,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122772044</v>
+        <v>122772707</v>
       </c>
       <c r="B32" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3884,34 +3884,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494524</v>
+        <v>494582</v>
       </c>
       <c r="R32" t="n">
-        <v>7023624</v>
+        <v>7023673</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3944,6 +3949,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3970,10 +3980,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122772707</v>
+        <v>122772044</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3986,39 +3996,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494582</v>
+        <v>494524</v>
       </c>
       <c r="R33" t="n">
-        <v>7023673</v>
+        <v>7023624</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4051,11 +4056,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4082,10 +4082,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122771489</v>
+        <v>122771474</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4098,34 +4098,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494147</v>
+        <v>494356</v>
       </c>
       <c r="R34" t="n">
-        <v>7023571</v>
+        <v>7023575</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4184,10 +4189,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122773458</v>
+        <v>122774372</v>
       </c>
       <c r="B35" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4200,21 +4205,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4224,10 +4229,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494786</v>
+        <v>494839</v>
       </c>
       <c r="R35" t="n">
-        <v>7023741</v>
+        <v>7023830</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4286,10 +4291,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122771474</v>
+        <v>122771489</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4302,39 +4307,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494356</v>
+        <v>494147</v>
       </c>
       <c r="R36" t="n">
-        <v>7023575</v>
+        <v>7023571</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122774372</v>
+        <v>122773458</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494839</v>
+        <v>494786</v>
       </c>
       <c r="R37" t="n">
-        <v>7023830</v>
+        <v>7023741</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122772874</v>
+        <v>122774455</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>91519</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,43 +910,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494680</v>
+        <v>494571</v>
       </c>
       <c r="R4" t="n">
-        <v>7023737</v>
+        <v>7023780</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1000,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122772290</v>
+        <v>122772874</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1050,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494557</v>
+        <v>494680</v>
       </c>
       <c r="R5" t="n">
-        <v>7023675</v>
+        <v>7023737</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122774566</v>
+        <v>122772290</v>
       </c>
       <c r="B6" t="n">
         <v>79847</v>
@@ -1146,16 +1141,21 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494563</v>
+        <v>494557</v>
       </c>
       <c r="R6" t="n">
-        <v>7023786</v>
+        <v>7023675</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122774455</v>
+        <v>122774566</v>
       </c>
       <c r="B7" t="n">
-        <v>91519</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,25 +1226,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494571</v>
+        <v>494563</v>
       </c>
       <c r="R7" t="n">
-        <v>7023780</v>
+        <v>7023786</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2249,10 +2249,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122771667</v>
+        <v>122771956</v>
       </c>
       <c r="B17" t="n">
-        <v>79807</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2261,38 +2261,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494425</v>
+        <v>494521</v>
       </c>
       <c r="R17" t="n">
-        <v>7023600</v>
+        <v>7023591</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2325,6 +2330,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2351,10 +2361,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122771956</v>
+        <v>122771667</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>79807</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2363,43 +2373,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494521</v>
+        <v>494425</v>
       </c>
       <c r="R18" t="n">
-        <v>7023591</v>
+        <v>7023600</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2432,11 +2437,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3868,10 +3868,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122772707</v>
+        <v>122772044</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3884,39 +3884,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494582</v>
+        <v>494524</v>
       </c>
       <c r="R32" t="n">
-        <v>7023673</v>
+        <v>7023624</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3949,11 +3944,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3980,10 +3970,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122772044</v>
+        <v>122772707</v>
       </c>
       <c r="B33" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3996,34 +3986,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494524</v>
+        <v>494582</v>
       </c>
       <c r="R33" t="n">
-        <v>7023624</v>
+        <v>7023673</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4056,6 +4051,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4495,10 +4495,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122773465</v>
+        <v>122773319</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>90963</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4507,43 +4507,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494786</v>
+        <v>494758</v>
       </c>
       <c r="R38" t="n">
-        <v>7023741</v>
+        <v>7023767</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4602,7 +4597,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122774764</v>
+        <v>122773465</v>
       </c>
       <c r="B39" t="n">
         <v>79847</v>
@@ -4636,16 +4631,21 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494568</v>
+        <v>494786</v>
       </c>
       <c r="R39" t="n">
-        <v>7023757</v>
+        <v>7023741</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,11 +4678,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4709,10 +4704,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122773319</v>
+        <v>122774764</v>
       </c>
       <c r="B40" t="n">
-        <v>90963</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4721,25 +4716,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4749,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494758</v>
+        <v>494568</v>
       </c>
       <c r="R40" t="n">
-        <v>7023767</v>
+        <v>7023757</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4785,6 +4780,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122774464</v>
+        <v>122773458</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494570</v>
+        <v>494786</v>
       </c>
       <c r="R2" t="n">
-        <v>7023783</v>
+        <v>7023741</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122770929</v>
+        <v>122773407</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,48 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494181</v>
+        <v>494790</v>
       </c>
       <c r="R3" t="n">
-        <v>7023603</v>
+        <v>7023741</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122774455</v>
+        <v>122774693</v>
       </c>
       <c r="B4" t="n">
-        <v>91519</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494571</v>
+        <v>494544</v>
       </c>
       <c r="R4" t="n">
-        <v>7023780</v>
+        <v>7023772</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122772874</v>
+        <v>122772729</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,27 +1002,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1045,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494680</v>
+        <v>494591</v>
       </c>
       <c r="R5" t="n">
-        <v>7023737</v>
+        <v>7023673</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122772290</v>
+        <v>122772994</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,27 +1114,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1152,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494557</v>
+        <v>494664</v>
       </c>
       <c r="R6" t="n">
-        <v>7023675</v>
+        <v>7023760</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122774566</v>
+        <v>122770929</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,34 +1225,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494563</v>
+        <v>494181</v>
       </c>
       <c r="R7" t="n">
-        <v>7023786</v>
+        <v>7023603</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122771661</v>
+        <v>122773254</v>
       </c>
       <c r="B8" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,38 +1337,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494425</v>
+        <v>494730</v>
       </c>
       <c r="R8" t="n">
-        <v>7023600</v>
+        <v>7023730</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122772413</v>
+        <v>122771489</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,34 +1448,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494559</v>
+        <v>494147</v>
       </c>
       <c r="R9" t="n">
-        <v>7023689</v>
+        <v>7023571</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,7 +1534,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122774597</v>
+        <v>122772413</v>
       </c>
       <c r="B10" t="n">
         <v>79847</v>
@@ -1560,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494556</v>
+        <v>494559</v>
       </c>
       <c r="R10" t="n">
-        <v>7023778</v>
+        <v>7023689</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1636,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122774693</v>
+        <v>122774393</v>
       </c>
       <c r="B11" t="n">
         <v>79847</v>
@@ -1662,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494544</v>
+        <v>494710</v>
       </c>
       <c r="R11" t="n">
-        <v>7023772</v>
+        <v>7023786</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,10 +1738,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122771481</v>
+        <v>122772985</v>
       </c>
       <c r="B12" t="n">
-        <v>79883</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,38 +1750,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494353</v>
+        <v>494655</v>
       </c>
       <c r="R12" t="n">
-        <v>7023580</v>
+        <v>7023708</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,6 +1819,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122772714</v>
+        <v>122774987</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1842,34 +1866,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494589</v>
+        <v>494357</v>
       </c>
       <c r="R13" t="n">
-        <v>7023675</v>
+        <v>7023735</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,6 +1931,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122774730</v>
+        <v>122770882</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,39 +1978,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494558</v>
+        <v>494160</v>
       </c>
       <c r="R14" t="n">
-        <v>7023767</v>
+        <v>7023595</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2035,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122774670</v>
+        <v>122771667</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,25 +2076,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2075,10 +2104,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494555</v>
+        <v>494425</v>
       </c>
       <c r="R15" t="n">
-        <v>7023779</v>
+        <v>7023600</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122773527</v>
+        <v>122774745</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2153,39 +2182,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494802</v>
+        <v>494558</v>
       </c>
       <c r="R16" t="n">
-        <v>7023657</v>
+        <v>7023767</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2218,11 +2242,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2249,10 +2268,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122771956</v>
+        <v>122772044</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2265,39 +2284,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494521</v>
+        <v>494524</v>
       </c>
       <c r="R17" t="n">
-        <v>7023591</v>
+        <v>7023624</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,11 +2344,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2361,10 +2370,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122771667</v>
+        <v>122772531</v>
       </c>
       <c r="B18" t="n">
-        <v>79807</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2373,38 +2382,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494425</v>
+        <v>494557</v>
       </c>
       <c r="R18" t="n">
-        <v>7023600</v>
+        <v>7023650</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,6 +2451,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2463,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122772994</v>
+        <v>122771481</v>
       </c>
       <c r="B19" t="n">
-        <v>57631</v>
+        <v>79883</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2475,47 +2494,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494664</v>
+        <v>494353</v>
       </c>
       <c r="R19" t="n">
-        <v>7023760</v>
+        <v>7023580</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2584,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122772081</v>
+        <v>122773465</v>
       </c>
       <c r="B20" t="n">
         <v>79847</v>
@@ -2608,16 +2618,21 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494512</v>
+        <v>494786</v>
       </c>
       <c r="R20" t="n">
-        <v>7023641</v>
+        <v>7023741</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2691,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122771384</v>
+        <v>122774715</v>
       </c>
       <c r="B21" t="n">
         <v>79847</v>
@@ -2716,10 +2731,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494334</v>
+        <v>494547</v>
       </c>
       <c r="R21" t="n">
-        <v>7023580</v>
+        <v>7023756</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122772356</v>
+        <v>122772707</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2794,34 +2809,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494558</v>
+        <v>494582</v>
       </c>
       <c r="R22" t="n">
-        <v>7023688</v>
+        <v>7023673</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2858,7 +2878,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2885,10 +2905,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122771901</v>
+        <v>122774563</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2901,39 +2921,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494516</v>
+        <v>494563</v>
       </c>
       <c r="R23" t="n">
-        <v>7023586</v>
+        <v>7023786</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2966,11 +2981,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2997,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122772531</v>
+        <v>122774670</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3013,39 +3023,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494557</v>
+        <v>494555</v>
       </c>
       <c r="R24" t="n">
-        <v>7023650</v>
+        <v>7023779</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3078,11 +3083,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3109,10 +3109,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122774538</v>
+        <v>122777145</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3125,27 +3125,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494563</v>
+        <v>494559</v>
       </c>
       <c r="R25" t="n">
-        <v>7023781</v>
+        <v>7023653</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3190,6 +3190,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3216,7 +3221,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122773407</v>
+        <v>122772081</v>
       </c>
       <c r="B26" t="n">
         <v>79847</v>
@@ -3256,10 +3261,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494790</v>
+        <v>494512</v>
       </c>
       <c r="R26" t="n">
-        <v>7023741</v>
+        <v>7023641</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3292,11 +3297,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3323,10 +3323,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122772729</v>
+        <v>122771474</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3339,27 +3339,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3368,10 +3368,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494591</v>
+        <v>494356</v>
       </c>
       <c r="R27" t="n">
-        <v>7023673</v>
+        <v>7023575</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3404,11 +3404,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3435,10 +3430,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122777145</v>
+        <v>122774464</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3451,27 +3446,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3480,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494559</v>
+        <v>494570</v>
       </c>
       <c r="R28" t="n">
-        <v>7023653</v>
+        <v>7023783</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3516,11 +3511,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3547,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122774987</v>
+        <v>122771384</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3563,39 +3553,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494357</v>
+        <v>494334</v>
       </c>
       <c r="R29" t="n">
-        <v>7023735</v>
+        <v>7023580</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3628,11 +3613,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3659,7 +3639,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122774828</v>
+        <v>122772356</v>
       </c>
       <c r="B30" t="n">
         <v>79847</v>
@@ -3699,10 +3679,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494562</v>
+        <v>494558</v>
       </c>
       <c r="R30" t="n">
-        <v>7023728</v>
+        <v>7023688</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3735,6 +3715,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3868,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122772044</v>
+        <v>122771956</v>
       </c>
       <c r="B32" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3884,34 +3869,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494524</v>
+        <v>494521</v>
       </c>
       <c r="R32" t="n">
-        <v>7023624</v>
+        <v>7023591</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3944,6 +3934,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3970,7 +3965,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122772707</v>
+        <v>122771891</v>
       </c>
       <c r="B33" t="n">
         <v>57478</v>
@@ -4015,10 +4010,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494582</v>
+        <v>494515</v>
       </c>
       <c r="R33" t="n">
-        <v>7023673</v>
+        <v>7023580</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4082,7 +4077,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122771474</v>
+        <v>122772874</v>
       </c>
       <c r="B34" t="n">
         <v>79847</v>
@@ -4127,10 +4122,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494356</v>
+        <v>494680</v>
       </c>
       <c r="R34" t="n">
-        <v>7023575</v>
+        <v>7023737</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4189,7 +4184,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122774372</v>
+        <v>122774696</v>
       </c>
       <c r="B35" t="n">
         <v>79847</v>
@@ -4229,10 +4224,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494839</v>
+        <v>494538</v>
       </c>
       <c r="R35" t="n">
-        <v>7023830</v>
+        <v>7023761</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4265,6 +4260,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4291,10 +4291,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122771489</v>
+        <v>122771745</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4307,34 +4307,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494147</v>
+        <v>494449</v>
       </c>
       <c r="R36" t="n">
-        <v>7023571</v>
+        <v>7023602</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122773458</v>
+        <v>122773319</v>
       </c>
       <c r="B37" t="n">
-        <v>79848</v>
+        <v>90963</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4405,25 +4405,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>1205</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494786</v>
+        <v>494758</v>
       </c>
       <c r="R37" t="n">
-        <v>7023741</v>
+        <v>7023767</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4495,10 +4495,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122773319</v>
+        <v>122772714</v>
       </c>
       <c r="B38" t="n">
-        <v>90963</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4507,25 +4507,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494758</v>
+        <v>494589</v>
       </c>
       <c r="R38" t="n">
-        <v>7023767</v>
+        <v>7023675</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,10 +4597,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122773465</v>
+        <v>122771901</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4613,27 +4613,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494786</v>
+        <v>494516</v>
       </c>
       <c r="R39" t="n">
-        <v>7023741</v>
+        <v>7023586</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,6 +4678,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4704,10 +4709,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122774764</v>
+        <v>122770429</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4720,34 +4725,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494568</v>
+        <v>493992</v>
       </c>
       <c r="R40" t="n">
-        <v>7023757</v>
+        <v>7023434</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4784,7 +4794,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4811,10 +4821,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122773088</v>
+        <v>122771661</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4823,43 +4833,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494700</v>
+        <v>494425</v>
       </c>
       <c r="R41" t="n">
-        <v>7023729</v>
+        <v>7023600</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4923,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122774696</v>
+        <v>122772030</v>
       </c>
       <c r="B42" t="n">
         <v>79847</v>
@@ -4958,10 +4963,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494538</v>
+        <v>494526</v>
       </c>
       <c r="R42" t="n">
-        <v>7023761</v>
+        <v>7023606</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4994,11 +4999,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5025,10 +5025,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122771891</v>
+        <v>122774455</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>91519</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5037,43 +5037,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494515</v>
+        <v>494571</v>
       </c>
       <c r="R43" t="n">
-        <v>7023580</v>
+        <v>7023780</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5106,11 +5101,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,10 +5127,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122774563</v>
+        <v>122774566</v>
       </c>
       <c r="B44" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5153,21 +5143,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5239,10 +5229,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122771655</v>
+        <v>122773527</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5255,34 +5245,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494427</v>
+        <v>494802</v>
       </c>
       <c r="R45" t="n">
-        <v>7023595</v>
+        <v>7023657</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5315,6 +5310,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5341,7 +5341,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122774715</v>
+        <v>122774764</v>
       </c>
       <c r="B46" t="n">
         <v>79847</v>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494547</v>
+        <v>494568</v>
       </c>
       <c r="R46" t="n">
-        <v>7023756</v>
+        <v>7023757</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5417,6 +5417,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5443,10 +5448,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122770429</v>
+        <v>122772290</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5459,39 +5464,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493992</v>
+        <v>494557</v>
       </c>
       <c r="R47" t="n">
-        <v>7023434</v>
+        <v>7023675</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5524,11 +5529,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5555,7 +5555,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122772030</v>
+        <v>122774828</v>
       </c>
       <c r="B48" t="n">
         <v>79847</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494526</v>
+        <v>494562</v>
       </c>
       <c r="R48" t="n">
-        <v>7023606</v>
+        <v>7023728</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5657,7 +5657,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122773216</v>
+        <v>122773088</v>
       </c>
       <c r="B49" t="n">
         <v>79847</v>
@@ -5702,10 +5702,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494716</v>
+        <v>494700</v>
       </c>
       <c r="R49" t="n">
-        <v>7023730</v>
+        <v>7023729</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5764,10 +5764,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122772985</v>
+        <v>122774597</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5780,39 +5780,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494655</v>
+        <v>494556</v>
       </c>
       <c r="R50" t="n">
-        <v>7023708</v>
+        <v>7023778</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5845,11 +5840,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5876,7 +5866,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122773254</v>
+        <v>122773216</v>
       </c>
       <c r="B51" t="n">
         <v>79847</v>
@@ -5921,7 +5911,7 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494730</v>
+        <v>494716</v>
       </c>
       <c r="R51" t="n">
         <v>7023730</v>
@@ -5983,7 +5973,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122774393</v>
+        <v>122774372</v>
       </c>
       <c r="B52" t="n">
         <v>79847</v>
@@ -6023,10 +6013,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494710</v>
+        <v>494839</v>
       </c>
       <c r="R52" t="n">
-        <v>7023786</v>
+        <v>7023830</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6085,7 +6075,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122771745</v>
+        <v>122774538</v>
       </c>
       <c r="B53" t="n">
         <v>79847</v>
@@ -6119,16 +6109,21 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494449</v>
+        <v>494563</v>
       </c>
       <c r="R53" t="n">
-        <v>7023602</v>
+        <v>7023781</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6187,10 +6182,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122770882</v>
+        <v>122771655</v>
       </c>
       <c r="B54" t="n">
-        <v>90970</v>
+        <v>79847</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6203,31 +6198,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494160</v>
+        <v>494427</v>
       </c>
       <c r="R54" t="n">
         <v>7023595</v>
@@ -6289,10 +6284,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122789784</v>
+        <v>122791151</v>
       </c>
       <c r="B55" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6305,31 +6300,27 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6338,10 +6329,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494225</v>
+        <v>494727</v>
       </c>
       <c r="R55" t="n">
-        <v>7023525</v>
+        <v>7023818</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6400,7 +6391,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122789892</v>
+        <v>122790452</v>
       </c>
       <c r="B56" t="n">
         <v>79847</v>
@@ -6434,16 +6425,21 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494409</v>
+        <v>494479</v>
       </c>
       <c r="R56" t="n">
-        <v>7023573</v>
+        <v>7023680</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6502,7 +6498,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122791171</v>
+        <v>122790289</v>
       </c>
       <c r="B57" t="n">
         <v>79847</v>
@@ -6542,10 +6538,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494727</v>
+        <v>494551</v>
       </c>
       <c r="R57" t="n">
-        <v>7023818</v>
+        <v>7023731</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6609,10 +6605,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122789797</v>
+        <v>122791209</v>
       </c>
       <c r="B58" t="n">
-        <v>57494</v>
+        <v>79848</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6625,53 +6621,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494329</v>
+        <v>494707</v>
       </c>
       <c r="R58" t="n">
-        <v>7023594</v>
+        <v>7023829</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6730,10 +6707,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122790194</v>
+        <v>122790826</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6746,39 +6723,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494560</v>
+        <v>494767</v>
       </c>
       <c r="R59" t="n">
-        <v>7023660</v>
+        <v>7023760</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6811,11 +6783,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6842,10 +6809,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122790826</v>
+        <v>122790839</v>
       </c>
       <c r="B60" t="n">
-        <v>79847</v>
+        <v>91640</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6854,25 +6821,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6885,7 +6852,7 @@
         <v>494767</v>
       </c>
       <c r="R60" t="n">
-        <v>7023760</v>
+        <v>7023761</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6944,7 +6911,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122790452</v>
+        <v>122791391</v>
       </c>
       <c r="B61" t="n">
         <v>79847</v>
@@ -6978,21 +6945,16 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494479</v>
+        <v>494717</v>
       </c>
       <c r="R61" t="n">
-        <v>7023680</v>
+        <v>7023829</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7051,10 +7013,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122791209</v>
+        <v>122789892</v>
       </c>
       <c r="B62" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7067,21 +7029,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7091,10 +7053,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494707</v>
+        <v>494409</v>
       </c>
       <c r="R62" t="n">
-        <v>7023829</v>
+        <v>7023573</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7153,10 +7115,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122791391</v>
+        <v>122789784</v>
       </c>
       <c r="B63" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7169,34 +7131,43 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494717</v>
+        <v>494225</v>
       </c>
       <c r="R63" t="n">
-        <v>7023829</v>
+        <v>7023525</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7255,10 +7226,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122790839</v>
+        <v>122790286</v>
       </c>
       <c r="B64" t="n">
-        <v>91640</v>
+        <v>79848</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7267,25 +7238,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7295,10 +7266,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494767</v>
+        <v>494551</v>
       </c>
       <c r="R64" t="n">
-        <v>7023761</v>
+        <v>7023728</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7331,6 +7302,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7357,10 +7333,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122790289</v>
+        <v>122789797</v>
       </c>
       <c r="B65" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7373,34 +7349,53 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494551</v>
+        <v>494329</v>
       </c>
       <c r="R65" t="n">
-        <v>7023731</v>
+        <v>7023594</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7433,11 +7428,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7464,10 +7454,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122790286</v>
+        <v>122790194</v>
       </c>
       <c r="B66" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7480,34 +7470,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494551</v>
+        <v>494560</v>
       </c>
       <c r="R66" t="n">
-        <v>7023728</v>
+        <v>7023660</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7544,7 +7539,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122773458</v>
+        <v>122774777</v>
       </c>
       <c r="B2" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494786</v>
+        <v>494582</v>
       </c>
       <c r="R2" t="n">
-        <v>7023741</v>
+        <v>7023728</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122773407</v>
+        <v>122773458</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,7 +822,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494790</v>
+        <v>494786</v>
       </c>
       <c r="R3" t="n">
         <v>7023741</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122774693</v>
+        <v>122772531</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494544</v>
+        <v>494557</v>
       </c>
       <c r="R4" t="n">
-        <v>7023772</v>
+        <v>7023650</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122772729</v>
+        <v>122770929</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,39 +1012,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494591</v>
+        <v>494181</v>
       </c>
       <c r="R5" t="n">
-        <v>7023673</v>
+        <v>7023603</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1086,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122772994</v>
+        <v>122772874</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,31 +1128,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1147,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494664</v>
+        <v>494680</v>
       </c>
       <c r="R6" t="n">
-        <v>7023760</v>
+        <v>7023737</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122770929</v>
+        <v>122774696</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,48 +1235,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494181</v>
+        <v>494538</v>
       </c>
       <c r="R7" t="n">
-        <v>7023603</v>
+        <v>7023761</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,6 +1295,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122773254</v>
+        <v>122772729</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,27 +1342,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1370,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494730</v>
+        <v>494591</v>
       </c>
       <c r="R8" t="n">
-        <v>7023730</v>
+        <v>7023673</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,6 +1407,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122771489</v>
+        <v>122772413</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,34 +1454,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494147</v>
+        <v>494559</v>
       </c>
       <c r="R9" t="n">
-        <v>7023571</v>
+        <v>7023689</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1540,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122772413</v>
+        <v>122774745</v>
       </c>
       <c r="B10" t="n">
         <v>79847</v>
@@ -1574,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494559</v>
+        <v>494558</v>
       </c>
       <c r="R10" t="n">
-        <v>7023689</v>
+        <v>7023767</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,7 +1642,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122774393</v>
+        <v>122771655</v>
       </c>
       <c r="B11" t="n">
         <v>79847</v>
@@ -1676,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494710</v>
+        <v>494427</v>
       </c>
       <c r="R11" t="n">
-        <v>7023786</v>
+        <v>7023595</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,7 +1744,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122772985</v>
+        <v>122773527</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1783,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494655</v>
+        <v>494802</v>
       </c>
       <c r="R12" t="n">
-        <v>7023708</v>
+        <v>7023657</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122774987</v>
+        <v>122771667</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>79807</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,43 +1868,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494357</v>
+        <v>494425</v>
       </c>
       <c r="R13" t="n">
-        <v>7023735</v>
+        <v>7023600</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,11 +1932,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122770882</v>
+        <v>122773465</v>
       </c>
       <c r="B14" t="n">
-        <v>90970</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1978,34 +1974,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494160</v>
+        <v>494786</v>
       </c>
       <c r="R14" t="n">
-        <v>7023595</v>
+        <v>7023741</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,10 +2065,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122771667</v>
+        <v>122772356</v>
       </c>
       <c r="B15" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2076,25 +2077,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2104,10 +2105,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494425</v>
+        <v>494558</v>
       </c>
       <c r="R15" t="n">
-        <v>7023600</v>
+        <v>7023688</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2140,6 +2141,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2166,10 +2172,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122774745</v>
+        <v>122774563</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2182,21 +2188,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2206,10 +2212,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494558</v>
+        <v>494563</v>
       </c>
       <c r="R16" t="n">
-        <v>7023767</v>
+        <v>7023786</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,10 +2274,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122772044</v>
+        <v>122771489</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2284,34 +2290,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494524</v>
+        <v>494147</v>
       </c>
       <c r="R17" t="n">
-        <v>7023624</v>
+        <v>7023571</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2376,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122772531</v>
+        <v>122771956</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2415,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494557</v>
+        <v>494521</v>
       </c>
       <c r="R18" t="n">
-        <v>7023650</v>
+        <v>7023591</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,10 +2488,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122771481</v>
+        <v>122771901</v>
       </c>
       <c r="B19" t="n">
-        <v>79883</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2494,38 +2500,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494353</v>
+        <v>494516</v>
       </c>
       <c r="R19" t="n">
-        <v>7023580</v>
+        <v>7023586</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2558,6 +2569,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2584,7 +2600,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122773465</v>
+        <v>122774538</v>
       </c>
       <c r="B20" t="n">
         <v>79847</v>
@@ -2629,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494786</v>
+        <v>494563</v>
       </c>
       <c r="R20" t="n">
-        <v>7023741</v>
+        <v>7023781</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2691,7 +2707,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122774715</v>
+        <v>122773254</v>
       </c>
       <c r="B21" t="n">
         <v>79847</v>
@@ -2725,16 +2741,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494547</v>
+        <v>494730</v>
       </c>
       <c r="R21" t="n">
-        <v>7023756</v>
+        <v>7023730</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,10 +2814,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122772707</v>
+        <v>122771474</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,27 +2830,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2838,10 +2859,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494582</v>
+        <v>494356</v>
       </c>
       <c r="R22" t="n">
-        <v>7023673</v>
+        <v>7023575</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2874,11 +2895,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2905,10 +2921,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122774563</v>
+        <v>122771745</v>
       </c>
       <c r="B23" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2921,21 +2937,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2945,10 +2961,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494563</v>
+        <v>494449</v>
       </c>
       <c r="R23" t="n">
-        <v>7023786</v>
+        <v>7023602</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,7 +3023,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122774670</v>
+        <v>122774764</v>
       </c>
       <c r="B24" t="n">
         <v>79847</v>
@@ -3047,10 +3063,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494555</v>
+        <v>494568</v>
       </c>
       <c r="R24" t="n">
-        <v>7023779</v>
+        <v>7023757</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3083,6 +3099,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3109,10 +3130,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122777145</v>
+        <v>122772714</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3125,39 +3146,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494559</v>
+        <v>494589</v>
       </c>
       <c r="R25" t="n">
-        <v>7023653</v>
+        <v>7023675</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3190,11 +3206,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3221,7 +3232,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122772081</v>
+        <v>122773407</v>
       </c>
       <c r="B26" t="n">
         <v>79847</v>
@@ -3261,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494512</v>
+        <v>494790</v>
       </c>
       <c r="R26" t="n">
-        <v>7023641</v>
+        <v>7023741</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3297,6 +3308,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3323,7 +3339,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122771474</v>
+        <v>122774566</v>
       </c>
       <c r="B27" t="n">
         <v>79847</v>
@@ -3357,21 +3373,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494356</v>
+        <v>494563</v>
       </c>
       <c r="R27" t="n">
-        <v>7023575</v>
+        <v>7023786</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,7 +3441,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122774464</v>
+        <v>122774693</v>
       </c>
       <c r="B28" t="n">
         <v>79847</v>
@@ -3464,21 +3475,16 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494570</v>
+        <v>494544</v>
       </c>
       <c r="R28" t="n">
-        <v>7023783</v>
+        <v>7023772</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,7 +3543,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122771384</v>
+        <v>122772290</v>
       </c>
       <c r="B29" t="n">
         <v>79847</v>
@@ -3571,16 +3577,21 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494334</v>
+        <v>494557</v>
       </c>
       <c r="R29" t="n">
-        <v>7023580</v>
+        <v>7023675</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,10 +3650,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122772356</v>
+        <v>122771481</v>
       </c>
       <c r="B30" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3651,25 +3662,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3679,10 +3690,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494558</v>
+        <v>494353</v>
       </c>
       <c r="R30" t="n">
-        <v>7023688</v>
+        <v>7023580</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3715,11 +3726,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3746,7 +3752,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122774777</v>
+        <v>122772081</v>
       </c>
       <c r="B31" t="n">
         <v>79847</v>
@@ -3786,10 +3792,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494582</v>
+        <v>494512</v>
       </c>
       <c r="R31" t="n">
-        <v>7023728</v>
+        <v>7023641</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,11 +3828,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3853,7 +3854,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122771956</v>
+        <v>122772985</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -3898,10 +3899,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494521</v>
+        <v>494655</v>
       </c>
       <c r="R32" t="n">
-        <v>7023591</v>
+        <v>7023708</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,7 +3966,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122771891</v>
+        <v>122772707</v>
       </c>
       <c r="B33" t="n">
         <v>57478</v>
@@ -4010,10 +4011,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494515</v>
+        <v>494582</v>
       </c>
       <c r="R33" t="n">
-        <v>7023580</v>
+        <v>7023673</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4077,10 +4078,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122772874</v>
+        <v>122772994</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4093,27 +4094,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4122,10 +4127,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494680</v>
+        <v>494664</v>
       </c>
       <c r="R34" t="n">
-        <v>7023737</v>
+        <v>7023760</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4184,10 +4189,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122774696</v>
+        <v>122774455</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>91519</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4196,25 +4201,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4224,10 +4229,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494538</v>
+        <v>494571</v>
       </c>
       <c r="R35" t="n">
-        <v>7023761</v>
+        <v>7023780</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4260,11 +4265,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4291,7 +4291,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122771745</v>
+        <v>122774372</v>
       </c>
       <c r="B36" t="n">
         <v>79847</v>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494449</v>
+        <v>494839</v>
       </c>
       <c r="R36" t="n">
-        <v>7023602</v>
+        <v>7023830</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122773319</v>
+        <v>122774393</v>
       </c>
       <c r="B37" t="n">
-        <v>90963</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4405,25 +4405,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494758</v>
+        <v>494710</v>
       </c>
       <c r="R37" t="n">
-        <v>7023767</v>
+        <v>7023786</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4495,10 +4495,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122772714</v>
+        <v>122770429</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4511,34 +4511,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494589</v>
+        <v>493992</v>
       </c>
       <c r="R38" t="n">
-        <v>7023675</v>
+        <v>7023434</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4571,6 +4576,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4597,10 +4607,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122771901</v>
+        <v>122774828</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4613,39 +4623,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494516</v>
+        <v>494562</v>
       </c>
       <c r="R39" t="n">
-        <v>7023586</v>
+        <v>7023728</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,11 +4683,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4709,7 +4709,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122770429</v>
+        <v>122771891</v>
       </c>
       <c r="B40" t="n">
         <v>57478</v>
@@ -4750,14 +4750,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493992</v>
+        <v>494515</v>
       </c>
       <c r="R40" t="n">
-        <v>7023434</v>
+        <v>7023580</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4821,10 +4821,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122771661</v>
+        <v>122777145</v>
       </c>
       <c r="B41" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4833,38 +4833,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494425</v>
+        <v>494559</v>
       </c>
       <c r="R41" t="n">
-        <v>7023600</v>
+        <v>7023653</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4897,6 +4902,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4923,7 +4933,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122772030</v>
+        <v>122774464</v>
       </c>
       <c r="B42" t="n">
         <v>79847</v>
@@ -4957,16 +4967,21 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494526</v>
+        <v>494570</v>
       </c>
       <c r="R42" t="n">
-        <v>7023606</v>
+        <v>7023783</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,10 +5040,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122774455</v>
+        <v>122774597</v>
       </c>
       <c r="B43" t="n">
-        <v>91519</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5037,25 +5052,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5065,10 +5080,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494571</v>
+        <v>494556</v>
       </c>
       <c r="R43" t="n">
-        <v>7023780</v>
+        <v>7023778</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5127,7 +5142,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122774566</v>
+        <v>122772030</v>
       </c>
       <c r="B44" t="n">
         <v>79847</v>
@@ -5167,10 +5182,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494563</v>
+        <v>494526</v>
       </c>
       <c r="R44" t="n">
-        <v>7023786</v>
+        <v>7023606</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,10 +5244,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122773527</v>
+        <v>122773216</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5245,27 +5260,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5274,10 +5289,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494802</v>
+        <v>494716</v>
       </c>
       <c r="R45" t="n">
-        <v>7023657</v>
+        <v>7023730</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5310,11 +5325,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5341,7 +5351,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122774764</v>
+        <v>122774670</v>
       </c>
       <c r="B46" t="n">
         <v>79847</v>
@@ -5381,10 +5391,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494568</v>
+        <v>494555</v>
       </c>
       <c r="R46" t="n">
-        <v>7023757</v>
+        <v>7023779</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5417,11 +5427,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5448,7 +5453,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122772290</v>
+        <v>122773088</v>
       </c>
       <c r="B47" t="n">
         <v>79847</v>
@@ -5493,10 +5498,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494557</v>
+        <v>494700</v>
       </c>
       <c r="R47" t="n">
-        <v>7023675</v>
+        <v>7023729</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5555,7 +5560,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122774828</v>
+        <v>122774715</v>
       </c>
       <c r="B48" t="n">
         <v>79847</v>
@@ -5595,10 +5600,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494562</v>
+        <v>494547</v>
       </c>
       <c r="R48" t="n">
-        <v>7023728</v>
+        <v>7023756</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5657,10 +5662,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122773088</v>
+        <v>122770882</v>
       </c>
       <c r="B49" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5673,39 +5678,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494700</v>
+        <v>494160</v>
       </c>
       <c r="R49" t="n">
-        <v>7023729</v>
+        <v>7023595</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5764,10 +5764,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122774597</v>
+        <v>122774987</v>
       </c>
       <c r="B50" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5780,34 +5780,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494556</v>
+        <v>494357</v>
       </c>
       <c r="R50" t="n">
-        <v>7023778</v>
+        <v>7023735</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5840,6 +5845,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5866,10 +5876,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122773216</v>
+        <v>122771661</v>
       </c>
       <c r="B51" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5878,43 +5888,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494716</v>
+        <v>494425</v>
       </c>
       <c r="R51" t="n">
-        <v>7023730</v>
+        <v>7023600</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5973,7 +5978,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122774372</v>
+        <v>122771384</v>
       </c>
       <c r="B52" t="n">
         <v>79847</v>
@@ -6013,10 +6018,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494839</v>
+        <v>494334</v>
       </c>
       <c r="R52" t="n">
-        <v>7023830</v>
+        <v>7023580</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6075,7 +6080,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122774538</v>
+        <v>122772044</v>
       </c>
       <c r="B53" t="n">
         <v>79847</v>
@@ -6109,21 +6114,16 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494563</v>
+        <v>494524</v>
       </c>
       <c r="R53" t="n">
-        <v>7023781</v>
+        <v>7023624</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6182,10 +6182,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122771655</v>
+        <v>122773319</v>
       </c>
       <c r="B54" t="n">
-        <v>79847</v>
+        <v>90963</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6194,25 +6194,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494427</v>
+        <v>494758</v>
       </c>
       <c r="R54" t="n">
-        <v>7023595</v>
+        <v>7023767</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6284,10 +6284,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122791151</v>
+        <v>122790839</v>
       </c>
       <c r="B55" t="n">
-        <v>79847</v>
+        <v>91640</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6296,43 +6296,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494727</v>
+        <v>494767</v>
       </c>
       <c r="R55" t="n">
-        <v>7023818</v>
+        <v>7023761</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6391,7 +6386,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122790452</v>
+        <v>122791151</v>
       </c>
       <c r="B56" t="n">
         <v>79847</v>
@@ -6436,10 +6431,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494479</v>
+        <v>494727</v>
       </c>
       <c r="R56" t="n">
-        <v>7023680</v>
+        <v>7023818</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6498,7 +6493,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122790289</v>
+        <v>122789892</v>
       </c>
       <c r="B57" t="n">
         <v>79847</v>
@@ -6538,10 +6533,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494551</v>
+        <v>494409</v>
       </c>
       <c r="R57" t="n">
-        <v>7023731</v>
+        <v>7023573</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6574,11 +6569,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6605,10 +6595,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122791209</v>
+        <v>122790194</v>
       </c>
       <c r="B58" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6621,34 +6611,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494707</v>
+        <v>494560</v>
       </c>
       <c r="R58" t="n">
-        <v>7023829</v>
+        <v>7023660</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6681,6 +6676,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6707,10 +6707,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122790826</v>
+        <v>122790286</v>
       </c>
       <c r="B59" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6723,21 +6723,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494767</v>
+        <v>494551</v>
       </c>
       <c r="R59" t="n">
-        <v>7023760</v>
+        <v>7023728</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6783,6 +6783,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6809,10 +6814,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122790839</v>
+        <v>122789784</v>
       </c>
       <c r="B60" t="n">
-        <v>91640</v>
+        <v>56680</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6821,38 +6826,47 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3298</v>
+        <v>102612</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494767</v>
+        <v>494225</v>
       </c>
       <c r="R60" t="n">
-        <v>7023761</v>
+        <v>7023525</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6911,7 +6925,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122791391</v>
+        <v>122790452</v>
       </c>
       <c r="B61" t="n">
         <v>79847</v>
@@ -6945,16 +6959,21 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494717</v>
+        <v>494479</v>
       </c>
       <c r="R61" t="n">
-        <v>7023829</v>
+        <v>7023680</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7013,7 +7032,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122789892</v>
+        <v>122790826</v>
       </c>
       <c r="B62" t="n">
         <v>79847</v>
@@ -7053,10 +7072,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494409</v>
+        <v>494767</v>
       </c>
       <c r="R62" t="n">
-        <v>7023573</v>
+        <v>7023760</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7115,10 +7134,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122789784</v>
+        <v>122789797</v>
       </c>
       <c r="B63" t="n">
-        <v>56680</v>
+        <v>57494</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7131,16 +7150,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7153,6 +7172,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -7164,10 +7193,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494225</v>
+        <v>494329</v>
       </c>
       <c r="R63" t="n">
-        <v>7023525</v>
+        <v>7023594</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7226,7 +7255,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122790286</v>
+        <v>122791209</v>
       </c>
       <c r="B64" t="n">
         <v>79848</v>
@@ -7266,10 +7295,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494551</v>
+        <v>494707</v>
       </c>
       <c r="R64" t="n">
-        <v>7023728</v>
+        <v>7023829</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7302,11 +7331,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7333,10 +7357,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122789797</v>
+        <v>122790289</v>
       </c>
       <c r="B65" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7349,53 +7373,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494329</v>
+        <v>494551</v>
       </c>
       <c r="R65" t="n">
-        <v>7023594</v>
+        <v>7023731</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7428,6 +7433,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7454,10 +7464,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122790194</v>
+        <v>122791391</v>
       </c>
       <c r="B66" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7470,39 +7480,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494560</v>
+        <v>494717</v>
       </c>
       <c r="R66" t="n">
-        <v>7023660</v>
+        <v>7023829</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7535,11 +7540,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -4189,10 +4189,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122774455</v>
+        <v>122770429</v>
       </c>
       <c r="B35" t="n">
-        <v>91519</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4201,38 +4201,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494571</v>
+        <v>493992</v>
       </c>
       <c r="R35" t="n">
-        <v>7023780</v>
+        <v>7023434</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4265,6 +4270,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4495,10 +4505,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122770429</v>
+        <v>122774455</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>91519</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4507,43 +4517,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493992</v>
+        <v>494571</v>
       </c>
       <c r="R38" t="n">
-        <v>7023434</v>
+        <v>7023780</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4576,11 +4581,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -6493,10 +6493,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122789892</v>
+        <v>122790194</v>
       </c>
       <c r="B57" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6509,34 +6509,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494409</v>
+        <v>494560</v>
       </c>
       <c r="R57" t="n">
-        <v>7023573</v>
+        <v>7023660</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6569,6 +6574,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6595,10 +6605,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122790194</v>
+        <v>122789892</v>
       </c>
       <c r="B58" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6611,39 +6621,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494560</v>
+        <v>494409</v>
       </c>
       <c r="R58" t="n">
-        <v>7023660</v>
+        <v>7023573</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6676,11 +6681,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -1856,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122771667</v>
+        <v>122773465</v>
       </c>
       <c r="B13" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,38 +1868,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494425</v>
+        <v>494786</v>
       </c>
       <c r="R13" t="n">
-        <v>7023600</v>
+        <v>7023741</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1958,7 +1963,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122773465</v>
+        <v>122772356</v>
       </c>
       <c r="B14" t="n">
         <v>79847</v>
@@ -1992,21 +1997,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494786</v>
+        <v>494558</v>
       </c>
       <c r="R14" t="n">
-        <v>7023741</v>
+        <v>7023688</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,6 +2039,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2065,10 +2070,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122772356</v>
+        <v>122774563</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2081,21 +2086,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2105,10 +2110,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494558</v>
+        <v>494563</v>
       </c>
       <c r="R15" t="n">
-        <v>7023688</v>
+        <v>7023786</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,11 +2146,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2172,10 +2172,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122774563</v>
+        <v>122771667</v>
       </c>
       <c r="B16" t="n">
-        <v>79848</v>
+        <v>79807</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2184,25 +2184,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494563</v>
+        <v>494425</v>
       </c>
       <c r="R16" t="n">
-        <v>7023786</v>
+        <v>7023600</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -1856,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773465</v>
+        <v>122771667</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,43 +1868,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494786</v>
+        <v>494425</v>
       </c>
       <c r="R13" t="n">
-        <v>7023741</v>
+        <v>7023600</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,7 +1958,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122772356</v>
+        <v>122773465</v>
       </c>
       <c r="B14" t="n">
         <v>79847</v>
@@ -1997,16 +1992,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494558</v>
+        <v>494786</v>
       </c>
       <c r="R14" t="n">
-        <v>7023688</v>
+        <v>7023741</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,11 +2039,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2070,10 +2065,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122774563</v>
+        <v>122772356</v>
       </c>
       <c r="B15" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2086,21 +2081,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2110,10 +2105,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494563</v>
+        <v>494558</v>
       </c>
       <c r="R15" t="n">
-        <v>7023786</v>
+        <v>7023688</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,6 +2141,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2172,10 +2172,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122771667</v>
+        <v>122774563</v>
       </c>
       <c r="B16" t="n">
-        <v>79807</v>
+        <v>79848</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2184,25 +2184,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494425</v>
+        <v>494563</v>
       </c>
       <c r="R16" t="n">
-        <v>7023600</v>
+        <v>7023786</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -4189,10 +4189,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122770429</v>
+        <v>122774372</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4205,39 +4205,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493992</v>
+        <v>494839</v>
       </c>
       <c r="R35" t="n">
-        <v>7023434</v>
+        <v>7023830</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4270,11 +4265,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4301,7 +4291,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122774372</v>
+        <v>122774393</v>
       </c>
       <c r="B36" t="n">
         <v>79847</v>
@@ -4341,10 +4331,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494839</v>
+        <v>494710</v>
       </c>
       <c r="R36" t="n">
-        <v>7023830</v>
+        <v>7023786</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4403,10 +4393,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122774393</v>
+        <v>122774455</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>91519</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4415,25 +4405,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4443,10 +4433,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494710</v>
+        <v>494571</v>
       </c>
       <c r="R37" t="n">
-        <v>7023786</v>
+        <v>7023780</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4505,10 +4495,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122774455</v>
+        <v>122770429</v>
       </c>
       <c r="B38" t="n">
-        <v>91519</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4517,38 +4507,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494571</v>
+        <v>493992</v>
       </c>
       <c r="R38" t="n">
-        <v>7023780</v>
+        <v>7023434</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4581,6 +4576,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122774777</v>
+        <v>122771745</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494582</v>
+        <v>494449</v>
       </c>
       <c r="R2" t="n">
-        <v>7023728</v>
+        <v>7023602</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122773458</v>
+        <v>122770882</v>
       </c>
       <c r="B3" t="n">
-        <v>79848</v>
+        <v>90973</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494786</v>
+        <v>494160</v>
       </c>
       <c r="R3" t="n">
-        <v>7023741</v>
+        <v>7023595</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122772531</v>
+        <v>122771901</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494557</v>
+        <v>494516</v>
       </c>
       <c r="R4" t="n">
-        <v>7023650</v>
+        <v>7023586</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122770929</v>
+        <v>122774828</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>79850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,48 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494181</v>
+        <v>494562</v>
       </c>
       <c r="R5" t="n">
-        <v>7023603</v>
+        <v>7023728</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122772874</v>
+        <v>122772994</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>57634</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,27 +1109,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1157,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494680</v>
+        <v>494664</v>
       </c>
       <c r="R6" t="n">
-        <v>7023737</v>
+        <v>7023760</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122774696</v>
+        <v>122771384</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494538</v>
+        <v>494334</v>
       </c>
       <c r="R7" t="n">
-        <v>7023761</v>
+        <v>7023580</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,11 +1280,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122772729</v>
+        <v>122772356</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,39 +1322,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494591</v>
+        <v>494558</v>
       </c>
       <c r="R8" t="n">
-        <v>7023673</v>
+        <v>7023688</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,7 +1386,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122772413</v>
+        <v>122771891</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,34 +1429,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494559</v>
+        <v>494515</v>
       </c>
       <c r="R9" t="n">
-        <v>7023689</v>
+        <v>7023580</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,6 +1494,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122774745</v>
+        <v>122773407</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494558</v>
+        <v>494790</v>
       </c>
       <c r="R10" t="n">
-        <v>7023767</v>
+        <v>7023741</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,6 +1601,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1642,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122771655</v>
+        <v>122772729</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,34 +1648,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494427</v>
+        <v>494591</v>
       </c>
       <c r="R11" t="n">
-        <v>7023595</v>
+        <v>7023673</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,6 +1713,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122773527</v>
+        <v>122774670</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,39 +1760,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494802</v>
+        <v>494555</v>
       </c>
       <c r="R12" t="n">
-        <v>7023657</v>
+        <v>7023779</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,11 +1820,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122771667</v>
+        <v>122772874</v>
       </c>
       <c r="B13" t="n">
-        <v>79807</v>
+        <v>79850</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,38 +1858,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494425</v>
+        <v>494680</v>
       </c>
       <c r="R13" t="n">
-        <v>7023600</v>
+        <v>7023737</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1958,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122773465</v>
+        <v>122774455</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>91522</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,43 +1965,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494786</v>
+        <v>494571</v>
       </c>
       <c r="R14" t="n">
-        <v>7023741</v>
+        <v>7023780</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2065,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122772356</v>
+        <v>122774987</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2081,34 +2071,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494558</v>
+        <v>494357</v>
       </c>
       <c r="R15" t="n">
-        <v>7023688</v>
+        <v>7023735</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,7 +2140,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2172,10 +2167,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122774563</v>
+        <v>122772081</v>
       </c>
       <c r="B16" t="n">
-        <v>79848</v>
+        <v>79850</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2188,21 +2183,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2212,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494563</v>
+        <v>494512</v>
       </c>
       <c r="R16" t="n">
-        <v>7023786</v>
+        <v>7023641</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,10 +2269,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122771489</v>
+        <v>122774597</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2290,34 +2285,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494147</v>
+        <v>494556</v>
       </c>
       <c r="R17" t="n">
-        <v>7023571</v>
+        <v>7023778</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122771956</v>
+        <v>122772413</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2392,39 +2387,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494521</v>
+        <v>494559</v>
       </c>
       <c r="R18" t="n">
-        <v>7023591</v>
+        <v>7023689</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,11 +2447,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2488,10 +2473,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122771901</v>
+        <v>122771667</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>79810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,43 +2485,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494516</v>
+        <v>494425</v>
       </c>
       <c r="R19" t="n">
-        <v>7023586</v>
+        <v>7023600</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,11 +2549,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2600,10 +2575,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122774538</v>
+        <v>122774372</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2634,21 +2609,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494563</v>
+        <v>494839</v>
       </c>
       <c r="R20" t="n">
-        <v>7023781</v>
+        <v>7023830</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2707,10 +2677,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122773254</v>
+        <v>122770929</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>57634</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2723,39 +2693,48 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494730</v>
+        <v>494181</v>
       </c>
       <c r="R21" t="n">
-        <v>7023730</v>
+        <v>7023603</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2814,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122771474</v>
+        <v>122771489</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2830,39 +2809,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494356</v>
+        <v>494147</v>
       </c>
       <c r="R22" t="n">
-        <v>7023575</v>
+        <v>7023571</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2921,10 +2895,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122771745</v>
+        <v>122774393</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2961,10 +2935,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494449</v>
+        <v>494710</v>
       </c>
       <c r="R23" t="n">
-        <v>7023602</v>
+        <v>7023786</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3023,10 +2997,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122774764</v>
+        <v>122771956</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3039,34 +3013,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494568</v>
+        <v>494521</v>
       </c>
       <c r="R24" t="n">
-        <v>7023757</v>
+        <v>7023591</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3103,7 +3082,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3130,10 +3109,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122772714</v>
+        <v>122772030</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3170,10 +3149,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494589</v>
+        <v>494526</v>
       </c>
       <c r="R25" t="n">
-        <v>7023675</v>
+        <v>7023606</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3232,10 +3211,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122773407</v>
+        <v>122770429</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3248,34 +3227,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494790</v>
+        <v>493992</v>
       </c>
       <c r="R26" t="n">
-        <v>7023741</v>
+        <v>7023434</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3312,7 +3296,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3339,10 +3323,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122774566</v>
+        <v>122773458</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>79851</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3355,21 +3339,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3379,10 +3363,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494563</v>
+        <v>494786</v>
       </c>
       <c r="R27" t="n">
-        <v>7023786</v>
+        <v>7023741</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122774693</v>
+        <v>122774464</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3475,16 +3459,21 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494544</v>
+        <v>494570</v>
       </c>
       <c r="R28" t="n">
-        <v>7023772</v>
+        <v>7023783</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3543,10 +3532,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122772290</v>
+        <v>122774566</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3577,21 +3566,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494557</v>
+        <v>494563</v>
       </c>
       <c r="R29" t="n">
-        <v>7023675</v>
+        <v>7023786</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3650,10 +3634,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122771481</v>
+        <v>122774693</v>
       </c>
       <c r="B30" t="n">
-        <v>79883</v>
+        <v>79850</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3662,25 +3646,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3690,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494353</v>
+        <v>494544</v>
       </c>
       <c r="R30" t="n">
-        <v>7023580</v>
+        <v>7023772</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3752,10 +3736,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122772081</v>
+        <v>122774715</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3792,10 +3776,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494512</v>
+        <v>494547</v>
       </c>
       <c r="R31" t="n">
-        <v>7023641</v>
+        <v>7023756</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3854,10 +3838,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122772985</v>
+        <v>122772044</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3870,39 +3854,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494655</v>
+        <v>494524</v>
       </c>
       <c r="R32" t="n">
-        <v>7023708</v>
+        <v>7023624</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3935,11 +3914,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3966,10 +3940,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122772707</v>
+        <v>122774563</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>79851</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3982,39 +3956,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494582</v>
+        <v>494563</v>
       </c>
       <c r="R33" t="n">
-        <v>7023673</v>
+        <v>7023786</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4047,11 +4016,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4078,10 +4042,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122772994</v>
+        <v>122772290</v>
       </c>
       <c r="B34" t="n">
-        <v>57631</v>
+        <v>79850</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4094,31 +4058,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4127,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494664</v>
+        <v>494557</v>
       </c>
       <c r="R34" t="n">
-        <v>7023760</v>
+        <v>7023675</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4189,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122774372</v>
+        <v>122773254</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4223,16 +4183,21 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494839</v>
+        <v>494730</v>
       </c>
       <c r="R35" t="n">
-        <v>7023830</v>
+        <v>7023730</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4291,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122774393</v>
+        <v>122774777</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4331,10 +4296,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494710</v>
+        <v>494582</v>
       </c>
       <c r="R36" t="n">
-        <v>7023786</v>
+        <v>7023728</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4367,6 +4332,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4393,10 +4363,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122774455</v>
+        <v>122773319</v>
       </c>
       <c r="B37" t="n">
-        <v>91519</v>
+        <v>90966</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4405,25 +4375,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>760</v>
+        <v>1205</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4433,10 +4403,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494571</v>
+        <v>494758</v>
       </c>
       <c r="R37" t="n">
-        <v>7023780</v>
+        <v>7023767</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4495,10 +4465,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122770429</v>
+        <v>122771655</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4511,39 +4481,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493992</v>
+        <v>494427</v>
       </c>
       <c r="R38" t="n">
-        <v>7023434</v>
+        <v>7023595</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4576,11 +4541,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4607,10 +4567,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122774828</v>
+        <v>122777145</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4623,34 +4583,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494562</v>
+        <v>494559</v>
       </c>
       <c r="R39" t="n">
-        <v>7023728</v>
+        <v>7023653</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4683,6 +4648,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4709,10 +4679,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122771891</v>
+        <v>122773465</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4725,27 +4695,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4754,10 +4724,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494515</v>
+        <v>494786</v>
       </c>
       <c r="R40" t="n">
-        <v>7023580</v>
+        <v>7023741</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4790,11 +4760,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4821,10 +4786,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122777145</v>
+        <v>122774764</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4837,39 +4802,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494559</v>
+        <v>494568</v>
       </c>
       <c r="R41" t="n">
-        <v>7023653</v>
+        <v>7023757</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4906,7 +4866,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4933,10 +4893,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122774464</v>
+        <v>122774696</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4967,21 +4927,16 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494570</v>
+        <v>494538</v>
       </c>
       <c r="R42" t="n">
-        <v>7023783</v>
+        <v>7023761</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5014,6 +4969,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5040,10 +5000,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122774597</v>
+        <v>122771661</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>79879</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5052,25 +5012,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5080,10 +5040,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494556</v>
+        <v>494425</v>
       </c>
       <c r="R43" t="n">
-        <v>7023778</v>
+        <v>7023600</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5142,10 +5102,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122772030</v>
+        <v>122773527</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5158,34 +5118,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494526</v>
+        <v>494802</v>
       </c>
       <c r="R44" t="n">
-        <v>7023606</v>
+        <v>7023657</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5218,6 +5183,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5244,10 +5214,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122773216</v>
+        <v>122772531</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5260,27 +5230,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5289,10 +5259,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494716</v>
+        <v>494557</v>
       </c>
       <c r="R45" t="n">
-        <v>7023730</v>
+        <v>7023650</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5325,6 +5295,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5351,10 +5326,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122774670</v>
+        <v>122774745</v>
       </c>
       <c r="B46" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5391,10 +5366,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494555</v>
+        <v>494558</v>
       </c>
       <c r="R46" t="n">
-        <v>7023779</v>
+        <v>7023767</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5453,10 +5428,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122773088</v>
+        <v>122772714</v>
       </c>
       <c r="B47" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5487,21 +5462,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494700</v>
+        <v>494589</v>
       </c>
       <c r="R47" t="n">
-        <v>7023729</v>
+        <v>7023675</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5560,10 +5530,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122774715</v>
+        <v>122774538</v>
       </c>
       <c r="B48" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5594,16 +5564,21 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494547</v>
+        <v>494563</v>
       </c>
       <c r="R48" t="n">
-        <v>7023756</v>
+        <v>7023781</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5662,10 +5637,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122770882</v>
+        <v>122771481</v>
       </c>
       <c r="B49" t="n">
-        <v>90970</v>
+        <v>79886</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5674,38 +5649,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494160</v>
+        <v>494353</v>
       </c>
       <c r="R49" t="n">
-        <v>7023595</v>
+        <v>7023580</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5764,10 +5739,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122774987</v>
+        <v>122771474</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5780,27 +5755,27 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5809,10 +5784,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494357</v>
+        <v>494356</v>
       </c>
       <c r="R50" t="n">
-        <v>7023735</v>
+        <v>7023575</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5845,11 +5820,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5876,10 +5846,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122771661</v>
+        <v>122773088</v>
       </c>
       <c r="B51" t="n">
-        <v>79876</v>
+        <v>79850</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5888,38 +5858,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494425</v>
+        <v>494700</v>
       </c>
       <c r="R51" t="n">
-        <v>7023600</v>
+        <v>7023729</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5978,10 +5953,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122771384</v>
+        <v>122773216</v>
       </c>
       <c r="B52" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6012,16 +5987,21 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494334</v>
+        <v>494716</v>
       </c>
       <c r="R52" t="n">
-        <v>7023580</v>
+        <v>7023730</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6080,10 +6060,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122772044</v>
+        <v>122772985</v>
       </c>
       <c r="B53" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6096,34 +6076,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494524</v>
+        <v>494655</v>
       </c>
       <c r="R53" t="n">
-        <v>7023624</v>
+        <v>7023708</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6156,6 +6141,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6182,10 +6172,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122773319</v>
+        <v>122772707</v>
       </c>
       <c r="B54" t="n">
-        <v>90963</v>
+        <v>57481</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6194,38 +6184,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494758</v>
+        <v>494582</v>
       </c>
       <c r="R54" t="n">
-        <v>7023767</v>
+        <v>7023673</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6258,6 +6253,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6284,10 +6284,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122790839</v>
+        <v>122789784</v>
       </c>
       <c r="B55" t="n">
-        <v>91640</v>
+        <v>56683</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6296,38 +6296,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494767</v>
+        <v>494225</v>
       </c>
       <c r="R55" t="n">
-        <v>7023761</v>
+        <v>7023525</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6386,10 +6395,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122791151</v>
+        <v>122790839</v>
       </c>
       <c r="B56" t="n">
-        <v>79847</v>
+        <v>91643</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6398,43 +6407,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494727</v>
+        <v>494767</v>
       </c>
       <c r="R56" t="n">
-        <v>7023818</v>
+        <v>7023761</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6493,10 +6497,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122790194</v>
+        <v>122791209</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
+        <v>79851</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6509,39 +6513,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494560</v>
+        <v>494707</v>
       </c>
       <c r="R57" t="n">
-        <v>7023660</v>
+        <v>7023829</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6574,11 +6573,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6605,10 +6599,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122789892</v>
+        <v>122790194</v>
       </c>
       <c r="B58" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6621,34 +6615,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494409</v>
+        <v>494560</v>
       </c>
       <c r="R58" t="n">
-        <v>7023573</v>
+        <v>7023660</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6681,6 +6680,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6707,10 +6711,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122790286</v>
+        <v>122790452</v>
       </c>
       <c r="B59" t="n">
-        <v>79848</v>
+        <v>79850</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6723,34 +6727,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494551</v>
+        <v>494479</v>
       </c>
       <c r="R59" t="n">
-        <v>7023728</v>
+        <v>7023680</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6783,11 +6792,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6814,10 +6818,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122789784</v>
+        <v>122790289</v>
       </c>
       <c r="B60" t="n">
-        <v>56680</v>
+        <v>79850</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6830,43 +6834,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494225</v>
+        <v>494551</v>
       </c>
       <c r="R60" t="n">
-        <v>7023525</v>
+        <v>7023731</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6899,6 +6894,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6925,10 +6925,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122790452</v>
+        <v>122790286</v>
       </c>
       <c r="B61" t="n">
-        <v>79847</v>
+        <v>79851</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6941,39 +6941,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494479</v>
+        <v>494551</v>
       </c>
       <c r="R61" t="n">
-        <v>7023680</v>
+        <v>7023728</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7006,6 +7001,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7032,10 +7032,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122790826</v>
+        <v>122791171</v>
       </c>
       <c r="B62" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494767</v>
+        <v>494727</v>
       </c>
       <c r="R62" t="n">
-        <v>7023760</v>
+        <v>7023818</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7108,6 +7108,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7134,10 +7139,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122789797</v>
+        <v>122790826</v>
       </c>
       <c r="B63" t="n">
-        <v>57494</v>
+        <v>79850</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7150,53 +7155,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494329</v>
+        <v>494767</v>
       </c>
       <c r="R63" t="n">
-        <v>7023594</v>
+        <v>7023760</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7255,10 +7241,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122791209</v>
+        <v>122789797</v>
       </c>
       <c r="B64" t="n">
-        <v>79848</v>
+        <v>57497</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7271,34 +7257,53 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494707</v>
+        <v>494329</v>
       </c>
       <c r="R64" t="n">
-        <v>7023829</v>
+        <v>7023594</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7357,10 +7362,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122790289</v>
+        <v>122789892</v>
       </c>
       <c r="B65" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7397,10 +7402,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494551</v>
+        <v>494409</v>
       </c>
       <c r="R65" t="n">
-        <v>7023731</v>
+        <v>7023573</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7433,11 +7438,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7467,7 +7467,7 @@
         <v>122791391</v>
       </c>
       <c r="B66" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>122773452</v>
       </c>
       <c r="B67" t="n">
-        <v>57428</v>
+        <v>57431</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122771745</v>
+        <v>122774372</v>
       </c>
       <c r="B2" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494449</v>
+        <v>494839</v>
       </c>
       <c r="R2" t="n">
-        <v>7023602</v>
+        <v>7023830</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122770882</v>
+        <v>122774455</v>
       </c>
       <c r="B3" t="n">
-        <v>90973</v>
+        <v>91524</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494160</v>
+        <v>494571</v>
       </c>
       <c r="R3" t="n">
-        <v>7023595</v>
+        <v>7023780</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122771901</v>
+        <v>122774987</v>
       </c>
       <c r="B4" t="n">
         <v>57481</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494516</v>
+        <v>494357</v>
       </c>
       <c r="R4" t="n">
-        <v>7023586</v>
+        <v>7023735</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122774828</v>
+        <v>122774670</v>
       </c>
       <c r="B5" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494562</v>
+        <v>494555</v>
       </c>
       <c r="R5" t="n">
-        <v>7023728</v>
+        <v>7023779</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122772994</v>
+        <v>122774764</v>
       </c>
       <c r="B6" t="n">
-        <v>57634</v>
+        <v>79852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,43 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494664</v>
+        <v>494568</v>
       </c>
       <c r="R6" t="n">
-        <v>7023760</v>
+        <v>7023757</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122771384</v>
+        <v>122772874</v>
       </c>
       <c r="B7" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,16 +1234,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494334</v>
+        <v>494680</v>
       </c>
       <c r="R7" t="n">
-        <v>7023580</v>
+        <v>7023737</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122772356</v>
+        <v>122774566</v>
       </c>
       <c r="B8" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1346,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494558</v>
+        <v>494563</v>
       </c>
       <c r="R8" t="n">
-        <v>7023688</v>
+        <v>7023786</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,11 +1383,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122771891</v>
+        <v>122772729</v>
       </c>
       <c r="B9" t="n">
         <v>57481</v>
@@ -1458,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494515</v>
+        <v>494591</v>
       </c>
       <c r="R9" t="n">
-        <v>7023580</v>
+        <v>7023673</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773407</v>
+        <v>122772707</v>
       </c>
       <c r="B10" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,34 +1537,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494790</v>
+        <v>494582</v>
       </c>
       <c r="R10" t="n">
-        <v>7023741</v>
+        <v>7023673</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1605,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122772729</v>
+        <v>122772994</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>57634</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,27 +1649,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1677,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494591</v>
+        <v>494664</v>
       </c>
       <c r="R11" t="n">
-        <v>7023673</v>
+        <v>7023760</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,11 +1718,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122774670</v>
+        <v>122773088</v>
       </c>
       <c r="B12" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1778,16 +1778,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494555</v>
+        <v>494700</v>
       </c>
       <c r="R12" t="n">
-        <v>7023779</v>
+        <v>7023729</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122772874</v>
+        <v>122772356</v>
       </c>
       <c r="B13" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1880,21 +1885,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494680</v>
+        <v>494558</v>
       </c>
       <c r="R13" t="n">
-        <v>7023737</v>
+        <v>7023688</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,6 +1927,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1953,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122774455</v>
+        <v>122774828</v>
       </c>
       <c r="B14" t="n">
-        <v>91522</v>
+        <v>79852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,25 +1970,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1993,10 +1998,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494571</v>
+        <v>494562</v>
       </c>
       <c r="R14" t="n">
-        <v>7023780</v>
+        <v>7023728</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122774987</v>
+        <v>122771655</v>
       </c>
       <c r="B15" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2071,39 +2076,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494357</v>
+        <v>494427</v>
       </c>
       <c r="R15" t="n">
-        <v>7023735</v>
+        <v>7023595</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,11 +2136,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2167,10 +2162,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122772081</v>
+        <v>122774393</v>
       </c>
       <c r="B16" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494512</v>
+        <v>494710</v>
       </c>
       <c r="R16" t="n">
-        <v>7023641</v>
+        <v>7023786</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122774597</v>
+        <v>122774464</v>
       </c>
       <c r="B17" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2303,16 +2298,21 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494556</v>
+        <v>494570</v>
       </c>
       <c r="R17" t="n">
-        <v>7023778</v>
+        <v>7023783</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122772413</v>
+        <v>122774715</v>
       </c>
       <c r="B18" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494559</v>
+        <v>494547</v>
       </c>
       <c r="R18" t="n">
-        <v>7023689</v>
+        <v>7023756</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2473,10 +2473,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122771667</v>
+        <v>122774597</v>
       </c>
       <c r="B19" t="n">
-        <v>79810</v>
+        <v>79852</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,25 +2485,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2513,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494425</v>
+        <v>494556</v>
       </c>
       <c r="R19" t="n">
-        <v>7023600</v>
+        <v>7023778</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122774372</v>
+        <v>122771489</v>
       </c>
       <c r="B20" t="n">
-        <v>79850</v>
+        <v>78771</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2591,34 +2591,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494839</v>
+        <v>494147</v>
       </c>
       <c r="R20" t="n">
-        <v>7023830</v>
+        <v>7023571</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2677,10 +2677,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122770929</v>
+        <v>122774777</v>
       </c>
       <c r="B21" t="n">
-        <v>57634</v>
+        <v>79852</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2693,48 +2693,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494181</v>
+        <v>494582</v>
       </c>
       <c r="R21" t="n">
-        <v>7023603</v>
+        <v>7023728</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2767,6 +2753,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2793,10 +2784,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122771489</v>
+        <v>122777145</v>
       </c>
       <c r="B22" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,34 +2800,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494147</v>
+        <v>494559</v>
       </c>
       <c r="R22" t="n">
-        <v>7023571</v>
+        <v>7023653</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2869,6 +2865,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2895,10 +2896,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122774393</v>
+        <v>122773458</v>
       </c>
       <c r="B23" t="n">
-        <v>79850</v>
+        <v>79853</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2911,21 +2912,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2935,10 +2936,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494710</v>
+        <v>494786</v>
       </c>
       <c r="R23" t="n">
-        <v>7023786</v>
+        <v>7023741</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,7 +2998,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122771956</v>
+        <v>122771901</v>
       </c>
       <c r="B24" t="n">
         <v>57481</v>
@@ -3042,10 +3043,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494521</v>
+        <v>494516</v>
       </c>
       <c r="R24" t="n">
-        <v>7023591</v>
+        <v>7023586</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,10 +3110,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122772030</v>
+        <v>122772081</v>
       </c>
       <c r="B25" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3149,10 +3150,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494526</v>
+        <v>494512</v>
       </c>
       <c r="R25" t="n">
-        <v>7023606</v>
+        <v>7023641</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3211,10 +3212,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122770429</v>
+        <v>122774745</v>
       </c>
       <c r="B26" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3227,39 +3228,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493992</v>
+        <v>494558</v>
       </c>
       <c r="R26" t="n">
-        <v>7023434</v>
+        <v>7023767</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3292,11 +3288,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3323,10 +3314,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122773458</v>
+        <v>122771661</v>
       </c>
       <c r="B27" t="n">
-        <v>79851</v>
+        <v>79881</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3335,25 +3326,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3363,10 +3354,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494786</v>
+        <v>494425</v>
       </c>
       <c r="R27" t="n">
-        <v>7023741</v>
+        <v>7023600</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,10 +3416,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122774464</v>
+        <v>122772985</v>
       </c>
       <c r="B28" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3441,27 +3432,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3470,10 +3461,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494570</v>
+        <v>494655</v>
       </c>
       <c r="R28" t="n">
-        <v>7023783</v>
+        <v>7023708</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3506,6 +3497,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,10 +3528,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122774566</v>
+        <v>122774538</v>
       </c>
       <c r="B29" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3566,6 +3562,11 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
@@ -3575,7 +3576,7 @@
         <v>494563</v>
       </c>
       <c r="R29" t="n">
-        <v>7023786</v>
+        <v>7023781</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,10 +3635,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122774693</v>
+        <v>122771474</v>
       </c>
       <c r="B30" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3668,16 +3669,21 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494544</v>
+        <v>494356</v>
       </c>
       <c r="R30" t="n">
-        <v>7023772</v>
+        <v>7023575</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,10 +3742,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122774715</v>
+        <v>122772044</v>
       </c>
       <c r="B31" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3776,10 +3782,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494547</v>
+        <v>494524</v>
       </c>
       <c r="R31" t="n">
-        <v>7023756</v>
+        <v>7023624</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,10 +3844,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122772044</v>
+        <v>122773319</v>
       </c>
       <c r="B32" t="n">
-        <v>79850</v>
+        <v>90968</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3850,25 +3856,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3878,10 +3884,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494524</v>
+        <v>494758</v>
       </c>
       <c r="R32" t="n">
-        <v>7023624</v>
+        <v>7023767</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3940,10 +3946,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122774563</v>
+        <v>122771481</v>
       </c>
       <c r="B33" t="n">
-        <v>79851</v>
+        <v>79888</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3952,25 +3958,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3980,10 +3986,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494563</v>
+        <v>494353</v>
       </c>
       <c r="R33" t="n">
-        <v>7023786</v>
+        <v>7023580</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4042,10 +4048,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122772290</v>
+        <v>122773407</v>
       </c>
       <c r="B34" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4076,21 +4082,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494557</v>
+        <v>494790</v>
       </c>
       <c r="R34" t="n">
-        <v>7023675</v>
+        <v>7023741</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4123,6 +4124,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4149,10 +4155,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122773254</v>
+        <v>122773527</v>
       </c>
       <c r="B35" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4165,27 +4171,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4194,10 +4200,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494730</v>
+        <v>494802</v>
       </c>
       <c r="R35" t="n">
-        <v>7023730</v>
+        <v>7023657</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4230,6 +4236,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4256,10 +4267,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122774777</v>
+        <v>122774563</v>
       </c>
       <c r="B36" t="n">
-        <v>79850</v>
+        <v>79853</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4272,21 +4283,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4296,10 +4307,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494582</v>
+        <v>494563</v>
       </c>
       <c r="R36" t="n">
-        <v>7023728</v>
+        <v>7023786</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4332,11 +4343,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4363,10 +4369,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122773319</v>
+        <v>122770882</v>
       </c>
       <c r="B37" t="n">
-        <v>90966</v>
+        <v>90975</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4375,38 +4381,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1205</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494758</v>
+        <v>494160</v>
       </c>
       <c r="R37" t="n">
-        <v>7023767</v>
+        <v>7023595</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4465,10 +4471,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122771655</v>
+        <v>122773254</v>
       </c>
       <c r="B38" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4499,16 +4505,21 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494427</v>
+        <v>494730</v>
       </c>
       <c r="R38" t="n">
-        <v>7023595</v>
+        <v>7023730</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4567,7 +4578,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122777145</v>
+        <v>122771956</v>
       </c>
       <c r="B39" t="n">
         <v>57481</v>
@@ -4603,7 +4614,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4612,10 +4623,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494559</v>
+        <v>494521</v>
       </c>
       <c r="R39" t="n">
-        <v>7023653</v>
+        <v>7023591</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4679,10 +4690,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122773465</v>
+        <v>122771745</v>
       </c>
       <c r="B40" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4713,21 +4724,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494786</v>
+        <v>494449</v>
       </c>
       <c r="R40" t="n">
-        <v>7023741</v>
+        <v>7023602</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4786,10 +4792,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122774764</v>
+        <v>122772531</v>
       </c>
       <c r="B41" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4802,34 +4808,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494568</v>
+        <v>494557</v>
       </c>
       <c r="R41" t="n">
-        <v>7023757</v>
+        <v>7023650</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4866,7 +4877,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4893,10 +4904,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122774696</v>
+        <v>122772290</v>
       </c>
       <c r="B42" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4927,16 +4938,21 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494538</v>
+        <v>494557</v>
       </c>
       <c r="R42" t="n">
-        <v>7023761</v>
+        <v>7023675</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4969,11 +4985,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5000,10 +5011,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122771661</v>
+        <v>122772030</v>
       </c>
       <c r="B43" t="n">
-        <v>79879</v>
+        <v>79852</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5012,25 +5023,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5040,10 +5051,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494425</v>
+        <v>494526</v>
       </c>
       <c r="R43" t="n">
-        <v>7023600</v>
+        <v>7023606</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5102,10 +5113,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122773527</v>
+        <v>122771384</v>
       </c>
       <c r="B44" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5118,39 +5129,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494802</v>
+        <v>494334</v>
       </c>
       <c r="R44" t="n">
-        <v>7023657</v>
+        <v>7023580</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5183,11 +5189,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5214,10 +5215,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122772531</v>
+        <v>122771667</v>
       </c>
       <c r="B45" t="n">
-        <v>57481</v>
+        <v>79812</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5226,43 +5227,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494557</v>
+        <v>494425</v>
       </c>
       <c r="R45" t="n">
-        <v>7023650</v>
+        <v>7023600</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5295,11 +5291,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5326,10 +5317,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122774745</v>
+        <v>122770929</v>
       </c>
       <c r="B46" t="n">
-        <v>79850</v>
+        <v>57634</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5342,34 +5333,48 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494558</v>
+        <v>494181</v>
       </c>
       <c r="R46" t="n">
-        <v>7023767</v>
+        <v>7023603</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5428,10 +5433,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122772714</v>
+        <v>122773465</v>
       </c>
       <c r="B47" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5462,16 +5467,21 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494589</v>
+        <v>494786</v>
       </c>
       <c r="R47" t="n">
-        <v>7023675</v>
+        <v>7023741</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5530,10 +5540,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122774538</v>
+        <v>122774696</v>
       </c>
       <c r="B48" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5564,21 +5574,16 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494563</v>
+        <v>494538</v>
       </c>
       <c r="R48" t="n">
-        <v>7023781</v>
+        <v>7023761</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5611,6 +5616,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5637,10 +5647,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122771481</v>
+        <v>122774693</v>
       </c>
       <c r="B49" t="n">
-        <v>79886</v>
+        <v>79852</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5649,25 +5659,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5677,10 +5687,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494353</v>
+        <v>494544</v>
       </c>
       <c r="R49" t="n">
-        <v>7023580</v>
+        <v>7023772</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5739,10 +5749,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122771474</v>
+        <v>122773216</v>
       </c>
       <c r="B50" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5784,10 +5794,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494356</v>
+        <v>494716</v>
       </c>
       <c r="R50" t="n">
-        <v>7023575</v>
+        <v>7023730</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5846,10 +5856,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122773088</v>
+        <v>122771891</v>
       </c>
       <c r="B51" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5862,27 +5872,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5891,10 +5901,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494700</v>
+        <v>494515</v>
       </c>
       <c r="R51" t="n">
-        <v>7023729</v>
+        <v>7023580</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5927,6 +5937,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5953,10 +5968,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122773216</v>
+        <v>122770429</v>
       </c>
       <c r="B52" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5969,39 +5984,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494716</v>
+        <v>493992</v>
       </c>
       <c r="R52" t="n">
-        <v>7023730</v>
+        <v>7023434</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6034,6 +6049,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6060,10 +6080,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122772985</v>
+        <v>122772714</v>
       </c>
       <c r="B53" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6076,39 +6096,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494655</v>
+        <v>494589</v>
       </c>
       <c r="R53" t="n">
-        <v>7023708</v>
+        <v>7023675</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6141,11 +6156,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6172,10 +6182,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122772707</v>
+        <v>122772413</v>
       </c>
       <c r="B54" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6188,39 +6198,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494582</v>
+        <v>494559</v>
       </c>
       <c r="R54" t="n">
-        <v>7023673</v>
+        <v>7023689</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6253,11 +6258,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6284,10 +6284,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122789784</v>
+        <v>122790286</v>
       </c>
       <c r="B55" t="n">
-        <v>56683</v>
+        <v>79853</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6300,43 +6300,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494225</v>
+        <v>494551</v>
       </c>
       <c r="R55" t="n">
-        <v>7023525</v>
+        <v>7023728</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6369,6 +6360,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6395,10 +6391,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122790839</v>
+        <v>122791151</v>
       </c>
       <c r="B56" t="n">
-        <v>91643</v>
+        <v>79852</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6407,38 +6403,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494767</v>
+        <v>494727</v>
       </c>
       <c r="R56" t="n">
-        <v>7023761</v>
+        <v>7023818</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6497,10 +6498,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122791209</v>
+        <v>122791391</v>
       </c>
       <c r="B57" t="n">
-        <v>79851</v>
+        <v>79852</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6513,21 +6514,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6537,7 +6538,7 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494707</v>
+        <v>494717</v>
       </c>
       <c r="R57" t="n">
         <v>7023829</v>
@@ -6711,10 +6712,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122790452</v>
+        <v>122790839</v>
       </c>
       <c r="B59" t="n">
-        <v>79850</v>
+        <v>91645</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6723,43 +6724,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494479</v>
+        <v>494767</v>
       </c>
       <c r="R59" t="n">
-        <v>7023680</v>
+        <v>7023761</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6818,10 +6814,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122790289</v>
+        <v>122789784</v>
       </c>
       <c r="B60" t="n">
-        <v>79850</v>
+        <v>56683</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6834,34 +6830,43 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494551</v>
+        <v>494225</v>
       </c>
       <c r="R60" t="n">
-        <v>7023731</v>
+        <v>7023525</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6894,11 +6899,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6925,10 +6925,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122790286</v>
+        <v>122790289</v>
       </c>
       <c r="B61" t="n">
-        <v>79851</v>
+        <v>79852</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6941,21 +6941,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6968,7 +6968,7 @@
         <v>494551</v>
       </c>
       <c r="R61" t="n">
-        <v>7023728</v>
+        <v>7023731</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7032,10 +7032,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122791171</v>
+        <v>122790826</v>
       </c>
       <c r="B62" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494727</v>
+        <v>494767</v>
       </c>
       <c r="R62" t="n">
-        <v>7023818</v>
+        <v>7023760</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7108,11 +7108,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7139,10 +7134,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122790826</v>
+        <v>122790452</v>
       </c>
       <c r="B63" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7173,16 +7168,21 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494767</v>
+        <v>494479</v>
       </c>
       <c r="R63" t="n">
-        <v>7023760</v>
+        <v>7023680</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7241,10 +7241,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122789797</v>
+        <v>122791209</v>
       </c>
       <c r="B64" t="n">
-        <v>57497</v>
+        <v>79853</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7257,53 +7257,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494329</v>
+        <v>494707</v>
       </c>
       <c r="R64" t="n">
-        <v>7023594</v>
+        <v>7023829</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7365,7 +7346,7 @@
         <v>122789892</v>
       </c>
       <c r="B65" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7464,10 +7445,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122791391</v>
+        <v>122789797</v>
       </c>
       <c r="B66" t="n">
-        <v>79850</v>
+        <v>57497</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7480,34 +7461,53 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494717</v>
+        <v>494329</v>
       </c>
       <c r="R66" t="n">
-        <v>7023829</v>
+        <v>7023594</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122774372</v>
+        <v>122774455</v>
       </c>
       <c r="B2" t="n">
-        <v>79852</v>
+        <v>91524</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494839</v>
+        <v>494571</v>
       </c>
       <c r="R2" t="n">
-        <v>7023830</v>
+        <v>7023780</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122774455</v>
+        <v>122774372</v>
       </c>
       <c r="B3" t="n">
-        <v>91524</v>
+        <v>79852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494571</v>
+        <v>494839</v>
       </c>
       <c r="R3" t="n">
-        <v>7023780</v>
+        <v>7023830</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -2998,10 +2998,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122771901</v>
+        <v>122772081</v>
       </c>
       <c r="B24" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3014,39 +3014,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494516</v>
+        <v>494512</v>
       </c>
       <c r="R24" t="n">
-        <v>7023586</v>
+        <v>7023641</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3079,11 +3074,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3110,10 +3100,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122772081</v>
+        <v>122771901</v>
       </c>
       <c r="B25" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3126,34 +3116,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494512</v>
+        <v>494516</v>
       </c>
       <c r="R25" t="n">
-        <v>7023641</v>
+        <v>7023586</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3186,6 +3181,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122774455</v>
+        <v>122771891</v>
       </c>
       <c r="B2" t="n">
-        <v>91524</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494571</v>
+        <v>494515</v>
       </c>
       <c r="R2" t="n">
-        <v>7023780</v>
+        <v>7023580</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122774372</v>
+        <v>122771489</v>
       </c>
       <c r="B3" t="n">
-        <v>79852</v>
+        <v>78772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494839</v>
+        <v>494147</v>
       </c>
       <c r="R3" t="n">
-        <v>7023830</v>
+        <v>7023571</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122774987</v>
+        <v>122772413</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494357</v>
+        <v>494559</v>
       </c>
       <c r="R4" t="n">
-        <v>7023735</v>
+        <v>7023689</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122774670</v>
+        <v>122772531</v>
       </c>
       <c r="B5" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494555</v>
+        <v>494557</v>
       </c>
       <c r="R5" t="n">
-        <v>7023779</v>
+        <v>7023650</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122774764</v>
+        <v>122774464</v>
       </c>
       <c r="B6" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,16 +1137,21 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494568</v>
+        <v>494570</v>
       </c>
       <c r="R6" t="n">
-        <v>7023757</v>
+        <v>7023783</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1184,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122772874</v>
+        <v>122773465</v>
       </c>
       <c r="B7" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494680</v>
+        <v>494786</v>
       </c>
       <c r="R7" t="n">
-        <v>7023737</v>
+        <v>7023741</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122774566</v>
+        <v>122774745</v>
       </c>
       <c r="B8" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494563</v>
+        <v>494558</v>
       </c>
       <c r="R8" t="n">
-        <v>7023786</v>
+        <v>7023767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122772729</v>
+        <v>122772985</v>
       </c>
       <c r="B9" t="n">
         <v>57481</v>
@@ -1454,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494591</v>
+        <v>494655</v>
       </c>
       <c r="R9" t="n">
-        <v>7023673</v>
+        <v>7023708</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122772707</v>
+        <v>122772356</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,39 +1547,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494582</v>
+        <v>494558</v>
       </c>
       <c r="R10" t="n">
-        <v>7023673</v>
+        <v>7023688</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122772994</v>
+        <v>122774372</v>
       </c>
       <c r="B11" t="n">
-        <v>57634</v>
+        <v>79853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,43 +1654,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494664</v>
+        <v>494839</v>
       </c>
       <c r="R11" t="n">
-        <v>7023760</v>
+        <v>7023830</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122773088</v>
+        <v>122772729</v>
       </c>
       <c r="B12" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,27 +1756,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1789,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494700</v>
+        <v>494591</v>
       </c>
       <c r="R12" t="n">
-        <v>7023729</v>
+        <v>7023673</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,6 +1821,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122772356</v>
+        <v>122772707</v>
       </c>
       <c r="B13" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,34 +1868,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494558</v>
+        <v>494582</v>
       </c>
       <c r="R13" t="n">
-        <v>7023688</v>
+        <v>7023673</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,7 +1937,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1958,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122774828</v>
+        <v>122773254</v>
       </c>
       <c r="B14" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1992,16 +1998,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494562</v>
+        <v>494730</v>
       </c>
       <c r="R14" t="n">
-        <v>7023728</v>
+        <v>7023730</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122771655</v>
+        <v>122771384</v>
       </c>
       <c r="B15" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2100,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494427</v>
+        <v>494334</v>
       </c>
       <c r="R15" t="n">
-        <v>7023595</v>
+        <v>7023580</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122774393</v>
+        <v>122774987</v>
       </c>
       <c r="B16" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2178,34 +2189,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494710</v>
+        <v>494357</v>
       </c>
       <c r="R16" t="n">
-        <v>7023786</v>
+        <v>7023735</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,6 +2254,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2264,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122774464</v>
+        <v>122772874</v>
       </c>
       <c r="B17" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2309,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494570</v>
+        <v>494680</v>
       </c>
       <c r="R17" t="n">
-        <v>7023783</v>
+        <v>7023737</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122774715</v>
+        <v>122774566</v>
       </c>
       <c r="B18" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494547</v>
+        <v>494563</v>
       </c>
       <c r="R18" t="n">
-        <v>7023756</v>
+        <v>7023786</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2473,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122774597</v>
+        <v>122772030</v>
       </c>
       <c r="B19" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494556</v>
+        <v>494526</v>
       </c>
       <c r="R19" t="n">
-        <v>7023778</v>
+        <v>7023606</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2575,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122771489</v>
+        <v>122771667</v>
       </c>
       <c r="B20" t="n">
-        <v>78771</v>
+        <v>79813</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,38 +2608,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494147</v>
+        <v>494425</v>
       </c>
       <c r="R20" t="n">
-        <v>7023571</v>
+        <v>7023600</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2677,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122774777</v>
+        <v>122771661</v>
       </c>
       <c r="B21" t="n">
-        <v>79852</v>
+        <v>79882</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2689,25 +2710,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2717,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494582</v>
+        <v>494425</v>
       </c>
       <c r="R21" t="n">
-        <v>7023728</v>
+        <v>7023600</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2753,11 +2774,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2784,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122777145</v>
+        <v>122772081</v>
       </c>
       <c r="B22" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2800,39 +2816,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494559</v>
+        <v>494512</v>
       </c>
       <c r="R22" t="n">
-        <v>7023653</v>
+        <v>7023641</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,11 +2876,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2896,7 +2902,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122773458</v>
+        <v>122774693</v>
       </c>
       <c r="B23" t="n">
         <v>79853</v>
@@ -2912,21 +2918,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2936,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494786</v>
+        <v>494544</v>
       </c>
       <c r="R23" t="n">
-        <v>7023741</v>
+        <v>7023772</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2998,10 +3004,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122772081</v>
+        <v>122772044</v>
       </c>
       <c r="B24" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3038,10 +3044,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494512</v>
+        <v>494524</v>
       </c>
       <c r="R24" t="n">
-        <v>7023641</v>
+        <v>7023624</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3100,10 +3106,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122771901</v>
+        <v>122771745</v>
       </c>
       <c r="B25" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3116,39 +3122,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494516</v>
+        <v>494449</v>
       </c>
       <c r="R25" t="n">
-        <v>7023586</v>
+        <v>7023602</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,11 +3182,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3212,10 +3208,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122774745</v>
+        <v>122774764</v>
       </c>
       <c r="B26" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3252,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494558</v>
+        <v>494568</v>
       </c>
       <c r="R26" t="n">
-        <v>7023767</v>
+        <v>7023757</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3288,6 +3284,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3314,10 +3315,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122771661</v>
+        <v>122771655</v>
       </c>
       <c r="B27" t="n">
-        <v>79881</v>
+        <v>79853</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3326,25 +3327,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3354,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494425</v>
+        <v>494427</v>
       </c>
       <c r="R27" t="n">
-        <v>7023600</v>
+        <v>7023595</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3416,10 +3417,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122772985</v>
+        <v>122770882</v>
       </c>
       <c r="B28" t="n">
-        <v>57481</v>
+        <v>90981</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3432,39 +3433,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494655</v>
+        <v>494160</v>
       </c>
       <c r="R28" t="n">
-        <v>7023708</v>
+        <v>7023595</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3497,11 +3493,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3528,10 +3519,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122774538</v>
+        <v>122774393</v>
       </c>
       <c r="B29" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3562,21 +3553,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494563</v>
+        <v>494710</v>
       </c>
       <c r="R29" t="n">
-        <v>7023781</v>
+        <v>7023786</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3635,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122771474</v>
+        <v>122770429</v>
       </c>
       <c r="B30" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3651,39 +3637,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494356</v>
+        <v>493992</v>
       </c>
       <c r="R30" t="n">
-        <v>7023575</v>
+        <v>7023434</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3716,6 +3702,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3742,10 +3733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122772044</v>
+        <v>122773319</v>
       </c>
       <c r="B31" t="n">
-        <v>79852</v>
+        <v>90974</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3754,25 +3745,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3782,10 +3773,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494524</v>
+        <v>494758</v>
       </c>
       <c r="R31" t="n">
-        <v>7023624</v>
+        <v>7023767</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3844,10 +3835,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122773319</v>
+        <v>122774538</v>
       </c>
       <c r="B32" t="n">
-        <v>90968</v>
+        <v>79853</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3856,38 +3847,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494758</v>
+        <v>494563</v>
       </c>
       <c r="R32" t="n">
-        <v>7023767</v>
+        <v>7023781</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3946,10 +3942,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122771481</v>
+        <v>122774696</v>
       </c>
       <c r="B33" t="n">
-        <v>79888</v>
+        <v>79853</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3958,25 +3954,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3986,10 +3982,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494353</v>
+        <v>494538</v>
       </c>
       <c r="R33" t="n">
-        <v>7023580</v>
+        <v>7023761</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4022,6 +4018,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4048,10 +4049,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122773407</v>
+        <v>122771956</v>
       </c>
       <c r="B34" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4064,34 +4065,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494790</v>
+        <v>494521</v>
       </c>
       <c r="R34" t="n">
-        <v>7023741</v>
+        <v>7023591</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4128,7 +4134,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4155,10 +4161,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122773527</v>
+        <v>122771474</v>
       </c>
       <c r="B35" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4171,27 +4177,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4200,10 +4206,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494802</v>
+        <v>494356</v>
       </c>
       <c r="R35" t="n">
-        <v>7023657</v>
+        <v>7023575</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4236,11 +4242,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4267,7 +4268,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122774563</v>
+        <v>122773407</v>
       </c>
       <c r="B36" t="n">
         <v>79853</v>
@@ -4283,21 +4284,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4307,10 +4308,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494563</v>
+        <v>494790</v>
       </c>
       <c r="R36" t="n">
-        <v>7023786</v>
+        <v>7023741</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4343,6 +4344,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4369,10 +4375,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122770882</v>
+        <v>122774597</v>
       </c>
       <c r="B37" t="n">
-        <v>90975</v>
+        <v>79853</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4385,34 +4391,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494160</v>
+        <v>494556</v>
       </c>
       <c r="R37" t="n">
-        <v>7023595</v>
+        <v>7023778</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4471,10 +4477,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122773254</v>
+        <v>122774777</v>
       </c>
       <c r="B38" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4505,21 +4511,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494730</v>
+        <v>494582</v>
       </c>
       <c r="R38" t="n">
-        <v>7023730</v>
+        <v>7023728</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4552,6 +4553,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4578,10 +4584,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122771956</v>
+        <v>122774455</v>
       </c>
       <c r="B39" t="n">
-        <v>57481</v>
+        <v>91530</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4590,43 +4596,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494521</v>
+        <v>494571</v>
       </c>
       <c r="R39" t="n">
-        <v>7023591</v>
+        <v>7023780</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4659,11 +4660,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4690,10 +4686,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122771745</v>
+        <v>122771901</v>
       </c>
       <c r="B40" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4706,34 +4702,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494449</v>
+        <v>494516</v>
       </c>
       <c r="R40" t="n">
-        <v>7023602</v>
+        <v>7023586</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4766,6 +4767,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4792,10 +4798,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122772531</v>
+        <v>122773216</v>
       </c>
       <c r="B41" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4808,27 +4814,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4837,10 +4843,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494557</v>
+        <v>494716</v>
       </c>
       <c r="R41" t="n">
-        <v>7023650</v>
+        <v>7023730</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4873,11 +4879,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4904,10 +4905,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122772290</v>
+        <v>122773458</v>
       </c>
       <c r="B42" t="n">
-        <v>79852</v>
+        <v>79854</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4920,39 +4921,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494557</v>
+        <v>494786</v>
       </c>
       <c r="R42" t="n">
-        <v>7023675</v>
+        <v>7023741</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5011,10 +5007,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122772030</v>
+        <v>122774563</v>
       </c>
       <c r="B43" t="n">
-        <v>79852</v>
+        <v>79854</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5027,21 +5023,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5051,10 +5047,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494526</v>
+        <v>494563</v>
       </c>
       <c r="R43" t="n">
-        <v>7023606</v>
+        <v>7023786</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5113,10 +5109,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122771384</v>
+        <v>122772290</v>
       </c>
       <c r="B44" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5147,16 +5143,21 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494334</v>
+        <v>494557</v>
       </c>
       <c r="R44" t="n">
-        <v>7023580</v>
+        <v>7023675</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5215,10 +5216,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122771667</v>
+        <v>122774828</v>
       </c>
       <c r="B45" t="n">
-        <v>79812</v>
+        <v>79853</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5227,25 +5228,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5255,10 +5256,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494425</v>
+        <v>494562</v>
       </c>
       <c r="R45" t="n">
-        <v>7023600</v>
+        <v>7023728</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5317,10 +5318,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122770929</v>
+        <v>122771481</v>
       </c>
       <c r="B46" t="n">
-        <v>57634</v>
+        <v>79889</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5329,52 +5330,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494181</v>
+        <v>494353</v>
       </c>
       <c r="R46" t="n">
-        <v>7023603</v>
+        <v>7023580</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5433,10 +5420,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122773465</v>
+        <v>122773088</v>
       </c>
       <c r="B47" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5478,10 +5465,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494786</v>
+        <v>494700</v>
       </c>
       <c r="R47" t="n">
-        <v>7023741</v>
+        <v>7023729</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5540,10 +5527,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122774696</v>
+        <v>122772714</v>
       </c>
       <c r="B48" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5580,10 +5567,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494538</v>
+        <v>494589</v>
       </c>
       <c r="R48" t="n">
-        <v>7023761</v>
+        <v>7023675</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5616,11 +5603,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5647,10 +5629,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122774693</v>
+        <v>122772994</v>
       </c>
       <c r="B49" t="n">
-        <v>79852</v>
+        <v>57634</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5663,34 +5645,43 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494544</v>
+        <v>494664</v>
       </c>
       <c r="R49" t="n">
-        <v>7023772</v>
+        <v>7023760</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5749,10 +5740,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122773216</v>
+        <v>122777145</v>
       </c>
       <c r="B50" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5765,27 +5756,27 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5794,10 +5785,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494716</v>
+        <v>494559</v>
       </c>
       <c r="R50" t="n">
-        <v>7023730</v>
+        <v>7023653</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5830,6 +5821,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5856,10 +5852,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122771891</v>
+        <v>122770929</v>
       </c>
       <c r="B51" t="n">
-        <v>57481</v>
+        <v>57634</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5872,39 +5868,48 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Flakamyren, Flakamyren, Jmt</t>
+          <t>Rapptorpen, Rapptorpen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494515</v>
+        <v>494181</v>
       </c>
       <c r="R51" t="n">
-        <v>7023580</v>
+        <v>7023603</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5937,11 +5942,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5968,10 +5968,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122770429</v>
+        <v>122774670</v>
       </c>
       <c r="B52" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5984,39 +5984,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Rapptorpen, Rapptorpen, Jmt</t>
+          <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493992</v>
+        <v>494555</v>
       </c>
       <c r="R52" t="n">
-        <v>7023434</v>
+        <v>7023779</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6049,11 +6044,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6080,10 +6070,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122772714</v>
+        <v>122774715</v>
       </c>
       <c r="B53" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6120,10 +6110,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494589</v>
+        <v>494547</v>
       </c>
       <c r="R53" t="n">
-        <v>7023675</v>
+        <v>7023756</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6182,10 +6172,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122772413</v>
+        <v>122773527</v>
       </c>
       <c r="B54" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6198,34 +6188,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494559</v>
+        <v>494802</v>
       </c>
       <c r="R54" t="n">
-        <v>7023689</v>
+        <v>7023657</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6258,6 +6253,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6284,10 +6284,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122790286</v>
+        <v>122790194</v>
       </c>
       <c r="B55" t="n">
-        <v>79853</v>
+        <v>57481</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6300,34 +6300,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494551</v>
+        <v>494560</v>
       </c>
       <c r="R55" t="n">
-        <v>7023728</v>
+        <v>7023660</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6364,7 +6369,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6391,10 +6396,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122791151</v>
+        <v>122790839</v>
       </c>
       <c r="B56" t="n">
-        <v>79852</v>
+        <v>91651</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6403,43 +6408,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494727</v>
+        <v>494767</v>
       </c>
       <c r="R56" t="n">
-        <v>7023818</v>
+        <v>7023761</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6498,10 +6498,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122791391</v>
+        <v>122790286</v>
       </c>
       <c r="B57" t="n">
-        <v>79852</v>
+        <v>79854</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494717</v>
+        <v>494551</v>
       </c>
       <c r="R57" t="n">
-        <v>7023829</v>
+        <v>7023728</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6574,6 +6574,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6600,10 +6605,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122790194</v>
+        <v>122789784</v>
       </c>
       <c r="B58" t="n">
-        <v>57481</v>
+        <v>56683</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6616,16 +6621,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6633,10 +6638,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6645,10 +6654,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494560</v>
+        <v>494225</v>
       </c>
       <c r="R58" t="n">
-        <v>7023660</v>
+        <v>7023525</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6681,11 +6690,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6712,10 +6716,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122790839</v>
+        <v>122791171</v>
       </c>
       <c r="B59" t="n">
-        <v>91645</v>
+        <v>79853</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6724,25 +6728,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6752,10 +6756,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494767</v>
+        <v>494727</v>
       </c>
       <c r="R59" t="n">
-        <v>7023761</v>
+        <v>7023818</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6788,6 +6792,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6814,10 +6823,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122789784</v>
+        <v>122790826</v>
       </c>
       <c r="B60" t="n">
-        <v>56683</v>
+        <v>79853</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6830,43 +6839,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494225</v>
+        <v>494767</v>
       </c>
       <c r="R60" t="n">
-        <v>7023525</v>
+        <v>7023760</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6925,10 +6925,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122790289</v>
+        <v>122790452</v>
       </c>
       <c r="B61" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6959,16 +6959,21 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494551</v>
+        <v>494479</v>
       </c>
       <c r="R61" t="n">
-        <v>7023731</v>
+        <v>7023680</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7001,11 +7006,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7032,10 +7032,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122790826</v>
+        <v>122790289</v>
       </c>
       <c r="B62" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494767</v>
+        <v>494551</v>
       </c>
       <c r="R62" t="n">
-        <v>7023760</v>
+        <v>7023731</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7108,6 +7108,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7134,10 +7139,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122790452</v>
+        <v>122789797</v>
       </c>
       <c r="B63" t="n">
-        <v>79852</v>
+        <v>57497</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7150,27 +7155,41 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7179,10 +7198,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494479</v>
+        <v>494329</v>
       </c>
       <c r="R63" t="n">
-        <v>7023680</v>
+        <v>7023594</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7244,7 +7263,7 @@
         <v>122791209</v>
       </c>
       <c r="B64" t="n">
-        <v>79853</v>
+        <v>79854</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7343,10 +7362,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122789892</v>
+        <v>122791391</v>
       </c>
       <c r="B65" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7383,10 +7402,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494409</v>
+        <v>494717</v>
       </c>
       <c r="R65" t="n">
-        <v>7023573</v>
+        <v>7023829</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7445,10 +7464,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122789797</v>
+        <v>122789892</v>
       </c>
       <c r="B66" t="n">
-        <v>57497</v>
+        <v>79853</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7461,53 +7480,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Flakamyren, Flakamyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494329</v>
+        <v>494409</v>
       </c>
       <c r="R66" t="n">
-        <v>7023594</v>
+        <v>7023573</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -7569,7 +7569,7 @@
         <v>122773452</v>
       </c>
       <c r="B67" t="n">
-        <v>57431</v>
+        <v>57437</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -7569,7 +7569,7 @@
         <v>122773452</v>
       </c>
       <c r="B67" t="n">
-        <v>57437</v>
+        <v>57440</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>

--- a/artfynd/A 19022-2022 artfynd.xlsx
+++ b/artfynd/A 19022-2022 artfynd.xlsx
@@ -7569,7 +7569,7 @@
         <v>122773452</v>
       </c>
       <c r="B67" t="n">
-        <v>57440</v>
+        <v>57441</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
